--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -131,720 +131,720 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 어필 컷</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/ilan_appeal.png</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 (1/2)</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일란 어필 컷</t>
         </is>
       </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.appeal.ilan</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 어필 컷</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/juno_appeal.png</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 (1/2)</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">주노 어필 컷</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.appeal.juno</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 어필 컷</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/karin_appeal.png</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 (1/2)</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">카린 어필 컷 — 억지 웃음 + 카메라를 본다 (M06 §7 최우선 컷)</t>
         </is>
       </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.appeal.karin</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 어필 컷</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/mor_appeal.png</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 (1/2)</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">모르 어필 컷</t>
         </is>
       </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.appeal.mor</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0">
+      <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 어필 컷</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/sela_appeal.png</t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 (1/2)</t>
         </is>
       </c>
-      <c r="F6" s="0" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">셀라 어필 컷</t>
         </is>
       </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H6" s="0" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.appeal.sela</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0">
+      <c r="A7" s="2">
         <v>2</v>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/shop_bench.png</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1152×792</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">② 편성실 우측 — 작업대</t>
         </is>
       </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.shop.bench</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0">
+      <c r="A8" s="2">
         <v>2</v>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/shop_room.png</t>
         </is>
       </c>
-      <c r="D8" s="0" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">752×792</t>
         </is>
       </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">② 편성실 좌측 — 방문자가 서는 자리</t>
         </is>
       </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.shop.room</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0">
+      <c r="A9" s="2">
         <v>2</v>
       </c>
-      <c r="B9" s="0" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/tower.png</t>
         </is>
       </c>
-      <c r="D9" s="0" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">744×720</t>
         </is>
       </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F9" s="0" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">③ 생방송 전투 칸 배경 (던전)</t>
         </is>
       </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.tower</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0">
+      <c r="A10" s="2">
         <v>2</v>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 전신</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/body_ilan.png</t>
         </is>
       </c>
-      <c r="D10" s="0" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">752×792</t>
         </is>
       </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일란 전신</t>
         </is>
       </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.body.ilan</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0">
+      <c r="A11" s="2">
         <v>2</v>
       </c>
-      <c r="B11" s="0" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 전신</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/body_juno.png</t>
         </is>
       </c>
-      <c r="D11" s="0" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">752×792</t>
         </is>
       </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">주노 전신</t>
         </is>
       </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.body.juno</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0">
+      <c r="A12" s="2">
         <v>2</v>
       </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 전신</t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/body_karin.png</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">752×792</t>
         </is>
       </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">카린 전신 (상점 좌측)</t>
         </is>
       </c>
-      <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.body.karin</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0">
+      <c r="A13" s="2">
         <v>2</v>
       </c>
-      <c r="B13" s="0" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 전신</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/body_mor.png</t>
         </is>
       </c>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">752×792</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">모르 전신</t>
         </is>
       </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H13" s="0" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.body.mor</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0">
+      <c r="A14" s="2">
         <v>2</v>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 전신</t>
         </is>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/body_sela.png</t>
         </is>
       </c>
-      <c r="D14" s="0" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">752×792</t>
         </is>
       </c>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F14" s="0" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">셀라 전신</t>
         </is>
       </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.body.sela</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0">
+      <c r="A15" s="2">
         <v>2</v>
       </c>
-      <c r="B15" s="0" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 초상</t>
         </is>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/ilan.png</t>
         </is>
       </c>
-      <c r="D15" s="0" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E15" s="0" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 생방송(1/2) · 384×480 상점(1:1)</t>
         </is>
       </c>
-      <c r="F15" s="0" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일란 초상</t>
         </is>
       </c>
-      <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H15" s="0" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.portrait.ilan</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0">
+      <c r="A16" s="2">
         <v>2</v>
       </c>
-      <c r="B16" s="0" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 초상</t>
         </is>
       </c>
-      <c r="C16" s="0" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/juno.png</t>
         </is>
       </c>
-      <c r="D16" s="0" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E16" s="0" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 생방송(1/2) · 384×480 상점(1:1)</t>
         </is>
       </c>
-      <c r="F16" s="0" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">주노 초상</t>
         </is>
       </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H16" s="0" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.portrait.juno</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="0">
+      <c r="A17" s="2">
         <v>2</v>
       </c>
-      <c r="B17" s="0" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 초상</t>
         </is>
       </c>
-      <c r="C17" s="0" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/karin.png</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E17" s="0" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 생방송(1/2) · 384×480 상점(1:1)</t>
         </is>
       </c>
-      <c r="F17" s="0" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">카린 초상 (생방송 우상단)</t>
         </is>
       </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H17" s="0" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.portrait.karin</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0">
+      <c r="A18" s="2">
         <v>2</v>
       </c>
-      <c r="B18" s="0" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 초상</t>
         </is>
       </c>
-      <c r="C18" s="0" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/mor.png</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E18" s="0" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 생방송(1/2) · 384×480 상점(1:1)</t>
         </is>
       </c>
-      <c r="F18" s="0" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">모르 초상</t>
         </is>
       </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.portrait.mor</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="0">
+      <c r="A19" s="2">
         <v>2</v>
       </c>
-      <c r="B19" s="0" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 초상</t>
         </is>
       </c>
-      <c r="C19" s="0" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star/sela.png</t>
         </is>
       </c>
-      <c r="D19" s="0" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">384×480</t>
         </is>
       </c>
-      <c r="E19" s="0" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×240 생방송(1/2) · 384×480 상점(1:1)</t>
         </is>
       </c>
-      <c r="F19" s="0" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">셀라 초상</t>
         </is>
       </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H19" s="0" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">star.portrait.sela</t>
         </is>
@@ -971,80 +971,80 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="0">
+      <c r="A23" s="2">
         <v>3</v>
       </c>
-      <c r="B23" s="0" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C23" s="0" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/revive_bench.png</t>
         </is>
       </c>
-      <c r="D23" s="0" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1152×792</t>
         </is>
       </c>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">① 소생실 우측 (없으면 bg.shop.bench 를 쓴다)</t>
         </is>
       </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H23" s="0" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.revive.bench</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="0">
+      <c r="A24" s="2">
         <v>3</v>
       </c>
-      <c r="B24" s="0" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C24" s="0" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/revive_room.png</t>
         </is>
       </c>
-      <c r="D24" s="0" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">752×792</t>
         </is>
       </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F24" s="0" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">① 소생실 좌측 (없으면 bg.shop.room 을 쓴다)</t>
         </is>
       </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H24" s="0" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.revive.room</t>
         </is>
@@ -1091,432 +1091,432 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="0">
+      <c r="A26" s="2">
         <v>3</v>
       </c>
-      <c r="B26" s="0" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C26" s="0" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg/title_lamp1.png</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920×1080</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 램프 밝기 1/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg.title.lamp1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>3</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">배경</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg/title_lamp2.png</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920×1080</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 램프 밝기 2/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg.title.lamp2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>3</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">배경</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg/title_lamp3.png</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920×1080</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 램프 밝기 3/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg.title.lamp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>3</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">배경</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg/title_lamp4.png</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920×1080</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 램프 밝기 4/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg.title.lamp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>3</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">배경</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/title.png</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1920×1080</t>
         </is>
       </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">타이틀 화면 배경</t>
         </is>
       </c>
-      <c r="G26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H26" s="0" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.title</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="0">
+    <row r="31">
+      <c r="A31" s="2">
         <v>3</v>
       </c>
-      <c r="B27" s="0" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="C27" s="0" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy/beast.png</t>
         </is>
       </c>
-      <c r="D27" s="0" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">512×512</t>
         </is>
       </c>
-      <c r="E27" s="0" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256×256 (1/2)</t>
         </is>
       </c>
-      <c r="F27" s="0" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">짐승 — 23~30F</t>
         </is>
       </c>
-      <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H27" s="0" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy.beast</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="0">
+    <row r="32">
+      <c r="A32" s="2">
         <v>3</v>
       </c>
-      <c r="B28" s="0" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy/flame.png</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">512×512</t>
         </is>
       </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256×256 (1/2)</t>
         </is>
       </c>
-      <c r="F28" s="0" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">화염 — 23~30F</t>
         </is>
       </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H28" s="0" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy.flame</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="0">
+    <row r="33">
+      <c r="A33" s="2">
         <v>3</v>
       </c>
-      <c r="B29" s="0" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="C29" s="0" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy/gatekeeper.png</t>
         </is>
       </c>
-      <c r="D29" s="0" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">512×512</t>
         </is>
       </c>
-      <c r="E29" s="0" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256×256 (1/2)</t>
         </is>
       </c>
-      <c r="F29" s="0" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">문지기 — 31F 이상</t>
         </is>
       </c>
-      <c r="G29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H29" s="0" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy.gatekeeper</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="0">
+    <row r="34">
+      <c r="A34" s="2">
         <v>3</v>
       </c>
-      <c r="B30" s="0" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="C30" s="0" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy/husk.png</t>
         </is>
       </c>
-      <c r="D30" s="0" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">512×512</t>
         </is>
       </c>
-      <c r="E30" s="0" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256×256 (1/2)</t>
         </is>
       </c>
-      <c r="F30" s="0" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">껍데기 — 22F 이하</t>
         </is>
       </c>
-      <c r="G30" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H30" s="0" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy.husk</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="0">
+    <row r="35">
+      <c r="A35" s="2">
         <v>3</v>
       </c>
-      <c r="B31" s="0" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="C31" s="0" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy/rat.png</t>
         </is>
       </c>
-      <c r="D31" s="0" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">512×512</t>
         </is>
       </c>
-      <c r="E31" s="0" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256×256 (1/2)</t>
         </is>
       </c>
-      <c r="F31" s="0" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">쥐 — 22F 이하</t>
         </is>
       </c>
-      <c r="G31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H31" s="0" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">enemy.rat</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0">
-        <v>3</v>
-      </c>
-      <c r="B32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 버튼</t>
-        </is>
-      </c>
-      <c r="C32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/button_danger.png</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 위험 (소생·어필·훼손)</t>
-        </is>
-      </c>
-      <c r="G32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.button.danger.9s</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0">
-        <v>3</v>
-      </c>
-      <c r="B33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 버튼</t>
-        </is>
-      </c>
-      <c r="C33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/button_ghost.png</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 보조 (테두리만 · 비활성/돌아가기)</t>
-        </is>
-      </c>
-      <c r="G33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.button.ghost.9s</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0">
-        <v>3</v>
-      </c>
-      <c r="B34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 버튼</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/button_hover.png</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 마우스오버</t>
-        </is>
-      </c>
-      <c r="G34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.button.hover.9s</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0">
-        <v>3</v>
-      </c>
-      <c r="B35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 버튼</t>
-        </is>
-      </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/button.png</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 평상</t>
-        </is>
-      </c>
-      <c r="G35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.button.9s</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/stamp.wav</t>
+          <t xml:space="preserve">ui/button_danger.png</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">32×32</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 찍는 소리</t>
+          <t xml:space="preserve">버튼 위험 (소생·어필·훼손)</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
@@ -1526,37 +1526,37 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.stamp</t>
+          <t xml:space="preserve">ui.button.danger.9s</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/superchat.wav</t>
+          <t xml:space="preserve">ui/button_ghost.png</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">32×32</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">슈퍼챗 알림</t>
+          <t xml:space="preserve">버튼 보조 (테두리만 · 비활성/돌아가기)</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
@@ -1566,37 +1566,37 @@
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.superchat</t>
+          <t xml:space="preserve">ui.button.ghost.9s</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/lamp.png</t>
+          <t xml:space="preserve">ui/button_hover.png</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">224×352</t>
+          <t xml:space="preserve">32×32</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 램프 (광원)</t>
+          <t xml:space="preserve">버튼 마우스오버</t>
         </is>
       </c>
       <c r="G38" s="0" t="inlineStr">
@@ -1606,37 +1606,37 @@
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.lamp</t>
+          <t xml:space="preserve">ui.button.hover.9s</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/ledger.png</t>
+          <t xml:space="preserve">ui/button.png</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">336×264</t>
+          <t xml:space="preserve">32×32</t>
         </is>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">장부</t>
+          <t xml:space="preserve">버튼 평상</t>
         </is>
       </c>
       <c r="G39" s="0" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.ledger</t>
+          <t xml:space="preserve">ui.button.9s</t>
         </is>
       </c>
     </row>
@@ -1656,17 +1656,17 @@
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/scroll.png</t>
+          <t xml:space="preserve">bgm/live.wav</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">176×64</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">두루마리</t>
+          <t xml:space="preserve">생방송 BGM — 하강 중 (긴장)</t>
         </is>
       </c>
       <c r="G40" s="0" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.scroll</t>
+          <t xml:space="preserve">bgm.live</t>
         </is>
       </c>
     </row>
@@ -1696,17 +1696,17 @@
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/stamp.png</t>
+          <t xml:space="preserve">bgm/shop.wav</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">128×208</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">도장</t>
+          <t xml:space="preserve">상점 BGM — 소생실·편성실 (낮고 느리게)</t>
         </is>
       </c>
       <c r="G41" s="0" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.stamp</t>
+          <t xml:space="preserve">bgm.shop</t>
         </is>
       </c>
     </row>
@@ -1736,17 +1736,17 @@
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tag.png</t>
+          <t xml:space="preserve">sfx/click.wav</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">152×104</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E42" s="0" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">가격표</t>
+          <t xml:space="preserve">버튼 누름</t>
         </is>
       </c>
       <c r="G42" s="0" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tag</t>
+          <t xml:space="preserve">sfx.click</t>
         </is>
       </c>
     </row>
@@ -1776,27 +1776,27 @@
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/silhouette.png</t>
+          <t xml:space="preserve">sfx/death.wav</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1536×480</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
         </is>
       </c>
       <c r="G43" s="0" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.silhouette</t>
+          <t xml:space="preserve">sfx.death</t>
         </is>
       </c>
     </row>
@@ -1816,17 +1816,17 @@
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/logo.png</t>
+          <t xml:space="preserve">sfx/record.wav</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">960×240</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 로고</t>
+          <t xml:space="preserve">신기록 갱신</t>
         </is>
       </c>
       <c r="G44" s="0" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.logo</t>
+          <t xml:space="preserve">sfx.record</t>
         </is>
       </c>
     </row>
@@ -1856,27 +1856,27 @@
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/seal.png</t>
+          <t xml:space="preserve">sfx/revive.wav</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">768×192</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
+          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
         </is>
       </c>
       <c r="G45" s="0" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.seal</t>
+          <t xml:space="preserve">sfx.revive</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,27 @@
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 패널</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/panel_sunken.png</t>
+          <t xml:space="preserve">sfx/stamp.wav</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">48×48</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
+          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
         </is>
       </c>
       <c r="G46" s="0" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.panel.sunken.9s</t>
+          <t xml:space="preserve">sfx.stamp</t>
         </is>
       </c>
     </row>
@@ -1936,41 +1936,481 @@
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">소리</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sfx/superchat.wav</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">슈퍼챗 알림</t>
+        </is>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sfx.superchat</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0">
+        <v>4</v>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/lamp.png</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224×352</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업대 램프 (광원)</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.lamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0">
+        <v>4</v>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/ledger.png</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336×264</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장부</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0">
+        <v>4</v>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/scroll.png</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176×64</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">두루마리</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.scroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0">
+        <v>4</v>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/stamp.png</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128×208</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도장</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.stamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0">
+        <v>4</v>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/tag.png</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152×104</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가격표</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0">
+        <v>4</v>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/silhouette.png</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536×480</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.silhouette</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0">
+        <v>4</v>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/cursor.png</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32×32</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.cursor</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0">
+        <v>4</v>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0">
+        <v>4</v>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0">
+        <v>4</v>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C47" s="0" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/panel_sunken.png</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48×48</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.panel.sunken.9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0">
+        <v>4</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 패널</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D47" s="0" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E47" s="0" t="inlineStr">
+      <c r="E58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F47" s="0" t="inlineStr">
+      <c r="F58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G47" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H47" s="0" t="inlineStr">
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H47"/>
+  <autoFilter ref="A1:H58"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -891,40 +891,40 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="0">
+      <c r="A21" s="2">
         <v>3</v>
       </c>
-      <c r="B21" s="0" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C21" s="0" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/death.png</t>
         </is>
       </c>
-      <c r="D21" s="0" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1920×936</t>
         </is>
       </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">④ 사망 화면</t>
         </is>
       </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.death</t>
         </is>
@@ -2331,86 +2331,286 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="0">
+      <c r="A57" s="2">
         <v>4</v>
       </c>
-      <c r="B57" s="0" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>4</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>4</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>4</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>4</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion5.png</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0">
+        <v>4</v>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C57" s="0" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D57" s="0" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E57" s="0" t="inlineStr">
+      <c r="E62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F57" s="0" t="inlineStr">
+      <c r="F62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G57" s="0" t="inlineStr">
+      <c r="G62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H57" s="0" t="inlineStr">
+      <c r="H62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="0">
+    <row r="63">
+      <c r="A63" s="0">
         <v>4</v>
       </c>
-      <c r="B58" s="0" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C58" s="0" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D58" s="0" t="inlineStr">
+      <c r="D63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E58" s="0" t="inlineStr">
+      <c r="E63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F58" s="0" t="inlineStr">
+      <c r="F63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G58" s="0" t="inlineStr">
+      <c r="G63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H58" s="0" t="inlineStr">
+      <c r="H63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H58"/>
+  <autoFilter ref="A1:H63"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -851,40 +851,40 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0">
+      <c r="A20" s="2">
         <v>3</v>
       </c>
-      <c r="B20" s="0" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C20" s="0" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/autopsy.png</t>
         </is>
       </c>
-      <c r="D20" s="0" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1920×936</t>
         </is>
       </c>
-      <c r="E20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F20" s="0" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">⑤ 검시실</t>
         </is>
       </c>
-      <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H20" s="0" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.autopsy</t>
         </is>
@@ -931,40 +931,40 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="0">
+      <c r="A22" s="2">
         <v>3</v>
       </c>
-      <c r="B22" s="0" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C22" s="0" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/live.png</t>
         </is>
       </c>
-      <c r="D22" s="0" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1920×1080</t>
         </is>
       </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">③ 생방송 5분할 바탕 (칸 사이 여백)</t>
         </is>
       </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.live</t>
         </is>
@@ -1051,40 +1051,40 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="0">
+      <c r="A25" s="2">
         <v>3</v>
       </c>
-      <c r="B25" s="0" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C25" s="0" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/studio.png</t>
         </is>
       </c>
-      <c r="D25" s="0" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1920×936</t>
         </is>
       </c>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F25" s="0" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">⑥ 발표 스튜디오</t>
         </is>
       </c>
-      <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H25" s="0" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.studio</t>
         </is>
@@ -1491,40 +1491,40 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="0">
+      <c r="A36" s="2">
         <v>3</v>
       </c>
-      <c r="B36" s="0" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
-      <c r="C36" s="0" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/button_danger.png</t>
         </is>
       </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F36" s="0" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208×88</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼 위험 (소생·어필·훼손)</t>
         </is>
       </c>
-      <c r="G36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H36" s="0" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.button.danger.9s</t>
         </is>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">32×32</t>
+          <t xml:space="preserve">208×88</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
+          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
@@ -1571,80 +1571,80 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="0">
+      <c r="A38" s="2">
         <v>3</v>
       </c>
-      <c r="B38" s="0" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
-      <c r="C38" s="0" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/button_hover.png</t>
         </is>
       </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E38" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F38" s="0" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208×88</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼 마우스오버</t>
         </is>
       </c>
-      <c r="G38" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H38" s="0" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.button.hover.9s</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="0">
+      <c r="A39" s="2">
         <v>3</v>
       </c>
-      <c r="B39" s="0" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
-      <c r="C39" s="0" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/button.png</t>
         </is>
       </c>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F39" s="0" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208×88</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼 평상</t>
         </is>
       </c>
-      <c r="G39" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H39" s="0" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.button.9s</t>
         </is>
@@ -1971,200 +1971,200 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="0">
-        <v>4</v>
-      </c>
-      <c r="B48" s="0" t="inlineStr">
+      <c r="A48" s="2">
+        <v>4</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">소품</t>
         </is>
       </c>
-      <c r="C48" s="0" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop/lamp.png</t>
         </is>
       </c>
-      <c r="D48" s="0" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">224×352</t>
         </is>
       </c>
-      <c r="E48" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F48" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작업대 램프 (광원)</t>
-        </is>
-      </c>
-      <c r="G48" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H48" s="0" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop.lamp</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="0">
-        <v>4</v>
-      </c>
-      <c r="B49" s="0" t="inlineStr">
+      <c r="A49" s="2">
+        <v>4</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">소품</t>
         </is>
       </c>
-      <c r="C49" s="0" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop/ledger.png</t>
         </is>
       </c>
-      <c r="D49" s="0" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">336×264</t>
         </is>
       </c>
-      <c r="E49" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F49" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">장부</t>
-        </is>
-      </c>
-      <c r="G49" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H49" s="0" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업대의 출연자 서류철</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop.ledger</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="0">
-        <v>4</v>
-      </c>
-      <c r="B50" s="0" t="inlineStr">
+      <c r="A50" s="2">
+        <v>4</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">소품</t>
         </is>
       </c>
-      <c r="C50" s="0" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop/scroll.png</t>
         </is>
       </c>
-      <c r="D50" s="0" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">176×64</t>
         </is>
       </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F50" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">두루마리</t>
-        </is>
-      </c>
-      <c r="G50" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H50" s="0" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계약서 서류 조각</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop.scroll</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="0">
-        <v>4</v>
-      </c>
-      <c r="B51" s="0" t="inlineStr">
+      <c r="A51" s="2">
+        <v>4</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">소품</t>
         </is>
       </c>
-      <c r="C51" s="0" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop/stamp.png</t>
         </is>
       </c>
-      <c r="D51" s="0" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">128×208</t>
         </is>
       </c>
-      <c r="E51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도장</t>
-        </is>
-      </c>
-      <c r="G51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H51" s="0" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop.stamp</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="0">
-        <v>4</v>
-      </c>
-      <c r="B52" s="0" t="inlineStr">
+      <c r="A52" s="2">
+        <v>4</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">소품</t>
         </is>
       </c>
-      <c r="C52" s="0" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop/tag.png</t>
         </is>
       </c>
-      <c r="D52" s="0" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">152×104</t>
         </is>
       </c>
-      <c r="E52" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F52" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가격표</t>
-        </is>
-      </c>
-      <c r="G52" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H52" s="0" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업대의 가격표</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prop.tag</t>
         </is>
@@ -2251,82 +2251,82 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="0">
-        <v>4</v>
-      </c>
-      <c r="B55" s="0" t="inlineStr">
+      <c r="A55" s="2">
+        <v>4</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D55" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E55" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F55" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G55" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H55" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/hud_status.png</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700×144</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.hud.status</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="0">
-        <v>4</v>
-      </c>
-      <c r="B56" s="0" t="inlineStr">
+      <c r="A56" s="2">
+        <v>4</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D56" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E56" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F56" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G56" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H56" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/hud_tools.png</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740×144</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.hud.tools</t>
         </is>
       </c>
     </row>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.icon.help.hover</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/icon_help.png</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.icon.help</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.icon.options.hover</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/icon_options.png</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.icon.options</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion5.png</t>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2526,47 +2526,47 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion5</t>
+          <t xml:space="preserve">ui.icon.save.hover</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="0">
-        <v>4</v>
-      </c>
-      <c r="B62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 패널</t>
-        </is>
-      </c>
-      <c r="C62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/panel_sunken.png</t>
-        </is>
-      </c>
-      <c r="D62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48×48</t>
-        </is>
-      </c>
-      <c r="E62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
-        </is>
-      </c>
-      <c r="G62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H62" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.panel.sunken.9s</t>
+      <c r="A62" s="2">
+        <v>4</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_save.png</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.save</t>
         </is>
       </c>
     </row>
@@ -2576,41 +2576,361 @@
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0">
+        <v>4</v>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>4</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <v>4</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <v>4</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2">
+        <v>4</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2">
+        <v>4</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion5.png</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0">
+        <v>4</v>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C63" s="0" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/panel_sunken.png</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48×48</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
+        </is>
+      </c>
+      <c r="F70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.panel.sunken.9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0">
+        <v>4</v>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 패널</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D63" s="0" t="inlineStr">
+      <c r="D71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E63" s="0" t="inlineStr">
+      <c r="E71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F63" s="0" t="inlineStr">
+      <c r="F71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G63" s="0" t="inlineStr">
+      <c r="G71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H63" s="0" t="inlineStr">
+      <c r="H71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H63"/>
+  <autoFilter ref="A1:H71"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -346,7 +346,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152×792</t>
+          <t xml:space="preserve">1244×792</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">650×792</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -426,7 +426,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">744×720</t>
+          <t xml:space="preserve">1000×792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">

--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -341,12 +341,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/shop_bench.png</t>
+          <t xml:space="preserve">bg/shop_bench_crop.png</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244×792</t>
+          <t xml:space="preserve">1645×1123</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/live.png</t>
+          <t xml:space="preserve">bg/live_desk.png</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×1080</t>
+          <t xml:space="preserve">738×936</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 생방송 5분할 바탕 (칸 사이 여백)</t>
+          <t xml:space="preserve">③ 생방송 좌측 책상 판 (지도·무전기가 올라간다)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.live</t>
+          <t xml:space="preserve">bg.live.desk</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/revive_bench.png</t>
+          <t xml:space="preserve">bg/live_final.png</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152×792</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">① 소생실 우측 (없으면 bg.shop.bench 를 쓴다)</t>
+          <t xml:space="preserve">③ 던전 · 최종 구역 (31F~)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.revive.bench</t>
+          <t xml:space="preserve">bg.live.final</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/revive_room.png</t>
+          <t xml:space="preserve">bg/live_flame.png</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">① 소생실 좌측 (없으면 bg.shop.room 을 쓴다)</t>
+          <t xml:space="preserve">③ 던전 · 화염 구역 (23~30F)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.revive.room</t>
+          <t xml:space="preserve">bg.live.flame</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/studio.png</t>
+          <t xml:space="preserve">bg/live_ice.png</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×936</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑥ 발표 스튜디오</t>
+          <t xml:space="preserve">③ 던전 · 얼음 구역 (23~30F)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.studio</t>
+          <t xml:space="preserve">bg.live.ice</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/title_lamp1.png</t>
+          <t xml:space="preserve">bg/live_stone.png</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×1080</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 램프 밝기 1/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+          <t xml:space="preserve">③ 던전 · 돌 구역 (~22F)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.title.lamp1</t>
+          <t xml:space="preserve">bg.live.stone</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/title_lamp2.png</t>
+          <t xml:space="preserve">bg/live.png</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 램프 밝기 2/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+          <t xml:space="preserve">③ 생방송 5분할 바탕 (칸 사이 여백)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1166,47 +1166,47 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.title.lamp2</t>
+          <t xml:space="preserve">bg.live</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2">
+      <c r="A28" s="0">
         <v>3</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bg/title_lamp3.png</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1920×1080</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 램프 밝기 3/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bg.title.lamp3</t>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg/revive_bench_crop.png</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1644×1122</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">① 소생실 우측 (없으면 bg.shop.bench 를 쓴다)</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bg.revive.bench</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/title_lamp4.png</t>
+          <t xml:space="preserve">bg/revive_room.png</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×1080</t>
+          <t xml:space="preserve">650×792</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 램프 밝기 4/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+          <t xml:space="preserve">① 소생실 좌측 (없으면 bg.shop.room 을 쓴다)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.title.lamp4</t>
+          <t xml:space="preserve">bg.revive.room</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/title.png</t>
+          <t xml:space="preserve">bg/studio.png</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×1080</t>
+          <t xml:space="preserve">1920×936</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 화면 배경</t>
+          <t xml:space="preserve">⑥ 발표 스튜디오</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.title</t>
+          <t xml:space="preserve">bg.studio</t>
         </is>
       </c>
     </row>
@@ -1296,27 +1296,27 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">적</t>
+          <t xml:space="preserve">배경</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/beast.png</t>
+          <t xml:space="preserve">bg/title_lamp1.png</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">512×512</t>
+          <t xml:space="preserve">1920×1080</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256×256 (1/2)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">짐승 — 23~30F</t>
+          <t xml:space="preserve">타이틀 램프 밝기 1/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.beast</t>
+          <t xml:space="preserve">bg.title.lamp1</t>
         </is>
       </c>
     </row>
@@ -1336,27 +1336,27 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">적</t>
+          <t xml:space="preserve">배경</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/flame.png</t>
+          <t xml:space="preserve">bg/title_lamp2.png</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">512×512</t>
+          <t xml:space="preserve">1920×1080</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256×256 (1/2)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">화염 — 23~30F</t>
+          <t xml:space="preserve">타이틀 램프 밝기 2/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.flame</t>
+          <t xml:space="preserve">bg.title.lamp2</t>
         </is>
       </c>
     </row>
@@ -1376,27 +1376,27 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">적</t>
+          <t xml:space="preserve">배경</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/gatekeeper.png</t>
+          <t xml:space="preserve">bg/title_lamp3.png</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">512×512</t>
+          <t xml:space="preserve">1920×1080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256×256 (1/2)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문지기 — 31F 이상</t>
+          <t xml:space="preserve">타이틀 램프 밝기 3/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.gatekeeper</t>
+          <t xml:space="preserve">bg.title.lamp3</t>
         </is>
       </c>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">적</t>
+          <t xml:space="preserve">배경</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/husk.png</t>
+          <t xml:space="preserve">bg/title_lamp4.png</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">512×512</t>
+          <t xml:space="preserve">1920×1080</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256×256 (1/2)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">껍데기 — 22F 이하</t>
+          <t xml:space="preserve">타이틀 램프 밝기 4/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.husk</t>
+          <t xml:space="preserve">bg.title.lamp4</t>
         </is>
       </c>
     </row>
@@ -1456,27 +1456,27 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">적</t>
+          <t xml:space="preserve">배경</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/rat.png</t>
+          <t xml:space="preserve">bg/title.png</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">512×512</t>
+          <t xml:space="preserve">1920×1080</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256×256 (1/2)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">쥐 — 22F 이하</t>
+          <t xml:space="preserve">타이틀 화면 배경</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.rat</t>
+          <t xml:space="preserve">bg.title</t>
         </is>
       </c>
     </row>
@@ -1496,27 +1496,27 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 버튼</t>
+          <t xml:space="preserve">적</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/button_danger.png</t>
+          <t xml:space="preserve">enemy/beast.png</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208×88</t>
+          <t xml:space="preserve">512×512</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
+          <t xml:space="preserve">256×256 (1/2)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 위험 (소생·어필·훼손)</t>
+          <t xml:space="preserve">짐승 — 23~30F</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1526,47 +1526,47 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.button.danger.9s</t>
+          <t xml:space="preserve">enemy.beast</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="0">
+      <c r="A37" s="2">
         <v>3</v>
       </c>
-      <c r="B37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 버튼</t>
-        </is>
-      </c>
-      <c r="C37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/button_ghost.png</t>
-        </is>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208×88</t>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
-        </is>
-      </c>
-      <c r="F37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 보조 (테두리만 · 비활성/돌아가기)</t>
-        </is>
-      </c>
-      <c r="G37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.button.ghost.9s</t>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">적</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy/flame.png</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">512×512</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256×256 (1/2)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화염 — 23~30F</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy.flame</t>
         </is>
       </c>
     </row>
@@ -1576,27 +1576,27 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 버튼</t>
+          <t xml:space="preserve">적</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/button_hover.png</t>
+          <t xml:space="preserve">enemy/gatekeeper.png</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208×88</t>
+          <t xml:space="preserve">512×512</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
+          <t xml:space="preserve">256×256 (1/2)</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 마우스오버</t>
+          <t xml:space="preserve">문지기 — 31F 이상</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.button.hover.9s</t>
+          <t xml:space="preserve">enemy.gatekeeper</t>
         </is>
       </c>
     </row>
@@ -1616,357 +1616,357 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">적</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy/husk.png</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">512×512</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256×256 (1/2)</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">껍데기 — 22F 이하</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy.husk</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>3</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">적</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy/rat.png</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">512×512</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256×256 (1/2)</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쥐 — 22F 이하</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy.rat</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>3</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/button.png</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/button_danger.png</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">208×88</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 평상</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.button.9s</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0">
-        <v>4</v>
-      </c>
-      <c r="B40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bgm/live.wav</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생방송 BGM — 하강 중 (긴장)</t>
-        </is>
-      </c>
-      <c r="G40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bgm.live</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0">
-        <v>4</v>
-      </c>
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타</t>
-        </is>
-      </c>
-      <c r="C41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bgm/shop.wav</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상점 BGM — 소생실·편성실 (낮고 느리게)</t>
-        </is>
-      </c>
-      <c r="G41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bgm.shop</t>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 위험 (소생·어필·훼손)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.button.danger.9s</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/click.wav</t>
+          <t xml:space="preserve">ui/button_ghost.png</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">208×88</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 보조 (테두리만 · 비활성/돌아가기)</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.button.ghost.9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>3</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 버튼</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/button_hover.png</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208×88</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 마우스오버</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.button.hover.9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>3</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 버튼</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/button.png</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208×88</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 평상</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.button.9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>4</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bgm/live.mp3</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 누름</t>
-        </is>
-      </c>
-      <c r="G42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx.click</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0">
-        <v>4</v>
-      </c>
-      <c r="B43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소리</t>
-        </is>
-      </c>
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx/death.wav</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생방송 BGM — 하강 중 (긴장)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bgm.live</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>4</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bgm/shop.mp3</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
-        </is>
-      </c>
-      <c r="G43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx.death</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0">
-        <v>4</v>
-      </c>
-      <c r="B44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소리</t>
-        </is>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx/record.wav</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상점 BGM — 소생실·편성실 (낮고 느리게)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bgm.shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>4</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bgm/title.mp3</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신기록 갱신</t>
-        </is>
-      </c>
-      <c r="G44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx.record</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0">
-        <v>4</v>
-      </c>
-      <c r="B45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소리</t>
-        </is>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx/revive.wav</t>
-        </is>
-      </c>
-      <c r="D45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
-        </is>
-      </c>
-      <c r="G45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx.revive</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0">
-        <v>4</v>
-      </c>
-      <c r="B46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소리</t>
-        </is>
-      </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx/stamp.wav</t>
-        </is>
-      </c>
-      <c r="D46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
-        </is>
-      </c>
-      <c r="G46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx.stamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0">
-        <v>4</v>
-      </c>
-      <c r="B47" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소리</t>
-        </is>
-      </c>
-      <c r="C47" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx/superchat.wav</t>
-        </is>
-      </c>
-      <c r="D47" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E47" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F47" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">슈퍼챗 알림</t>
-        </is>
-      </c>
-      <c r="G47" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H47" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sfx.superchat</t>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 화면 BGM</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bgm.title</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/lamp.png</t>
+          <t xml:space="preserve">item/blade_tallow.png</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224×352</t>
+          <t xml:space="preserve">174×189</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+          <t xml:space="preserve">촛농검 장비 도트</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.lamp</t>
+          <t xml:space="preserve">item.blade_tallow</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2016,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/ledger.png</t>
+          <t xml:space="preserve">item/boots_quiet.png</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336×264</t>
+          <t xml:space="preserve">165×159</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 출연자 서류철</t>
+          <t xml:space="preserve">죽은 자의 신발 장비 도트</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.ledger</t>
+          <t xml:space="preserve">item.boots_quiet</t>
         </is>
       </c>
     </row>
@@ -2056,17 +2056,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/scroll.png</t>
+          <t xml:space="preserve">item/charm_seal.png</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176×64</t>
+          <t xml:space="preserve">156×141</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 서류 조각</t>
+          <t xml:space="preserve">봉랍 부적 장비 도트</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.scroll</t>
+          <t xml:space="preserve">item.charm_seal</t>
         </is>
       </c>
     </row>
@@ -2096,17 +2096,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/stamp.png</t>
+          <t xml:space="preserve">item/cloak_ash.png</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128×208</t>
+          <t xml:space="preserve">144×171</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+          <t xml:space="preserve">재의 망토 장비 도트</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.stamp</t>
+          <t xml:space="preserve">item.cloak_ash</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tag.png</t>
+          <t xml:space="preserve">item/dagger_crack.png</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152×104</t>
+          <t xml:space="preserve">99×150</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 가격표</t>
+          <t xml:space="preserve">균열난 단검 장비 도트</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2166,87 +2166,87 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tag</t>
+          <t xml:space="preserve">item.dagger_crack</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="0">
-        <v>4</v>
-      </c>
-      <c r="B53" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
-        </is>
-      </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star/silhouette.png</t>
-        </is>
-      </c>
-      <c r="D53" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1536×480</t>
-        </is>
-      </c>
-      <c r="E53" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F53" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
-        </is>
-      </c>
-      <c r="G53" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H53" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star.silhouette</t>
+      <c r="A53" s="2">
+        <v>4</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item/lantern_old.png</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105×192</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">낡은 랜턴 장비 도트</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.lantern_old</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="0">
-        <v>4</v>
-      </c>
-      <c r="B54" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/cursor.png</t>
-        </is>
-      </c>
-      <c r="D54" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E54" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F54" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
-        </is>
-      </c>
-      <c r="G54" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H54" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.cursor</t>
+      <c r="A54" s="2">
+        <v>4</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item/mask_bone.png</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177×129</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뼈가면 장비 도트</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.mask_bone</t>
         </is>
       </c>
     </row>
@@ -2256,17 +2256,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">item/page_torn.png</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">156×147</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">찢어진 낱장 유품 도트</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">item.page_torn</t>
         </is>
       </c>
     </row>
@@ -2296,17 +2296,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
+          <t xml:space="preserve">item/potion_crimson.png</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×144</t>
+          <t xml:space="preserve">105×168</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+          <t xml:space="preserve">붉은 회복약 장비 도트</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+          <t xml:space="preserve">item.potion_crimson</t>
         </is>
       </c>
     </row>
@@ -2336,17 +2336,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">item/potion_moon.png</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">75×159</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">은빛 회복약 장비 도트</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">item.potion_moon</t>
         </is>
       </c>
     </row>
@@ -2376,17 +2376,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">item/ring_rust.png</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">108×105</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">녹슨 반지 장비 도트</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">item.ring_rust</t>
         </is>
       </c>
     </row>
@@ -2416,17 +2416,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">item/rope_hemp.png</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">117×147</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">삼줄 장비 도트</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">item.rope_hemp</t>
         </is>
       </c>
     </row>
@@ -2456,17 +2456,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">item/soil_deep.png</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">102×150</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">아래의 흙 한 줌 유품 도트</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">item.soil_deep</t>
         </is>
       </c>
     </row>
@@ -2496,17 +2496,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">item/tooth_gate.png</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">129×174</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">문지기의 이빨 장비 도트</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">item.tooth_gate</t>
         </is>
       </c>
     </row>
@@ -2536,17 +2536,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">sfx/click.mp3</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">버튼 누름</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2566,87 +2566,87 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">sfx.click</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="0">
-        <v>4</v>
-      </c>
-      <c r="B63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H63" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
+      <c r="A63" s="2">
+        <v>4</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소리</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sfx/death.mp3</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sfx.death</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="0">
-        <v>4</v>
-      </c>
-      <c r="B64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H64" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="A64" s="2">
+        <v>4</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소리</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sfx/record.mp3</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신기록 갱신</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sfx.record</t>
         </is>
       </c>
     </row>
@@ -2656,17 +2656,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">sfx/revive.mp3</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">sfx.revive</t>
         </is>
       </c>
     </row>
@@ -2696,17 +2696,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">sfx/stamp.mp3</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">sfx.stamp</t>
         </is>
       </c>
     </row>
@@ -2736,17 +2736,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">sfx/superchat.mp3</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">슈퍼챗 알림</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">sfx.superchat</t>
         </is>
       </c>
     </row>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">sfx/text.mp3</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">sfx.text</t>
         </is>
       </c>
     </row>
@@ -2816,121 +2816,1921 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">소리</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sfx/title_door.mp3</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sfx.title.door</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <v>4</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/lamp.png</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224×352</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.lamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <v>4</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/ledger.png</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336×264</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업대의 출연자 서류철</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <v>4</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/scroll.png</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176×64</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계약서 서류 조각</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.scroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <v>4</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/stamp.png</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128×208</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.stamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <v>4</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/tag.png</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152×104</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업대의 가격표</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0">
+        <v>4</v>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/silhouette.png</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536×480</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+        </is>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.silhouette</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <v>4</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/character_cover.png</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1087×258</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.guest.cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <v>4</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/clock_hour.png</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29×42</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUD game-clock hour hand</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.clock.hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2">
+        <v>4</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/clock_minute.png</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8×56</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUD game-clock minute hand</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.clock.minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2">
+        <v>4</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/contract_sheet.png</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700×914</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.contract.sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0">
+        <v>4</v>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/cursor.png</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32×32</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
+        </is>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.cursor</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2">
+        <v>4</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/hud_status.png</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700×144</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.hud.status</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2">
+        <v>4</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/hud_tools.png</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740×144</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.hud.tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2">
+        <v>4</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.help.hover</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <v>4</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_help.png</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.help</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2">
+        <v>4</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.options.hover</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2">
+        <v>4</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_options.png</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.options</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2">
+        <v>4</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.save.hover</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2">
+        <v>4</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_save.png</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.save</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2">
+        <v>4</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/inventory_window.png</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1452×831</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.window</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2">
+        <v>4</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×94</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2">
+        <v>4</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×302</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2">
+        <v>4</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_section.png</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×238</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.section</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2">
+        <v>4</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×177</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2">
+        <v>4</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_top.png</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×318</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.top</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2">
+        <v>4</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_window.png</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×1129</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장비 상세 정보창</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2">
+        <v>4</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_selected.png</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228×240</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2">
+        <v>4</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_badge.png</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206×74</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ LIVE 표시</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.badge</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2">
+        <v>4</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_blink.png</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26×28</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.blink</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2">
+        <v>4</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_chat.png</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424×298</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2">
+        <v>4</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1040×200</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.dialogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2">
+        <v>4</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_door.png</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.door</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2">
+        <v>4</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_floors.png</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2">
+        <v>4</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_lantern.png</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">460×568</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.lantern</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2">
+        <v>4</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_map.png</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620×786</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.map</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2">
+        <v>4</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_noise.png</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2">
+        <v>4</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_radio.png</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220×420</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 무전기</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2">
+        <v>4</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_superchat.png</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">528×86</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 슈퍼챗 한 줄 (고정 크기)</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.superchat</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0">
+        <v>4</v>
+      </c>
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0">
+        <v>4</v>
+      </c>
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2">
+        <v>4</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2">
+        <v>4</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2">
+        <v>4</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2">
+        <v>4</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2">
+        <v>4</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/suspicion5.png</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×128</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.suspicion5</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="0">
-        <v>4</v>
-      </c>
-      <c r="B70" s="0" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="0">
+        <v>4</v>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C70" s="0" t="inlineStr">
+      <c r="C115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D70" s="0" t="inlineStr">
+      <c r="D115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E70" s="0" t="inlineStr">
+      <c r="E115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F70" s="0" t="inlineStr">
+      <c r="F115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G70" s="0" t="inlineStr">
+      <c r="G115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H70" s="0" t="inlineStr">
+      <c r="H115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="0">
-        <v>4</v>
-      </c>
-      <c r="B71" s="0" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="0">
+        <v>4</v>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C71" s="0" t="inlineStr">
+      <c r="C116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D71" s="0" t="inlineStr">
+      <c r="D116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E71" s="0" t="inlineStr">
+      <c r="E116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F71" s="0" t="inlineStr">
+      <c r="F116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G71" s="0" t="inlineStr">
+      <c r="G116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H71" s="0" t="inlineStr">
+      <c r="H116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H71"/>
+  <autoFilter ref="A1:H116"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -1171,40 +1171,40 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="0">
+      <c r="A28" s="2">
         <v>3</v>
       </c>
-      <c r="B28" s="0" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배경</t>
         </is>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg/revive_bench_crop.png</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1644×1122</t>
         </is>
       </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F28" s="0" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">① 소생실 우측 (없으면 bg.shop.bench 를 쓴다)</t>
         </is>
       </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H28" s="0" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bg.revive.bench</t>
         </is>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm/title.mp3</t>
+          <t xml:space="preserve">bgm/title_noise.mp3</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 화면 BGM</t>
+          <t xml:space="preserve">타이틀 화면 저음량 백색소음</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm.title</t>
+          <t xml:space="preserve">bgm.title.noise</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/blade_tallow.png</t>
+          <t xml:space="preserve">bgm/title.mp3</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174×189</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">촛농검 장비 도트</t>
+          <t xml:space="preserve">타이틀 화면 BGM (원본 앞 2초 제거)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.blade_tallow</t>
+          <t xml:space="preserve">bgm.title</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/boots_quiet.png</t>
+          <t xml:space="preserve">item/blade_tallow.png</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165×159</t>
+          <t xml:space="preserve">174×189</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">죽은 자의 신발 장비 도트</t>
+          <t xml:space="preserve">촛농검 장비 도트</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.boots_quiet</t>
+          <t xml:space="preserve">item.blade_tallow</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/charm_seal.png</t>
+          <t xml:space="preserve">item/boots_quiet.png</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156×141</t>
+          <t xml:space="preserve">165×159</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 부적 장비 도트</t>
+          <t xml:space="preserve">죽은 자의 신발 장비 도트</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.charm_seal</t>
+          <t xml:space="preserve">item.boots_quiet</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/cloak_ash.png</t>
+          <t xml:space="preserve">item/charm_seal.png</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144×171</t>
+          <t xml:space="preserve">156×141</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재의 망토 장비 도트</t>
+          <t xml:space="preserve">봉랍 부적 장비 도트</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.cloak_ash</t>
+          <t xml:space="preserve">item.charm_seal</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/dagger_crack.png</t>
+          <t xml:space="preserve">item/cloak_ash.png</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99×150</t>
+          <t xml:space="preserve">144×171</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">균열난 단검 장비 도트</t>
+          <t xml:space="preserve">재의 망토 장비 도트</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.dagger_crack</t>
+          <t xml:space="preserve">item.cloak_ash</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/lantern_old.png</t>
+          <t xml:space="preserve">item/dagger_crack.png</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105×192</t>
+          <t xml:space="preserve">99×150</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">낡은 랜턴 장비 도트</t>
+          <t xml:space="preserve">균열난 단검 장비 도트</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.lantern_old</t>
+          <t xml:space="preserve">item.dagger_crack</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/mask_bone.png</t>
+          <t xml:space="preserve">item/lantern_old.png</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177×129</t>
+          <t xml:space="preserve">105×192</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">뼈가면 장비 도트</t>
+          <t xml:space="preserve">낡은 랜턴 장비 도트</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.mask_bone</t>
+          <t xml:space="preserve">item.lantern_old</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/page_torn.png</t>
+          <t xml:space="preserve">item/mask_bone.png</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156×147</t>
+          <t xml:space="preserve">177×129</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">찢어진 낱장 유품 도트</t>
+          <t xml:space="preserve">뼈가면 장비 도트</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.page_torn</t>
+          <t xml:space="preserve">item.mask_bone</t>
         </is>
       </c>
     </row>
@@ -2301,12 +2301,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/potion_crimson.png</t>
+          <t xml:space="preserve">item/page_torn.png</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105×168</t>
+          <t xml:space="preserve">156×147</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">붉은 회복약 장비 도트</t>
+          <t xml:space="preserve">찢어진 낱장 유품 도트</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.potion_crimson</t>
+          <t xml:space="preserve">item.page_torn</t>
         </is>
       </c>
     </row>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/potion_moon.png</t>
+          <t xml:space="preserve">item/potion_crimson.png</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75×159</t>
+          <t xml:space="preserve">105×168</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">은빛 회복약 장비 도트</t>
+          <t xml:space="preserve">붉은 회복약 장비 도트</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.potion_moon</t>
+          <t xml:space="preserve">item.potion_crimson</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/ring_rust.png</t>
+          <t xml:space="preserve">item/potion_moon.png</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108×105</t>
+          <t xml:space="preserve">75×159</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">녹슨 반지 장비 도트</t>
+          <t xml:space="preserve">은빛 회복약 장비 도트</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.ring_rust</t>
+          <t xml:space="preserve">item.potion_moon</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/rope_hemp.png</t>
+          <t xml:space="preserve">item/ring_rust.png</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117×147</t>
+          <t xml:space="preserve">108×105</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼줄 장비 도트</t>
+          <t xml:space="preserve">녹슨 반지 장비 도트</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.rope_hemp</t>
+          <t xml:space="preserve">item.ring_rust</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/soil_deep.png</t>
+          <t xml:space="preserve">item/rope_hemp.png</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102×150</t>
+          <t xml:space="preserve">117×147</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래의 흙 한 줌 유품 도트</t>
+          <t xml:space="preserve">삼줄 장비 도트</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.soil_deep</t>
+          <t xml:space="preserve">item.rope_hemp</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/tooth_gate.png</t>
+          <t xml:space="preserve">item/soil_deep.png</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129×174</t>
+          <t xml:space="preserve">102×150</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문지기의 이빨 장비 도트</t>
+          <t xml:space="preserve">아래의 흙 한 줌 유품 도트</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.tooth_gate</t>
+          <t xml:space="preserve">item.soil_deep</t>
         </is>
       </c>
     </row>
@@ -2536,17 +2536,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/click.mp3</t>
+          <t xml:space="preserve">item/tooth_gate.png</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">129×174</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 누름</t>
+          <t xml:space="preserve">문지기의 이빨 장비 도트</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.click</t>
+          <t xml:space="preserve">item.tooth_gate</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/death.mp3</t>
+          <t xml:space="preserve">sfx/click.mp3</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
+          <t xml:space="preserve">버튼 누름</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.death</t>
+          <t xml:space="preserve">sfx.click</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/record.mp3</t>
+          <t xml:space="preserve">sfx/death.mp3</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신기록 갱신</t>
+          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.record</t>
+          <t xml:space="preserve">sfx.death</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive.mp3</t>
+          <t xml:space="preserve">sfx/record.mp3</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
+          <t xml:space="preserve">신기록 갱신</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive</t>
+          <t xml:space="preserve">sfx.record</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/stamp.mp3</t>
+          <t xml:space="preserve">sfx/revive.mp3</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
+          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.stamp</t>
+          <t xml:space="preserve">sfx.revive</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/superchat.mp3</t>
+          <t xml:space="preserve">sfx/stamp.mp3</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">슈퍼챗 알림</t>
+          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.superchat</t>
+          <t xml:space="preserve">sfx.stamp</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text.mp3</t>
+          <t xml:space="preserve">sfx/superchat.mp3</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
+          <t xml:space="preserve">슈퍼챗 알림</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text</t>
+          <t xml:space="preserve">sfx.superchat</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_door.mp3</t>
+          <t xml:space="preserve">sfx/text.mp3</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리</t>
+          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.door</t>
+          <t xml:space="preserve">sfx.text</t>
         </is>
       </c>
     </row>
@@ -2856,17 +2856,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/lamp.png</t>
+          <t xml:space="preserve">sfx/title_chime.mp3</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224×352</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.lamp</t>
+          <t xml:space="preserve">sfx.title.chime</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/ledger.png</t>
+          <t xml:space="preserve">sfx/title_door.mp3</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336×264</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 출연자 서류철</t>
+          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.ledger</t>
+          <t xml:space="preserve">sfx.title.door</t>
         </is>
       </c>
     </row>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/scroll.png</t>
+          <t xml:space="preserve">prop/lamp.png</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176×64</t>
+          <t xml:space="preserve">224×352</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 서류 조각</t>
+          <t xml:space="preserve">작업대의 실제 석유 램프</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.scroll</t>
+          <t xml:space="preserve">prop.lamp</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/stamp.png</t>
+          <t xml:space="preserve">prop/ledger.png</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128×208</t>
+          <t xml:space="preserve">336×264</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+          <t xml:space="preserve">작업대의 출연자 서류철</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.stamp</t>
+          <t xml:space="preserve">prop.ledger</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tag.png</t>
+          <t xml:space="preserve">prop/scroll.png</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152×104</t>
+          <t xml:space="preserve">176×64</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 가격표</t>
+          <t xml:space="preserve">계약서 서류 조각</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3046,47 +3046,47 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tag</t>
+          <t xml:space="preserve">prop.scroll</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="0">
-        <v>4</v>
-      </c>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star/silhouette.png</t>
-        </is>
-      </c>
-      <c r="D75" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1536×480</t>
-        </is>
-      </c>
-      <c r="E75" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F75" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
-        </is>
-      </c>
-      <c r="G75" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H75" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star.silhouette</t>
+      <c r="A75" s="2">
+        <v>4</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/stamp.png</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128×208</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.stamp</t>
         </is>
       </c>
     </row>
@@ -3096,17 +3096,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/character_cover.png</t>
+          <t xml:space="preserve">prop/tag.png</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1087×258</t>
+          <t xml:space="preserve">152×104</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
+          <t xml:space="preserve">작업대의 가격표</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3126,47 +3126,47 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.guest.cover</t>
+          <t xml:space="preserve">prop.tag</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2">
-        <v>4</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/clock_hour.png</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29×42</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HUD game-clock hour hand</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.clock.hour</t>
+      <c r="A77" s="0">
+        <v>4</v>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/silhouette.png</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536×480</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+        </is>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.silhouette</t>
         </is>
       </c>
     </row>
@@ -3181,12 +3181,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_minute.png</t>
+          <t xml:space="preserve">ui/character_cover.png</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8×56</t>
+          <t xml:space="preserve">1087×258</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock minute hand</t>
+          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.minute</t>
+          <t xml:space="preserve">ui.guest.cover</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/contract_sheet.png</t>
+          <t xml:space="preserve">ui/clock_hour.png</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×914</t>
+          <t xml:space="preserve">29×42</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
+          <t xml:space="preserve">HUD game-clock hour hand</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3246,47 +3246,47 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.contract.sheet</t>
+          <t xml:space="preserve">ui.clock.hour</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="0">
-        <v>4</v>
-      </c>
-      <c r="B80" s="0" t="inlineStr">
+      <c r="A80" s="2">
+        <v>4</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C80" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/cursor.png</t>
-        </is>
-      </c>
-      <c r="D80" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E80" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F80" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
-        </is>
-      </c>
-      <c r="G80" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H80" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.cursor</t>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/clock_minute.png</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8×56</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUD game-clock minute hand</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.clock.minute</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">ui/contract_sheet.png</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">700×914</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3326,47 +3326,47 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">ui.contract.sheet</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2">
-        <v>4</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="A82" s="0">
+        <v>4</v>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">740×144</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/cursor.png</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32×32</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.cursor</t>
         </is>
       </c>
     </row>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">ui/hud_status.png</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">700×144</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">ui.hud.status</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3421,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">ui/hud_tools.png</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">740×144</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">ui.hud.tools</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">ui.icon.help.hover</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">ui/icon_help.png</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">ui.icon.help</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">ui.icon.options.hover</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">ui/icon_options.png</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">ui.icon.options</t>
         </is>
       </c>
     </row>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452×831</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+          <t xml:space="preserve">ui.icon.save.hover</t>
         </is>
       </c>
     </row>
@@ -3661,12 +3661,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">ui/icon_save.png</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">ui.icon.save</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
+          <t xml:space="preserve">ui/inventory_window.png</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×302</t>
+          <t xml:space="preserve">1452×831</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+          <t xml:space="preserve">ui.inventory.window</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">536×94</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">536×302</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">ui/item_info_section.png</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">536×238</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">ui.inventory.info.section</t>
         </is>
       </c>
     </row>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">536×177</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
         </is>
       </c>
     </row>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_selected.png</t>
+          <t xml:space="preserve">ui/item_info_top.png</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×240</t>
+          <t xml:space="preserve">536×318</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">ui.inventory.info.top</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">ui/item_info_window.png</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">536×1129</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">장비 상세 정보창</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">ui.inventory.info</t>
         </is>
       </c>
     </row>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">ui/item_selected.png</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">228×240</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">ui.inventory.selected</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">ui/live_badge.png</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">206×74</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">③ LIVE 표시</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">ui.live.badge</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">ui/live_blink.png</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">26×28</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">ui.live.blink</t>
         </is>
       </c>
     </row>
@@ -4101,12 +4101,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">ui/live_chat.png</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">424×298</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">ui.live.chat</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">1040×200</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">ui.live.dialogue</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">ui/live_door.png</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">ui.live.door</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">ui/live_floors.png</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">ui.live.floors</t>
         </is>
       </c>
     </row>
@@ -4261,12 +4261,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">ui/live_lantern.png</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">460×568</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">ui.live.lantern</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">ui/live_map.png</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">620×786</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">ui.live.map</t>
         </is>
       </c>
     </row>
@@ -4341,192 +4341,192 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/live_noise.png</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2">
+        <v>4</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_radio.png</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220×420</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 무전기</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2">
+        <v>4</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/live_superchat.png</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">528×86</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">③ 슈퍼챗 한 줄 (고정 크기)</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.live.superchat</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="0">
-        <v>4</v>
-      </c>
-      <c r="B108" s="0" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="0">
+        <v>4</v>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C108" s="0" t="inlineStr">
+      <c r="C110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/logo.png</t>
         </is>
       </c>
-      <c r="D108" s="0" t="inlineStr">
+      <c r="D110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">960×240</t>
         </is>
       </c>
-      <c r="E108" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F108" s="0" t="inlineStr">
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">타이틀 로고</t>
         </is>
       </c>
-      <c r="G108" s="0" t="inlineStr">
+      <c r="G110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H108" s="0" t="inlineStr">
+      <c r="H110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.logo</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="0">
-        <v>4</v>
-      </c>
-      <c r="B109" s="0" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="0">
+        <v>4</v>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C109" s="0" t="inlineStr">
+      <c r="C111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/seal.png</t>
         </is>
       </c>
-      <c r="D109" s="0" t="inlineStr">
+      <c r="D111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">768×192</t>
         </is>
       </c>
-      <c r="E109" s="0" t="inlineStr">
+      <c r="E111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
         </is>
       </c>
-      <c r="F109" s="0" t="inlineStr">
+      <c r="F111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">봉랍 도장 4프레임</t>
         </is>
       </c>
-      <c r="G109" s="0" t="inlineStr">
+      <c r="G111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H109" s="0" t="inlineStr">
+      <c r="H111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.seal</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2">
-        <v>4</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×128</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.suspicion1</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2">
-        <v>4</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×128</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.suspicion2</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/suspicion1.png</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.suspicion1</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/suspicion2.png</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.suspicion2</t>
         </is>
       </c>
     </row>
@@ -4621,116 +4621,196 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2">
+        <v>4</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2">
+        <v>4</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/suspicion5.png</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×128</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.suspicion5</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="0">
-        <v>4</v>
-      </c>
-      <c r="B115" s="0" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="0">
+        <v>4</v>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C115" s="0" t="inlineStr">
+      <c r="C117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D115" s="0" t="inlineStr">
+      <c r="D117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E115" s="0" t="inlineStr">
+      <c r="E117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F115" s="0" t="inlineStr">
+      <c r="F117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G115" s="0" t="inlineStr">
+      <c r="G117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H115" s="0" t="inlineStr">
+      <c r="H117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="0">
-        <v>4</v>
-      </c>
-      <c r="B116" s="0" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="0">
+        <v>4</v>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C116" s="0" t="inlineStr">
+      <c r="C118" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D116" s="0" t="inlineStr">
+      <c r="D118" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E116" s="0" t="inlineStr">
+      <c r="E118" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F116" s="0" t="inlineStr">
+      <c r="F118" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G116" s="0" t="inlineStr">
+      <c r="G118" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H116" s="0" t="inlineStr">
+      <c r="H118" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H116"/>
+  <autoFilter ref="A1:H118"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -346,7 +346,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645×1123</t>
+          <t xml:space="preserve">1755×1198</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/live_stone.png</t>
+          <t xml:space="preserve">bg/live_screen_final.png</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">462×452</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 던전 · 돌 구역 (~22F)</t>
+          <t xml:space="preserve">③ 방송화면 액자 · 최종 구역</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.live.stone</t>
+          <t xml:space="preserve">bg.live.screen.final</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/live.png</t>
+          <t xml:space="preserve">bg/live_screen_flame.png</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×1080</t>
+          <t xml:space="preserve">462×452</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 생방송 5분할 바탕 (칸 사이 여백)</t>
+          <t xml:space="preserve">③ 방송화면 액자 · 화염 구역</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.live</t>
+          <t xml:space="preserve">bg.live.screen.flame</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/revive_bench_crop.png</t>
+          <t xml:space="preserve">bg/live_screen_ice.png</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644×1122</t>
+          <t xml:space="preserve">462×452</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">① 소생실 우측 (없으면 bg.shop.bench 를 쓴다)</t>
+          <t xml:space="preserve">③ 방송화면 액자 · 얼음 구역</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.revive.bench</t>
+          <t xml:space="preserve">bg.live.screen.ice</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/revive_room.png</t>
+          <t xml:space="preserve">bg/live_screen_stone.png</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">650×792</t>
+          <t xml:space="preserve">462×452</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">① 소생실 좌측 (없으면 bg.shop.room 을 쓴다)</t>
+          <t xml:space="preserve">③ 방송화면 액자 · 돌 구역 — 적 스프라이트 뒤에 깔린다</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.revive.room</t>
+          <t xml:space="preserve">bg.live.screen.stone</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/studio.png</t>
+          <t xml:space="preserve">bg/live_stone.png</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×936</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑥ 발표 스튜디오</t>
+          <t xml:space="preserve">③ 던전 · 돌 구역 (~22F)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.studio</t>
+          <t xml:space="preserve">bg.live.stone</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/title_lamp1.png</t>
+          <t xml:space="preserve">bg/live.png</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 램프 밝기 1/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+          <t xml:space="preserve">③ 생방송 5분할 바탕 (칸 사이 여백)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.title.lamp1</t>
+          <t xml:space="preserve">bg.live</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/title_lamp2.png</t>
+          <t xml:space="preserve">bg/revive_bench_crop.png</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×1080</t>
+          <t xml:space="preserve">1745×1191</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 램프 밝기 2/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+          <t xml:space="preserve">① 소생실 우측 (없으면 bg.shop.bench 를 쓴다)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.title.lamp2</t>
+          <t xml:space="preserve">bg.revive.bench</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/title_lamp3.png</t>
+          <t xml:space="preserve">bg/revive_room.png</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×1080</t>
+          <t xml:space="preserve">650×792</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 램프 밝기 3/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+          <t xml:space="preserve">① 소생실 좌측 (없으면 bg.shop.room 을 쓴다)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.title.lamp3</t>
+          <t xml:space="preserve">bg.revive.room</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/title_lamp4.png</t>
+          <t xml:space="preserve">bg/studio.png</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×1080</t>
+          <t xml:space="preserve">1920×936</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 램프 밝기 4/4 — 넣으면 창의 불빛이 깜빡인다 (4장 다 있어야 켜진다)</t>
+          <t xml:space="preserve">⑥ 발표 스튜디오</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.title.lamp4</t>
+          <t xml:space="preserve">bg.studio</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg/title.png</t>
+          <t xml:space="preserve">bg/title_lantern.png</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×1080</t>
+          <t xml:space="preserve">86×59</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 화면 배경</t>
+          <t xml:space="preserve">타이틀 처마등 실루엣 — 문 위 등 자리에 얹고 약하게 흔든다</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bg.title</t>
+          <t xml:space="preserve">bg.title.lantern</t>
         </is>
       </c>
     </row>
@@ -1496,27 +1496,27 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">적</t>
+          <t xml:space="preserve">배경</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/beast.png</t>
+          <t xml:space="preserve">bg/title_window.png</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">512×512</t>
+          <t xml:space="preserve">567×300</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256×256 (1/2)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">짐승 — 23~30F</t>
+          <t xml:space="preserve">타이틀 진열창 빛 조절판 — 창 위에 얹고 알파로 밝기를 조절한다 (lamp1~4 를 대체)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.beast</t>
+          <t xml:space="preserve">bg.title.window</t>
         </is>
       </c>
     </row>
@@ -1536,27 +1536,27 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">적</t>
+          <t xml:space="preserve">배경</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/flame.png</t>
+          <t xml:space="preserve">bg/title.png</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">512×512</t>
+          <t xml:space="preserve">1920×1080</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256×256 (1/2)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">화염 — 23~30F</t>
+          <t xml:space="preserve">타이틀 화면 배경</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.flame</t>
+          <t xml:space="preserve">bg.title</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/gatekeeper.png</t>
+          <t xml:space="preserve">enemy/beast.png</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문지기 — 31F 이상</t>
+          <t xml:space="preserve">짐승 — 23~30F</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.gatekeeper</t>
+          <t xml:space="preserve">enemy.beast</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/husk.png</t>
+          <t xml:space="preserve">enemy/flame.png</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">껍데기 — 22F 이하</t>
+          <t xml:space="preserve">화염 — 23~30F</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.husk</t>
+          <t xml:space="preserve">enemy.flame</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy/rat.png</t>
+          <t xml:space="preserve">enemy/gatekeeper.png</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">쥐 — 22F 이하</t>
+          <t xml:space="preserve">문지기 — 31F 이상</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemy.rat</t>
+          <t xml:space="preserve">enemy.gatekeeper</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 버튼</t>
+          <t xml:space="preserve">적</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/button_danger.png</t>
+          <t xml:space="preserve">enemy/husk.png</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208×88</t>
+          <t xml:space="preserve">512×512</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
+          <t xml:space="preserve">256×256 (1/2)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 위험 (소생·어필·훼손)</t>
+          <t xml:space="preserve">껍데기 — 22F 이하</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -1726,47 +1726,47 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.button.danger.9s</t>
+          <t xml:space="preserve">enemy.husk</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="0">
+      <c r="A42" s="2">
         <v>3</v>
       </c>
-      <c r="B42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 버튼</t>
-        </is>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/button_ghost.png</t>
-        </is>
-      </c>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208×88</t>
-        </is>
-      </c>
-      <c r="E42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 보조 (테두리만 · 비활성/돌아가기)</t>
-        </is>
-      </c>
-      <c r="G42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.button.ghost.9s</t>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">적</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy/rat.png</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">512×512</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256×256 (1/2)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쥐 — 22F 이하</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy.rat</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/button_hover.png</t>
+          <t xml:space="preserve">ui/button_danger.png</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 마우스오버</t>
+          <t xml:space="preserve">버튼 위험 (소생·어필·훼손)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -1806,77 +1806,77 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.button.hover.9s</t>
+          <t xml:space="preserve">ui.button.danger.9s</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2">
+      <c r="A44" s="0">
         <v>3</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/button.png</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/button_ghost.png</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">208×88</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼 평상</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.button.9s</t>
+      <c r="F44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼 보조 (테두리만 · 비활성/돌아가기)</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.button.ghost.9s</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타</t>
+          <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm/live.mp3</t>
+          <t xml:space="preserve">ui/button_hover.png</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">208×88</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생방송 BGM — 하강 중 (긴장)</t>
+          <t xml:space="preserve">버튼 마우스오버</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -1886,37 +1886,37 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm.live</t>
+          <t xml:space="preserve">ui.button.hover.9s</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타</t>
+          <t xml:space="preserve">UI · 버튼</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm/shop.mp3</t>
+          <t xml:space="preserve">ui/button.png</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">208×88</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">버튼 크기에 맞춰 늘어난다 (모서리 22px 고정)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상점 BGM — 소생실·편성실 (낮고 느리게)</t>
+          <t xml:space="preserve">버튼 평상</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm.shop</t>
+          <t xml:space="preserve">ui.button.9s</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm/title_noise.mp3</t>
+          <t xml:space="preserve">bgm/live.mp3</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 화면 저음량 백색소음</t>
+          <t xml:space="preserve">생방송 BGM — 하강 중 (긴장)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm.title.noise</t>
+          <t xml:space="preserve">bgm.live</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm/title.mp3</t>
+          <t xml:space="preserve">bgm/shop.mp3</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 화면 BGM (원본 앞 2초 제거)</t>
+          <t xml:space="preserve">상점 BGM — 소생실·편성실 (낮고 느리게)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm.title</t>
+          <t xml:space="preserve">bgm.shop</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/blade_tallow.png</t>
+          <t xml:space="preserve">bgm/title_noise.mp3</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174×189</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">촛농검 장비 도트</t>
+          <t xml:space="preserve">타이틀 화면 저음량 백색소음</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.blade_tallow</t>
+          <t xml:space="preserve">bgm.title.noise</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/boots_quiet.png</t>
+          <t xml:space="preserve">bgm/title.mp3</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165×159</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">죽은 자의 신발 장비 도트</t>
+          <t xml:space="preserve">타이틀 화면 BGM (원본 앞 2초 제거)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.boots_quiet</t>
+          <t xml:space="preserve">bgm.title</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/charm_seal.png</t>
+          <t xml:space="preserve">item/blade_tallow.png</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156×141</t>
+          <t xml:space="preserve">174×189</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 부적 장비 도트</t>
+          <t xml:space="preserve">촛농검 장비 도트</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.charm_seal</t>
+          <t xml:space="preserve">item.blade_tallow</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/cloak_ash.png</t>
+          <t xml:space="preserve">item/boots_quiet.png</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144×171</t>
+          <t xml:space="preserve">165×159</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재의 망토 장비 도트</t>
+          <t xml:space="preserve">죽은 자의 신발 장비 도트</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.cloak_ash</t>
+          <t xml:space="preserve">item.boots_quiet</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/dagger_crack.png</t>
+          <t xml:space="preserve">item/charm_seal.png</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99×150</t>
+          <t xml:space="preserve">156×141</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">균열난 단검 장비 도트</t>
+          <t xml:space="preserve">봉랍 부적 장비 도트</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.dagger_crack</t>
+          <t xml:space="preserve">item.charm_seal</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/lantern_old.png</t>
+          <t xml:space="preserve">item/cloak_ash.png</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105×192</t>
+          <t xml:space="preserve">144×171</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">낡은 랜턴 장비 도트</t>
+          <t xml:space="preserve">재의 망토 장비 도트</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.lantern_old</t>
+          <t xml:space="preserve">item.cloak_ash</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/mask_bone.png</t>
+          <t xml:space="preserve">item/dagger_crack.png</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177×129</t>
+          <t xml:space="preserve">99×150</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">뼈가면 장비 도트</t>
+          <t xml:space="preserve">균열난 단검 장비 도트</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.mask_bone</t>
+          <t xml:space="preserve">item.dagger_crack</t>
         </is>
       </c>
     </row>
@@ -2301,12 +2301,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/page_torn.png</t>
+          <t xml:space="preserve">item/lantern_old.png</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156×147</t>
+          <t xml:space="preserve">105×192</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">찢어진 낱장 유품 도트</t>
+          <t xml:space="preserve">낡은 랜턴 장비 도트</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.page_torn</t>
+          <t xml:space="preserve">item.lantern_old</t>
         </is>
       </c>
     </row>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/potion_crimson.png</t>
+          <t xml:space="preserve">item/mask_bone.png</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105×168</t>
+          <t xml:space="preserve">177×129</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">붉은 회복약 장비 도트</t>
+          <t xml:space="preserve">뼈가면 장비 도트</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.potion_crimson</t>
+          <t xml:space="preserve">item.mask_bone</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/potion_moon.png</t>
+          <t xml:space="preserve">item/page_torn.png</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75×159</t>
+          <t xml:space="preserve">156×147</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">은빛 회복약 장비 도트</t>
+          <t xml:space="preserve">찢어진 낱장 유품 도트</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.potion_moon</t>
+          <t xml:space="preserve">item.page_torn</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/ring_rust.png</t>
+          <t xml:space="preserve">item/potion_crimson.png</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108×105</t>
+          <t xml:space="preserve">105×168</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">녹슨 반지 장비 도트</t>
+          <t xml:space="preserve">붉은 회복약 장비 도트</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.ring_rust</t>
+          <t xml:space="preserve">item.potion_crimson</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/rope_hemp.png</t>
+          <t xml:space="preserve">item/potion_moon.png</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117×147</t>
+          <t xml:space="preserve">75×159</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼줄 장비 도트</t>
+          <t xml:space="preserve">은빛 회복약 장비 도트</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.rope_hemp</t>
+          <t xml:space="preserve">item.potion_moon</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/soil_deep.png</t>
+          <t xml:space="preserve">item/ring_rust.png</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102×150</t>
+          <t xml:space="preserve">108×105</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래의 흙 한 줌 유품 도트</t>
+          <t xml:space="preserve">녹슨 반지 장비 도트</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.soil_deep</t>
+          <t xml:space="preserve">item.ring_rust</t>
         </is>
       </c>
     </row>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/tooth_gate.png</t>
+          <t xml:space="preserve">item/rope_hemp.png</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129×174</t>
+          <t xml:space="preserve">117×147</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문지기의 이빨 장비 도트</t>
+          <t xml:space="preserve">삼줄 장비 도트</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.tooth_gate</t>
+          <t xml:space="preserve">item.rope_hemp</t>
         </is>
       </c>
     </row>
@@ -2576,17 +2576,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/click.mp3</t>
+          <t xml:space="preserve">item/soil_deep.png</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">102×150</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 누름</t>
+          <t xml:space="preserve">아래의 흙 한 줌 유품 도트</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.click</t>
+          <t xml:space="preserve">item.soil_deep</t>
         </is>
       </c>
     </row>
@@ -2616,17 +2616,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/death.mp3</t>
+          <t xml:space="preserve">item/tooth_gate.png</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">129×174</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
+          <t xml:space="preserve">문지기의 이빨 장비 도트</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.death</t>
+          <t xml:space="preserve">item.tooth_gate</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/record.mp3</t>
+          <t xml:space="preserve">sfx/click.mp3</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신기록 갱신</t>
+          <t xml:space="preserve">버튼 누름</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.record</t>
+          <t xml:space="preserve">sfx.click</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive.mp3</t>
+          <t xml:space="preserve">sfx/death.mp3</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
+          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive</t>
+          <t xml:space="preserve">sfx.death</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/stamp.mp3</t>
+          <t xml:space="preserve">sfx/record.mp3</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
+          <t xml:space="preserve">신기록 갱신</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.stamp</t>
+          <t xml:space="preserve">sfx.record</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/superchat.mp3</t>
+          <t xml:space="preserve">sfx/revive_knock.mp3</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">슈퍼챗 알림</t>
+          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.superchat</t>
+          <t xml:space="preserve">sfx.revive.knock</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text.mp3</t>
+          <t xml:space="preserve">sfx/revive.mp3</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
+          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text</t>
+          <t xml:space="preserve">sfx.revive</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_chime.mp3</t>
+          <t xml:space="preserve">sfx/stamp.mp3</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
+          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.chime</t>
+          <t xml:space="preserve">sfx.stamp</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_door.mp3</t>
+          <t xml:space="preserve">sfx/superchat.mp3</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
+          <t xml:space="preserve">슈퍼챗 알림</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.door</t>
+          <t xml:space="preserve">sfx.superchat</t>
         </is>
       </c>
     </row>
@@ -2936,17 +2936,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/lamp.png</t>
+          <t xml:space="preserve">sfx/text.mp3</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224×352</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.lamp</t>
+          <t xml:space="preserve">sfx.text</t>
         </is>
       </c>
     </row>
@@ -2976,17 +2976,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/ledger.png</t>
+          <t xml:space="preserve">sfx/title_chime.mp3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336×264</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 출연자 서류철</t>
+          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.ledger</t>
+          <t xml:space="preserve">sfx.title.chime</t>
         </is>
       </c>
     </row>
@@ -3016,17 +3016,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/scroll.png</t>
+          <t xml:space="preserve">sfx/title_door.mp3</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176×64</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 서류 조각</t>
+          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.scroll</t>
+          <t xml:space="preserve">sfx.title.door</t>
         </is>
       </c>
     </row>
@@ -3061,12 +3061,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/stamp.png</t>
+          <t xml:space="preserve">prop/lamp.png</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128×208</t>
+          <t xml:space="preserve">224×352</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+          <t xml:space="preserve">작업대의 실제 석유 램프</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.stamp</t>
+          <t xml:space="preserve">prop.lamp</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tag.png</t>
+          <t xml:space="preserve">prop/ledger.png</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152×104</t>
+          <t xml:space="preserve">336×264</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 가격표</t>
+          <t xml:space="preserve">작업대의 출연자 서류철</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3126,47 +3126,47 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tag</t>
+          <t xml:space="preserve">prop.ledger</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="0">
-        <v>4</v>
-      </c>
-      <c r="B77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
-        </is>
-      </c>
-      <c r="C77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star/silhouette.png</t>
-        </is>
-      </c>
-      <c r="D77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1536×480</t>
-        </is>
-      </c>
-      <c r="E77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
-        </is>
-      </c>
-      <c r="G77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star.silhouette</t>
+      <c r="A77" s="2">
+        <v>4</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소품</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop/scroll.png</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176×64</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계약서 서류 조각</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop.scroll</t>
         </is>
       </c>
     </row>
@@ -3176,17 +3176,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/character_cover.png</t>
+          <t xml:space="preserve">prop/stamp.png</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1087×258</t>
+          <t xml:space="preserve">128×208</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
+          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.guest.cover</t>
+          <t xml:space="preserve">prop.stamp</t>
         </is>
       </c>
     </row>
@@ -3216,17 +3216,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_hour.png</t>
+          <t xml:space="preserve">prop/tag.png</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29×42</t>
+          <t xml:space="preserve">152×104</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock hour hand</t>
+          <t xml:space="preserve">작업대의 가격표</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.hour</t>
+          <t xml:space="preserve">prop.tag</t>
         </is>
       </c>
     </row>
@@ -3256,17 +3256,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_minute.png</t>
+          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8×56</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock minute hand</t>
+          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.minute</t>
+          <t xml:space="preserve">star.expression.ilan.angry</t>
         </is>
       </c>
     </row>
@@ -3296,17 +3296,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/contract_sheet.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×914</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
+          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3326,47 +3326,47 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.contract.sheet</t>
+          <t xml:space="preserve">star.expression.ilan.blank</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="0">
-        <v>4</v>
-      </c>
-      <c r="B82" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C82" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/cursor.png</t>
-        </is>
-      </c>
-      <c r="D82" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E82" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F82" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
-        </is>
-      </c>
-      <c r="G82" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H82" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.cursor</t>
+      <c r="A82" s="2">
+        <v>4</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.ilan.blush</t>
         </is>
       </c>
     </row>
@@ -3376,17 +3376,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">star.expression.ilan.empty</t>
         </is>
       </c>
     </row>
@@ -3416,17 +3416,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
+          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×144</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+          <t xml:space="preserve">star.expression.ilan.neutral</t>
         </is>
       </c>
     </row>
@@ -3456,17 +3456,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">star.expression.ilan.pain</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">star.expression.ilan.sad</t>
         </is>
       </c>
     </row>
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">star.expression.ilan.smile</t>
         </is>
       </c>
     </row>
@@ -3576,17 +3576,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">star.expression.ilan.surprise</t>
         </is>
       </c>
     </row>
@@ -3616,17 +3616,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">star/expressions/juno_angry.png</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">juno angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">star.expression.juno.angry</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">star/expressions/juno_blank.png</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">juno blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">star.expression.juno.blank</t>
         </is>
       </c>
     </row>
@@ -3696,17 +3696,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
+          <t xml:space="preserve">star/expressions/juno_blush.png</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452×831</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
+          <t xml:space="preserve">juno blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+          <t xml:space="preserve">star.expression.juno.blush</t>
         </is>
       </c>
     </row>
@@ -3736,17 +3736,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">star/expressions/juno_empty.png</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">juno empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">star.expression.juno.empty</t>
         </is>
       </c>
     </row>
@@ -3776,17 +3776,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
+          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×302</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+          <t xml:space="preserve">star.expression.juno.neutral</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">star/expressions/juno_pain.png</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">juno pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">star.expression.juno.pain</t>
         </is>
       </c>
     </row>
@@ -3856,17 +3856,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">star/expressions/juno_sad.png</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">juno sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">star.expression.juno.sad</t>
         </is>
       </c>
     </row>
@@ -3896,17 +3896,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">star/expressions/juno_smile.png</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">juno smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">star.expression.juno.smile</t>
         </is>
       </c>
     </row>
@@ -3936,17 +3936,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">star.expression.juno.surprise</t>
         </is>
       </c>
     </row>
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_selected.png</t>
+          <t xml:space="preserve">star/expressions/karin_angry.png</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×240</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+          <t xml:space="preserve">karin angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">star.expression.karin.angry</t>
         </is>
       </c>
     </row>
@@ -4016,17 +4016,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">star/expressions/karin_blank.png</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">karin blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">star.expression.karin.blank</t>
         </is>
       </c>
     </row>
@@ -4056,17 +4056,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">star/expressions/karin_blush.png</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">karin blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">star.expression.karin.blush</t>
         </is>
       </c>
     </row>
@@ -4096,17 +4096,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">star/expressions/karin_empty.png</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">karin empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">star.expression.karin.empty</t>
         </is>
       </c>
     </row>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">star.expression.karin.neutral</t>
         </is>
       </c>
     </row>
@@ -4176,17 +4176,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">star/expressions/karin_pain.png</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">karin pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">star.expression.karin.pain</t>
         </is>
       </c>
     </row>
@@ -4216,17 +4216,17 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">star/expressions/karin_sad.png</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">karin sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">star.expression.karin.sad</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">star/expressions/karin_smile.png</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">karin smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">star.expression.karin.smile</t>
         </is>
       </c>
     </row>
@@ -4296,17 +4296,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">star.expression.karin.surprise</t>
         </is>
       </c>
     </row>
@@ -4336,17 +4336,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">star/expressions/mor_angry.png</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">mor angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">star.expression.mor.angry</t>
         </is>
       </c>
     </row>
@@ -4376,17 +4376,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">star/expressions/mor_blank.png</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">mor blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">star.expression.mor.blank</t>
         </is>
       </c>
     </row>
@@ -4416,17 +4416,17 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_superchat.png</t>
+          <t xml:space="preserve">star/expressions/mor_blush.png</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">528×86</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 슈퍼챗 한 줄 (고정 크기)</t>
+          <t xml:space="preserve">mor blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4446,87 +4446,87 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.superchat</t>
+          <t xml:space="preserve">star.expression.mor.blush</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="0">
-        <v>4</v>
-      </c>
-      <c r="B110" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C110" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D110" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E110" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F110" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G110" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H110" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
+      <c r="A110" s="2">
+        <v>4</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/mor_empty.png</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mor empty 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.mor.empty</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="0">
-        <v>4</v>
-      </c>
-      <c r="B111" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C111" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D111" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E111" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F111" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G111" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H111" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="A111" s="2">
+        <v>4</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.mor.neutral</t>
         </is>
       </c>
     </row>
@@ -4536,17 +4536,17 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">star/expressions/mor_pain.png</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">mor pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">star.expression.mor.pain</t>
         </is>
       </c>
     </row>
@@ -4576,17 +4576,17 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">star/expressions/mor_sad.png</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">mor sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">star.expression.mor.sad</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">star/expressions/mor_smile.png</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">mor smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">star.expression.mor.smile</t>
         </is>
       </c>
     </row>
@@ -4656,17 +4656,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">star.expression.mor.surprise</t>
         </is>
       </c>
     </row>
@@ -4696,121 +4696,2481 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/sela_angry.png</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela angry 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela.angry</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2">
+        <v>4</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/sela_blank.png</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela blank 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela.blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2">
+        <v>4</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/sela_blush.png</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela blush 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela.blush</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2">
+        <v>4</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/sela_empty.png</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela empty 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela.empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2">
+        <v>4</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela.neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2">
+        <v>4</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/sela_pain.png</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela pain 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela.pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2">
+        <v>4</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/sela_sad.png</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela sad 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela.sad</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2">
+        <v>4</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/sela_smile.png</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela smile 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela.smile</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2">
+        <v>4</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela.surprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2">
+        <v>4</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/ilan_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일란 대사 전신</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.dialogue.ilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2">
+        <v>4</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/ilan_expression.png</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일란 표정 전신</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.ilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2">
+        <v>4</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/juno_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주노 대사 전신</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.dialogue.juno</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2">
+        <v>4</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/juno_expression.png</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.juno</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2">
+        <v>4</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/karin_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카린 대사 전신</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.dialogue.karin</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2">
+        <v>4</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/karin_expression.png</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카린 표정 전신</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.karin</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2">
+        <v>4</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/mor_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모르 대사 전신</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.dialogue.mor</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2">
+        <v>4</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/mor_expression.png</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모르 표정 전신</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.mor</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2">
+        <v>4</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/sela_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세라 대사 전신</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.dialogue.sela</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2">
+        <v>4</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/sela_expression.png</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세라 표정 전신</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.sela</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0">
+        <v>4</v>
+      </c>
+      <c r="B135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/silhouette.png</t>
+        </is>
+      </c>
+      <c r="D135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536×480</t>
+        </is>
+      </c>
+      <c r="E135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+        </is>
+      </c>
+      <c r="G135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.silhouette</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2">
+        <v>4</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/character_cover.png</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1087×258</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.guest.cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2">
+        <v>4</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/clock_hour.png</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29×42</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUD game-clock hour hand</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.clock.hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2">
+        <v>4</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/clock_minute.png</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8×56</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUD game-clock minute hand</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.clock.minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2">
+        <v>4</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/contract_sheet.png</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700×914</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.contract.sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0">
+        <v>4</v>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/cursor.png</t>
+        </is>
+      </c>
+      <c r="D140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32×32</t>
+        </is>
+      </c>
+      <c r="E140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
+        </is>
+      </c>
+      <c r="G140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.cursor</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2">
+        <v>4</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/hud_status.png</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700×144</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.hud.status</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2">
+        <v>4</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/hud_tools.png</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740×144</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.hud.tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2">
+        <v>4</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.help.hover</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2">
+        <v>4</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_help.png</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.help</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2">
+        <v>4</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.options.hover</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2">
+        <v>4</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_options.png</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.options</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2">
+        <v>4</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.save.hover</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2">
+        <v>4</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_save.png</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.save</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2">
+        <v>4</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/inventory_window.png</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1452×831</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.window</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2">
+        <v>4</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×94</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2">
+        <v>4</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×302</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2">
+        <v>4</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_section.png</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×238</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.section</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2">
+        <v>4</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×177</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2">
+        <v>4</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_top.png</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×318</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.top</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2">
+        <v>4</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_window.png</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×1129</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장비 상세 정보창</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2">
+        <v>4</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_selected.png</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228×240</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2">
+        <v>4</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_badge.png</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206×74</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ LIVE 표시</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.badge</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2">
+        <v>4</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_blink.png</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26×28</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.blink</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2">
+        <v>4</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_chat.png</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424×298</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2">
+        <v>4</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1040×200</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.dialogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2">
+        <v>4</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_door.png</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.door</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2">
+        <v>4</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_floors.png</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2">
+        <v>4</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_lantern.png</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">460×568</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.lantern</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2">
+        <v>4</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_map.png</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620×786</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.map</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2">
+        <v>4</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_noise.png</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2">
+        <v>4</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_radio.png</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220×420</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 무전기</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2">
+        <v>4</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_superchat.png</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383×62</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.superchat</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0">
+        <v>4</v>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0">
+        <v>4</v>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2">
+        <v>4</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154×161</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.shelf.arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2">
+        <v>4</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2">
+        <v>4</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2">
+        <v>4</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2">
+        <v>4</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2">
+        <v>4</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/suspicion5.png</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×128</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.suspicion5</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="0">
-        <v>4</v>
-      </c>
-      <c r="B117" s="0" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="0">
+        <v>4</v>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C117" s="0" t="inlineStr">
+      <c r="C176" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D117" s="0" t="inlineStr">
+      <c r="D176" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E117" s="0" t="inlineStr">
+      <c r="E176" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F117" s="0" t="inlineStr">
+      <c r="F176" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G117" s="0" t="inlineStr">
+      <c r="G176" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H117" s="0" t="inlineStr">
+      <c r="H176" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="0">
-        <v>4</v>
-      </c>
-      <c r="B118" s="0" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="0">
+        <v>4</v>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C118" s="0" t="inlineStr">
+      <c r="C177" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D118" s="0" t="inlineStr">
+      <c r="D177" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E118" s="0" t="inlineStr">
+      <c r="E177" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F118" s="0" t="inlineStr">
+      <c r="F177" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G118" s="0" t="inlineStr">
+      <c r="G177" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H118" s="0" t="inlineStr">
+      <c r="H177" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H118"/>
+  <autoFilter ref="A1:H177"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생방송 BGM — 하강 중 (긴장)</t>
+          <t xml:space="preserve">③ 생방송 BGM — 하강 중 (사운드V4 · 던전기본브금 122초)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm/shop.mp3</t>
+          <t xml:space="preserve">bgm/revive.mp3</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상점 BGM — 소생실·편성실 (낮고 느리게)</t>
+          <t xml:space="preserve">① 소생실 BGM (사운드V4 · 소생실메인브금 122초)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm.shop</t>
+          <t xml:space="preserve">bgm.revive</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm/title_noise.mp3</t>
+          <t xml:space="preserve">bgm/shop.mp3</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 화면 저음량 백색소음</t>
+          <t xml:space="preserve">② 편성실 BGM (사운드V4 · 메인화면 브금 120초)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm.title.noise</t>
+          <t xml:space="preserve">bgm.shop</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm/title.mp3</t>
+          <t xml:space="preserve">bgm/tension.mp3</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 화면 BGM (원본 앞 2초 제거)</t>
+          <t xml:space="preserve">④⑤⑥ 사망·검시·발표 BGM (사운드V4 · 완전 똥줄타는 긴장감 123초)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bgm.title</t>
+          <t xml:space="preserve">bgm.tension</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/blade_tallow.png</t>
+          <t xml:space="preserve">bgm/title_noise.mp3</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174×189</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">촛농검 장비 도트</t>
+          <t xml:space="preserve">타이틀 화면 저음량 백색소음</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.blade_tallow</t>
+          <t xml:space="preserve">bgm.title.noise</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/boots_quiet.png</t>
+          <t xml:space="preserve">bgm/title.mp3</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165×159</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">죽은 자의 신발 장비 도트</t>
+          <t xml:space="preserve">타이틀 화면 BGM (원본 앞 2초 제거)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.boots_quiet</t>
+          <t xml:space="preserve">bgm.title</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/charm_seal.png</t>
+          <t xml:space="preserve">item/blade_tallow.png</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156×141</t>
+          <t xml:space="preserve">174×189</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 부적 장비 도트</t>
+          <t xml:space="preserve">촛농검 장비 도트</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.charm_seal</t>
+          <t xml:space="preserve">item.blade_tallow</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/cloak_ash.png</t>
+          <t xml:space="preserve">item/boots_quiet.png</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144×171</t>
+          <t xml:space="preserve">165×159</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재의 망토 장비 도트</t>
+          <t xml:space="preserve">죽은 자의 신발 장비 도트</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.cloak_ash</t>
+          <t xml:space="preserve">item.boots_quiet</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/dagger_crack.png</t>
+          <t xml:space="preserve">item/charm_seal.png</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99×150</t>
+          <t xml:space="preserve">156×141</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">균열난 단검 장비 도트</t>
+          <t xml:space="preserve">봉랍 부적 장비 도트</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.dagger_crack</t>
+          <t xml:space="preserve">item.charm_seal</t>
         </is>
       </c>
     </row>
@@ -2301,12 +2301,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/lantern_old.png</t>
+          <t xml:space="preserve">item/cloak_ash.png</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105×192</t>
+          <t xml:space="preserve">144×171</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">낡은 랜턴 장비 도트</t>
+          <t xml:space="preserve">재의 망토 장비 도트</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.lantern_old</t>
+          <t xml:space="preserve">item.cloak_ash</t>
         </is>
       </c>
     </row>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/mask_bone.png</t>
+          <t xml:space="preserve">item/dagger_crack.png</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177×129</t>
+          <t xml:space="preserve">99×150</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">뼈가면 장비 도트</t>
+          <t xml:space="preserve">균열난 단검 장비 도트</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.mask_bone</t>
+          <t xml:space="preserve">item.dagger_crack</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/page_torn.png</t>
+          <t xml:space="preserve">item/lantern_old.png</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156×147</t>
+          <t xml:space="preserve">105×192</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">찢어진 낱장 유품 도트</t>
+          <t xml:space="preserve">낡은 랜턴 장비 도트</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.page_torn</t>
+          <t xml:space="preserve">item.lantern_old</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/potion_crimson.png</t>
+          <t xml:space="preserve">item/mask_bone.png</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105×168</t>
+          <t xml:space="preserve">177×129</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">붉은 회복약 장비 도트</t>
+          <t xml:space="preserve">뼈가면 장비 도트</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.potion_crimson</t>
+          <t xml:space="preserve">item.mask_bone</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/potion_moon.png</t>
+          <t xml:space="preserve">item/page_torn.png</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75×159</t>
+          <t xml:space="preserve">156×147</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">은빛 회복약 장비 도트</t>
+          <t xml:space="preserve">찢어진 낱장 유품 도트</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.potion_moon</t>
+          <t xml:space="preserve">item.page_torn</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/ring_rust.png</t>
+          <t xml:space="preserve">item/potion_crimson.png</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108×105</t>
+          <t xml:space="preserve">105×168</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">녹슨 반지 장비 도트</t>
+          <t xml:space="preserve">붉은 회복약 장비 도트</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.ring_rust</t>
+          <t xml:space="preserve">item.potion_crimson</t>
         </is>
       </c>
     </row>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/rope_hemp.png</t>
+          <t xml:space="preserve">item/potion_moon.png</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117×147</t>
+          <t xml:space="preserve">75×159</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼줄 장비 도트</t>
+          <t xml:space="preserve">은빛 회복약 장비 도트</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.rope_hemp</t>
+          <t xml:space="preserve">item.potion_moon</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/soil_deep.png</t>
+          <t xml:space="preserve">item/ring_rust.png</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102×150</t>
+          <t xml:space="preserve">108×105</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래의 흙 한 줌 유품 도트</t>
+          <t xml:space="preserve">녹슨 반지 장비 도트</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.soil_deep</t>
+          <t xml:space="preserve">item.ring_rust</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item/tooth_gate.png</t>
+          <t xml:space="preserve">item/rope_hemp.png</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129×174</t>
+          <t xml:space="preserve">117×147</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문지기의 이빨 장비 도트</t>
+          <t xml:space="preserve">삼줄 장비 도트</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.tooth_gate</t>
+          <t xml:space="preserve">item.rope_hemp</t>
         </is>
       </c>
     </row>
@@ -2656,17 +2656,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/click.mp3</t>
+          <t xml:space="preserve">item/soil_deep.png</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">102×150</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 누름</t>
+          <t xml:space="preserve">아래의 흙 한 줌 유품 도트</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.click</t>
+          <t xml:space="preserve">item.soil_deep</t>
         </is>
       </c>
     </row>
@@ -2696,17 +2696,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">기타</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/death.mp3</t>
+          <t xml:space="preserve">item/tooth_gate.png</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">129×174</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
+          <t xml:space="preserve">문지기의 이빨 장비 도트</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.death</t>
+          <t xml:space="preserve">item.tooth_gate</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/record.mp3</t>
+          <t xml:space="preserve">sfx/click.mp3</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신기록 갱신</t>
+          <t xml:space="preserve">버튼 누름</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.record</t>
+          <t xml:space="preserve">sfx.click</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive_knock.mp3</t>
+          <t xml:space="preserve">sfx/death.mp3</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
+          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive.knock</t>
+          <t xml:space="preserve">sfx.death</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive.mp3</t>
+          <t xml:space="preserve">sfx/record.mp3</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
+          <t xml:space="preserve">신기록 갱신</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive</t>
+          <t xml:space="preserve">sfx.record</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/stamp.mp3</t>
+          <t xml:space="preserve">sfx/revive_knock.mp3</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
+          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.stamp</t>
+          <t xml:space="preserve">sfx.revive.knock</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/superchat.mp3</t>
+          <t xml:space="preserve">sfx/revive.mp3</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">슈퍼챗 알림</t>
+          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.superchat</t>
+          <t xml:space="preserve">sfx.revive</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text.mp3</t>
+          <t xml:space="preserve">sfx/stamp.mp3</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
+          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text</t>
+          <t xml:space="preserve">sfx.stamp</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_chime.mp3</t>
+          <t xml:space="preserve">sfx/superchat.mp3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
+          <t xml:space="preserve">슈퍼챗 알림</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.chime</t>
+          <t xml:space="preserve">sfx.superchat</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_door.mp3</t>
+          <t xml:space="preserve">sfx/text_female.wav</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
+          <t xml:space="preserve">대사 타자음 · 여성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.door</t>
+          <t xml:space="preserve">sfx.text.female</t>
         </is>
       </c>
     </row>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/lamp.png</t>
+          <t xml:space="preserve">sfx/text_male.wav</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224×352</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+          <t xml:space="preserve">대사 타자음 · 남성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.lamp</t>
+          <t xml:space="preserve">sfx.text.male</t>
         </is>
       </c>
     </row>
@@ -3096,17 +3096,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/ledger.png</t>
+          <t xml:space="preserve">sfx/text.mp3</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336×264</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 출연자 서류철</t>
+          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.ledger</t>
+          <t xml:space="preserve">sfx.text</t>
         </is>
       </c>
     </row>
@@ -3136,17 +3136,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/scroll.png</t>
+          <t xml:space="preserve">sfx/title_chime.mp3</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176×64</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 서류 조각</t>
+          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.scroll</t>
+          <t xml:space="preserve">sfx.title.chime</t>
         </is>
       </c>
     </row>
@@ -3176,17 +3176,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/stamp.png</t>
+          <t xml:space="preserve">sfx/title_door.mp3</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128×208</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.stamp</t>
+          <t xml:space="preserve">sfx.title.door</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tag.png</t>
+          <t xml:space="preserve">prop/lamp.png</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152×104</t>
+          <t xml:space="preserve">224×352</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 가격표</t>
+          <t xml:space="preserve">작업대의 실제 석유 램프</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tag</t>
+          <t xml:space="preserve">prop.lamp</t>
         </is>
       </c>
     </row>
@@ -3256,17 +3256,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
+          <t xml:space="preserve">prop/ledger.png</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">336×264</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
+          <t xml:space="preserve">작업대의 출연자 서류철</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.angry</t>
+          <t xml:space="preserve">prop.ledger</t>
         </is>
       </c>
     </row>
@@ -3296,17 +3296,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
+          <t xml:space="preserve">prop/scroll.png</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">176×64</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
+          <t xml:space="preserve">계약서 서류 조각</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blank</t>
+          <t xml:space="preserve">prop.scroll</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
+          <t xml:space="preserve">prop/stamp.png</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">128×208</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
+          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blush</t>
+          <t xml:space="preserve">prop.stamp</t>
         </is>
       </c>
     </row>
@@ -3376,17 +3376,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
+          <t xml:space="preserve">prop/tag.png</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">152×104</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
+          <t xml:space="preserve">작업대의 가격표</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.empty</t>
+          <t xml:space="preserve">prop.tag</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
+          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
+          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.neutral</t>
+          <t xml:space="preserve">star.expression.ilan.angry</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.pain</t>
+          <t xml:space="preserve">star.expression.ilan.blank</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.sad</t>
+          <t xml:space="preserve">star.expression.ilan.blush</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
+          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
+          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.smile</t>
+          <t xml:space="preserve">star.expression.ilan.empty</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
+          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
+          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.surprise</t>
+          <t xml:space="preserve">star.expression.ilan.neutral</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_angry.png</t>
+          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno angry 대사 표정 전신</t>
+          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.angry</t>
+          <t xml:space="preserve">star.expression.ilan.pain</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blank.png</t>
+          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blank 대사 표정 전신</t>
+          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blank</t>
+          <t xml:space="preserve">star.expression.ilan.sad</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blush.png</t>
+          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blush 대사 표정 전신</t>
+          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blush</t>
+          <t xml:space="preserve">star.expression.ilan.smile</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_empty.png</t>
+          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno empty 대사 표정 전신</t>
+          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.empty</t>
+          <t xml:space="preserve">star.expression.ilan.surprise</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
+          <t xml:space="preserve">star/expressions/juno_angry.png</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
+          <t xml:space="preserve">juno angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.neutral</t>
+          <t xml:space="preserve">star.expression.juno.angry</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_pain.png</t>
+          <t xml:space="preserve">star/expressions/juno_blank.png</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno pain 대사 표정 전신</t>
+          <t xml:space="preserve">juno blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.pain</t>
+          <t xml:space="preserve">star.expression.juno.blank</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_sad.png</t>
+          <t xml:space="preserve">star/expressions/juno_blush.png</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno sad 대사 표정 전신</t>
+          <t xml:space="preserve">juno blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.sad</t>
+          <t xml:space="preserve">star.expression.juno.blush</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_smile.png</t>
+          <t xml:space="preserve">star/expressions/juno_empty.png</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno smile 대사 표정 전신</t>
+          <t xml:space="preserve">juno empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.smile</t>
+          <t xml:space="preserve">star.expression.juno.empty</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
+          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
+          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.surprise</t>
+          <t xml:space="preserve">star.expression.juno.neutral</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_angry.png</t>
+          <t xml:space="preserve">star/expressions/juno_pain.png</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin angry 대사 표정 전신</t>
+          <t xml:space="preserve">juno pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.angry</t>
+          <t xml:space="preserve">star.expression.juno.pain</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blank.png</t>
+          <t xml:space="preserve">star/expressions/juno_sad.png</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blank 대사 표정 전신</t>
+          <t xml:space="preserve">juno sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blank</t>
+          <t xml:space="preserve">star.expression.juno.sad</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blush.png</t>
+          <t xml:space="preserve">star/expressions/juno_smile.png</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blush 대사 표정 전신</t>
+          <t xml:space="preserve">juno smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blush</t>
+          <t xml:space="preserve">star.expression.juno.smile</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_empty.png</t>
+          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin empty 대사 표정 전신</t>
+          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.empty</t>
+          <t xml:space="preserve">star.expression.juno.surprise</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
+          <t xml:space="preserve">star/expressions/karin_angry.png</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
+          <t xml:space="preserve">karin angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.neutral</t>
+          <t xml:space="preserve">star.expression.karin.angry</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_pain.png</t>
+          <t xml:space="preserve">star/expressions/karin_blank.png</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin pain 대사 표정 전신</t>
+          <t xml:space="preserve">karin blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.pain</t>
+          <t xml:space="preserve">star.expression.karin.blank</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_sad.png</t>
+          <t xml:space="preserve">star/expressions/karin_blush.png</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin sad 대사 표정 전신</t>
+          <t xml:space="preserve">karin blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.sad</t>
+          <t xml:space="preserve">star.expression.karin.blush</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_smile.png</t>
+          <t xml:space="preserve">star/expressions/karin_empty.png</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin smile 대사 표정 전신</t>
+          <t xml:space="preserve">karin empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.smile</t>
+          <t xml:space="preserve">star.expression.karin.empty</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
+          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
+          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.surprise</t>
+          <t xml:space="preserve">star.expression.karin.neutral</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_angry.png</t>
+          <t xml:space="preserve">star/expressions/karin_pain.png</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor angry 대사 표정 전신</t>
+          <t xml:space="preserve">karin pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.angry</t>
+          <t xml:space="preserve">star.expression.karin.pain</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blank.png</t>
+          <t xml:space="preserve">star/expressions/karin_sad.png</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blank 대사 표정 전신</t>
+          <t xml:space="preserve">karin sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blank</t>
+          <t xml:space="preserve">star.expression.karin.sad</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blush.png</t>
+          <t xml:space="preserve">star/expressions/karin_smile.png</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blush 대사 표정 전신</t>
+          <t xml:space="preserve">karin smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blush</t>
+          <t xml:space="preserve">star.expression.karin.smile</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_empty.png</t>
+          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor empty 대사 표정 전신</t>
+          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.empty</t>
+          <t xml:space="preserve">star.expression.karin.surprise</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
+          <t xml:space="preserve">star/expressions/mor_angry.png</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
+          <t xml:space="preserve">mor angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.neutral</t>
+          <t xml:space="preserve">star.expression.mor.angry</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_pain.png</t>
+          <t xml:space="preserve">star/expressions/mor_blank.png</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor pain 대사 표정 전신</t>
+          <t xml:space="preserve">mor blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.pain</t>
+          <t xml:space="preserve">star.expression.mor.blank</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_sad.png</t>
+          <t xml:space="preserve">star/expressions/mor_blush.png</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor sad 대사 표정 전신</t>
+          <t xml:space="preserve">mor blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.sad</t>
+          <t xml:space="preserve">star.expression.mor.blush</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_smile.png</t>
+          <t xml:space="preserve">star/expressions/mor_empty.png</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor smile 대사 표정 전신</t>
+          <t xml:space="preserve">mor empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.smile</t>
+          <t xml:space="preserve">star.expression.mor.empty</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
+          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
+          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.surprise</t>
+          <t xml:space="preserve">star.expression.mor.neutral</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_angry.png</t>
+          <t xml:space="preserve">star/expressions/mor_pain.png</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela angry 대사 표정 전신</t>
+          <t xml:space="preserve">mor pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.angry</t>
+          <t xml:space="preserve">star.expression.mor.pain</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blank.png</t>
+          <t xml:space="preserve">star/expressions/mor_sad.png</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blank 대사 표정 전신</t>
+          <t xml:space="preserve">mor sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blank</t>
+          <t xml:space="preserve">star.expression.mor.sad</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blush.png</t>
+          <t xml:space="preserve">star/expressions/mor_smile.png</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blush 대사 표정 전신</t>
+          <t xml:space="preserve">mor smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blush</t>
+          <t xml:space="preserve">star.expression.mor.smile</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_empty.png</t>
+          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela empty 대사 표정 전신</t>
+          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.empty</t>
+          <t xml:space="preserve">star.expression.mor.surprise</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
+          <t xml:space="preserve">star/expressions/sela_angry.png</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
+          <t xml:space="preserve">sela angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.neutral</t>
+          <t xml:space="preserve">star.expression.sela.angry</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_pain.png</t>
+          <t xml:space="preserve">star/expressions/sela_blank.png</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela pain 대사 표정 전신</t>
+          <t xml:space="preserve">sela blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.pain</t>
+          <t xml:space="preserve">star.expression.sela.blank</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_sad.png</t>
+          <t xml:space="preserve">star/expressions/sela_blush.png</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela sad 대사 표정 전신</t>
+          <t xml:space="preserve">sela blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.sad</t>
+          <t xml:space="preserve">star.expression.sela.blush</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_smile.png</t>
+          <t xml:space="preserve">star/expressions/sela_empty.png</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela smile 대사 표정 전신</t>
+          <t xml:space="preserve">sela empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.smile</t>
+          <t xml:space="preserve">star.expression.sela.empty</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
+          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
+          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.surprise</t>
+          <t xml:space="preserve">star.expression.sela.neutral</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_pain.png</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 대사 전신</t>
+          <t xml:space="preserve">sela pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.ilan</t>
+          <t xml:space="preserve">star.expression.sela.pain</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_sad.png</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 표정 전신</t>
+          <t xml:space="preserve">sela sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan</t>
+          <t xml:space="preserve">star.expression.sela.sad</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_smile.png</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 대사 전신</t>
+          <t xml:space="preserve">sela smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.juno</t>
+          <t xml:space="preserve">star.expression.sela.smile</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
+          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno</t>
+          <t xml:space="preserve">star.expression.sela.surprise</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_dialogue.png</t>
+          <t xml:space="preserve">star/ilan_dialogue.png</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 대사 전신</t>
+          <t xml:space="preserve">일란 대사 전신</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.karin</t>
+          <t xml:space="preserve">star.dialogue.ilan</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_expression.png</t>
+          <t xml:space="preserve">star/ilan_expression.png</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 표정 전신</t>
+          <t xml:space="preserve">일란 표정 전신</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin</t>
+          <t xml:space="preserve">star.expression.ilan</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_dialogue.png</t>
+          <t xml:space="preserve">star/juno_dialogue.png</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 대사 전신</t>
+          <t xml:space="preserve">주노 대사 전신</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.mor</t>
+          <t xml:space="preserve">star.dialogue.juno</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_expression.png</t>
+          <t xml:space="preserve">star/juno_expression.png</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 표정 전신</t>
+          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor</t>
+          <t xml:space="preserve">star.expression.juno</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_dialogue.png</t>
+          <t xml:space="preserve">star/karin_dialogue.png</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 대사 전신</t>
+          <t xml:space="preserve">카린 대사 전신</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.sela</t>
+          <t xml:space="preserve">star.dialogue.karin</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_expression.png</t>
+          <t xml:space="preserve">star/karin_expression.png</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 표정 전신</t>
+          <t xml:space="preserve">카린 표정 전신</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -5446,47 +5446,47 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela</t>
+          <t xml:space="preserve">star.expression.karin</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="0">
-        <v>4</v>
-      </c>
-      <c r="B135" s="0" t="inlineStr">
+      <c r="A135" s="2">
+        <v>4</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
-      <c r="C135" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star/silhouette.png</t>
-        </is>
-      </c>
-      <c r="D135" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1536×480</t>
-        </is>
-      </c>
-      <c r="E135" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F135" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
-        </is>
-      </c>
-      <c r="G135" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H135" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star.silhouette</t>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/mor_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모르 대사 전신</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.dialogue.mor</t>
         </is>
       </c>
     </row>
@@ -5496,17 +5496,17 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/character_cover.png</t>
+          <t xml:space="preserve">star/mor_expression.png</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1087×258</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
+          <t xml:space="preserve">모르 표정 전신</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.guest.cover</t>
+          <t xml:space="preserve">star.expression.mor</t>
         </is>
       </c>
     </row>
@@ -5536,17 +5536,17 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_hour.png</t>
+          <t xml:space="preserve">star/mouth/ilan.png</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29×42</t>
+          <t xml:space="preserve">50×60</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock hour hand</t>
+          <t xml:space="preserve">ilan 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.hour</t>
+          <t xml:space="preserve">star.mouth.ilan</t>
         </is>
       </c>
     </row>
@@ -5576,17 +5576,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_minute.png</t>
+          <t xml:space="preserve">star/mouth/juno.png</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8×56</t>
+          <t xml:space="preserve">64×55</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock minute hand</t>
+          <t xml:space="preserve">juno 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.minute</t>
+          <t xml:space="preserve">star.mouth.juno</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/contract_sheet.png</t>
+          <t xml:space="preserve">star/mouth/karin.png</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×914</t>
+          <t xml:space="preserve">84×57</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
+          <t xml:space="preserve">karin 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -5646,47 +5646,47 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.contract.sheet</t>
+          <t xml:space="preserve">star.mouth.karin</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="0">
-        <v>4</v>
-      </c>
-      <c r="B140" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C140" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/cursor.png</t>
-        </is>
-      </c>
-      <c r="D140" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E140" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F140" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
-        </is>
-      </c>
-      <c r="G140" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H140" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.cursor</t>
+      <c r="A140" s="2">
+        <v>4</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/mouth/mor.png</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56×40</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mor 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.mouth.mor</t>
         </is>
       </c>
     </row>
@@ -5696,17 +5696,17 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">star/mouth/sela.png</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">40×16</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">sela 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">star.mouth.sela</t>
         </is>
       </c>
     </row>
@@ -5736,17 +5736,17 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
+          <t xml:space="preserve">star/sela_dialogue.png</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×144</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+          <t xml:space="preserve">세라 대사 전신</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+          <t xml:space="preserve">star.dialogue.sela</t>
         </is>
       </c>
     </row>
@@ -5776,17 +5776,17 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">star/sela_expression.png</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">세라 표정 전신</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -5806,47 +5806,47 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">star.expression.sela</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2">
-        <v>4</v>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112×112</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.icon.help</t>
+      <c r="A144" s="0">
+        <v>4</v>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/silhouette.png</t>
+        </is>
+      </c>
+      <c r="D144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536×480</t>
+        </is>
+      </c>
+      <c r="E144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+        </is>
+      </c>
+      <c r="G144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.silhouette</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">ui/character_cover.png</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">1087×258</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">ui.guest.cover</t>
         </is>
       </c>
     </row>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">ui/clock_hour.png</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">29×42</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">HUD game-clock hour hand</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">ui.clock.hour</t>
         </is>
       </c>
     </row>
@@ -5941,12 +5941,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">ui/clock_minute.png</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">8×56</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">HUD game-clock minute hand</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">ui.clock.minute</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">ui/contract_sheet.png</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">700×914</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -6006,47 +6006,47 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">ui.contract.sheet</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2">
-        <v>4</v>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="A149" s="0">
+        <v>4</v>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1452×831</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/cursor.png</t>
+        </is>
+      </c>
+      <c r="D149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32×32</t>
+        </is>
+      </c>
+      <c r="E149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
+        </is>
+      </c>
+      <c r="G149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.cursor</t>
         </is>
       </c>
     </row>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">ui/hud_status.png</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">700×144</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">ui.hud.status</t>
         </is>
       </c>
     </row>
@@ -6101,12 +6101,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
+          <t xml:space="preserve">ui/hud_tools.png</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×302</t>
+          <t xml:space="preserve">740×144</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+          <t xml:space="preserve">ui.hud.tools</t>
         </is>
       </c>
     </row>
@@ -6141,12 +6141,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">ui.icon.help.hover</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">ui/icon_help.png</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">ui.icon.help</t>
         </is>
       </c>
     </row>
@@ -6221,12 +6221,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">ui.icon.options.hover</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6261,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">ui/icon_options.png</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">ui.icon.options</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_selected.png</t>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×240</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">ui.icon.save.hover</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">ui/icon_save.png</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">ui.icon.save</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">ui/inventory_window.png</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">1452×831</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">ui.inventory.window</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">536×94</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
         </is>
       </c>
     </row>
@@ -6461,12 +6461,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">536×302</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
         </is>
       </c>
     </row>
@@ -6501,12 +6501,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">ui/item_info_section.png</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">536×238</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">ui.inventory.info.section</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">536×177</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
         </is>
       </c>
     </row>
@@ -6581,12 +6581,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">ui/item_info_top.png</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">536×318</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">ui.inventory.info.top</t>
         </is>
       </c>
     </row>
@@ -6621,12 +6621,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">ui/item_info_window.png</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">536×1129</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">장비 상세 정보창</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">ui.inventory.info</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">ui/item_selected.png</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">228×240</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">ui.inventory.selected</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">ui/live_badge.png</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">206×74</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">③ LIVE 표시</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">ui.live.badge</t>
         </is>
       </c>
     </row>
@@ -6741,12 +6741,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_superchat.png</t>
+          <t xml:space="preserve">ui/live_blink.png</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383×62</t>
+          <t xml:space="preserve">26×28</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -6766,87 +6766,87 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.superchat</t>
+          <t xml:space="preserve">ui.live.blink</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="0">
-        <v>4</v>
-      </c>
-      <c r="B168" s="0" t="inlineStr">
+      <c r="A168" s="2">
+        <v>4</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C168" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D168" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E168" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F168" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G168" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H168" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_chat.png</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424×298</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.chat</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="0">
-        <v>4</v>
-      </c>
-      <c r="B169" s="0" t="inlineStr">
+      <c r="A169" s="2">
+        <v>4</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C169" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D169" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E169" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F169" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G169" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H169" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1040×200</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.dialogue</t>
         </is>
       </c>
     </row>
@@ -6861,22 +6861,22 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/shelf_arrow.png</t>
+          <t xml:space="preserve">ui/live_door.png</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154×161</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.shelf.arrow</t>
+          <t xml:space="preserve">ui.live.door</t>
         </is>
       </c>
     </row>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/live_floors.png</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.live.floors</t>
         </is>
       </c>
     </row>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/live_lantern.png</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">460×568</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.live.lantern</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/live_map.png</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">620×786</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.live.map</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/live_noise.png</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.live.noise</t>
         </is>
       </c>
     </row>
@@ -7061,12 +7061,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion5.png</t>
+          <t xml:space="preserve">ui/live_radio.png</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">220×420</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 무전기</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -7086,47 +7086,47 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion5</t>
+          <t xml:space="preserve">ui.live.radio</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="0">
-        <v>4</v>
-      </c>
-      <c r="B176" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 패널</t>
-        </is>
-      </c>
-      <c r="C176" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/panel_sunken.png</t>
-        </is>
-      </c>
-      <c r="D176" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48×48</t>
-        </is>
-      </c>
-      <c r="E176" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F176" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
-        </is>
-      </c>
-      <c r="G176" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H176" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.panel.sunken.9s</t>
+      <c r="A176" s="2">
+        <v>4</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_superchat.png</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383×62</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.superchat</t>
         </is>
       </c>
     </row>
@@ -7136,41 +7136,401 @@
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0">
+        <v>4</v>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2">
+        <v>4</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154×161</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.shelf.arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2">
+        <v>4</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2">
+        <v>4</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2">
+        <v>4</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2">
+        <v>4</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2">
+        <v>4</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion5.png</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion5</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0">
+        <v>4</v>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C177" s="0" t="inlineStr">
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/panel_sunken.png</t>
+        </is>
+      </c>
+      <c r="D185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48×48</t>
+        </is>
+      </c>
+      <c r="E185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
+        </is>
+      </c>
+      <c r="F185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
+        </is>
+      </c>
+      <c r="G185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.panel.sunken.9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0">
+        <v>4</v>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 패널</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D177" s="0" t="inlineStr">
+      <c r="D186" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E177" s="0" t="inlineStr">
+      <c r="E186" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F177" s="0" t="inlineStr">
+      <c r="F186" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G177" s="0" t="inlineStr">
+      <c r="G186" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H177" s="0" t="inlineStr">
+      <c r="H186" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H177"/>
+  <autoFilter ref="A1:H186"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 화면 저음량 백색소음</t>
+          <t xml:space="preserve">타이틀 화면 저음량 백색소음 (사운드V4 원본)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/click.mp3</t>
+          <t xml:space="preserve">sfx/attack.mp3</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 누름</t>
+          <t xml:space="preserve">전투 — 용사가 때린다 (사운드V4 · 공격_확)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.click</t>
+          <t xml:space="preserve">sfx.combat.attack</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/death.mp3</t>
+          <t xml:space="preserve">sfx/click.mp3</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
+          <t xml:space="preserve">버튼 누름</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.death</t>
+          <t xml:space="preserve">sfx.click</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/record.mp3</t>
+          <t xml:space="preserve">sfx/death.mp3</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신기록 갱신</t>
+          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.record</t>
+          <t xml:space="preserve">sfx.death</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive_knock.mp3</t>
+          <t xml:space="preserve">sfx/fork.mp3</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
+          <t xml:space="preserve">무전 — 갈림길에서 문을 열었다 (사운드V4)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive.knock</t>
+          <t xml:space="preserve">sfx.radio.fork</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive.mp3</t>
+          <t xml:space="preserve">sfx/guard.mp3</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
+          <t xml:space="preserve">전투 — 막았다 (사운드V4)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive</t>
+          <t xml:space="preserve">sfx.combat.guard</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/stamp.mp3</t>
+          <t xml:space="preserve">sfx/hit.mp3</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
+          <t xml:space="preserve">전투 — 적의 반격이 들어왔다 (사운드V4 · 공격_혹)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.stamp</t>
+          <t xml:space="preserve">sfx.combat.hit</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/superchat.mp3</t>
+          <t xml:space="preserve">sfx/item_drop.mp3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">슈퍼챗 알림</t>
+          <t xml:space="preserve">장비를 진열대에 놓는다 (사운드V4 · 물건드랍_중간 철)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.superchat</t>
+          <t xml:space="preserve">sfx.item.drop</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text_female.wav</t>
+          <t xml:space="preserve">sfx/item_pick.mp3</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대사 타자음 · 여성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
+          <t xml:space="preserve">장비를 집어 든다 (사운드V4 · 버튼 뽑)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text.female</t>
+          <t xml:space="preserve">sfx.item.pick</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text_male.wav</t>
+          <t xml:space="preserve">sfx/potion.mp3</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대사 타자음 · 남성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
+          <t xml:space="preserve">전투 — 물약을 마신다 (사운드V4 · 포션먹음이)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text.male</t>
+          <t xml:space="preserve">sfx.potion</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text.mp3</t>
+          <t xml:space="preserve">sfx/record.mp3</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
+          <t xml:space="preserve">신기록 갱신</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text</t>
+          <t xml:space="preserve">sfx.record</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_chime.mp3</t>
+          <t xml:space="preserve">sfx/revive_knock.mp3</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
+          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.chime</t>
+          <t xml:space="preserve">sfx.revive.knock</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_door.mp3</t>
+          <t xml:space="preserve">sfx/revive.mp3</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
+          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.door</t>
+          <t xml:space="preserve">sfx.revive</t>
         </is>
       </c>
     </row>
@@ -3216,17 +3216,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/lamp.png</t>
+          <t xml:space="preserve">sfx/signal_back.mp3</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224×352</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+          <t xml:space="preserve">방송 개시 — 끊겼던 신호가 돌아온다 (사운드V4 · 방송사고_끝)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.lamp</t>
+          <t xml:space="preserve">sfx.signal.back</t>
         </is>
       </c>
     </row>
@@ -3256,17 +3256,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/ledger.png</t>
+          <t xml:space="preserve">sfx/stamp.mp3</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336×264</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 출연자 서류철</t>
+          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.ledger</t>
+          <t xml:space="preserve">sfx.stamp</t>
         </is>
       </c>
     </row>
@@ -3296,17 +3296,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/scroll.png</t>
+          <t xml:space="preserve">sfx/superchat.mp3</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176×64</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 서류 조각</t>
+          <t xml:space="preserve">슈퍼챗 알림 (사운드V4 · 전용 효과음)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.scroll</t>
+          <t xml:space="preserve">sfx.superchat</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/stamp.png</t>
+          <t xml:space="preserve">sfx/text_female.wav</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128×208</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+          <t xml:space="preserve">대사 타자음 · 여성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.stamp</t>
+          <t xml:space="preserve">sfx.text.female</t>
         </is>
       </c>
     </row>
@@ -3376,17 +3376,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tag.png</t>
+          <t xml:space="preserve">sfx/text_male.wav</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152×104</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 가격표</t>
+          <t xml:space="preserve">대사 타자음 · 남성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tag</t>
+          <t xml:space="preserve">sfx.text.male</t>
         </is>
       </c>
     </row>
@@ -3416,17 +3416,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
+          <t xml:space="preserve">sfx/text.mp3</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
+          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.angry</t>
+          <t xml:space="preserve">sfx.text</t>
         </is>
       </c>
     </row>
@@ -3456,17 +3456,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
+          <t xml:space="preserve">sfx/title_chime.mp3</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
+          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blank</t>
+          <t xml:space="preserve">sfx.title.chime</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
+          <t xml:space="preserve">sfx/title_door.mp3</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
+          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blush</t>
+          <t xml:space="preserve">sfx.title.door</t>
         </is>
       </c>
     </row>
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
+          <t xml:space="preserve">prop/lamp.png</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">224×352</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
+          <t xml:space="preserve">작업대의 실제 석유 램프</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.empty</t>
+          <t xml:space="preserve">prop.lamp</t>
         </is>
       </c>
     </row>
@@ -3576,17 +3576,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
+          <t xml:space="preserve">prop/ledger.png</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">336×264</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
+          <t xml:space="preserve">작업대의 출연자 서류철</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.neutral</t>
+          <t xml:space="preserve">prop.ledger</t>
         </is>
       </c>
     </row>
@@ -3616,17 +3616,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
+          <t xml:space="preserve">prop/scroll.png</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">176×64</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
+          <t xml:space="preserve">계약서 서류 조각</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.pain</t>
+          <t xml:space="preserve">prop.scroll</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
+          <t xml:space="preserve">prop/stamp.png</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">128×208</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
+          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.sad</t>
+          <t xml:space="preserve">prop.stamp</t>
         </is>
       </c>
     </row>
@@ -3696,17 +3696,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
+          <t xml:space="preserve">prop/tag.png</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">152×104</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
+          <t xml:space="preserve">작업대의 가격표</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.smile</t>
+          <t xml:space="preserve">prop.tag</t>
         </is>
       </c>
     </row>
@@ -3736,17 +3736,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
+          <t xml:space="preserve">prop/tv_live_hover.png</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">228×216</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
+          <t xml:space="preserve">방송 시작 TV의 마우스 오버 상태</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.surprise</t>
+          <t xml:space="preserve">prop.tv.live.hover</t>
         </is>
       </c>
     </row>
@@ -3776,17 +3776,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_angry.png</t>
+          <t xml:space="preserve">prop/tv_live.png</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">219×202</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno angry 대사 표정 전신</t>
+          <t xml:space="preserve">계약 확정 뒤 방송을 시작할 수 있는 TV</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.angry</t>
+          <t xml:space="preserve">prop.tv.live</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blank.png</t>
+          <t xml:space="preserve">prop/tv.png</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">219×202</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blank 대사 표정 전신</t>
+          <t xml:space="preserve">편성실 용사 배경의 왼쪽 상자 위 브라운관 TV</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blank</t>
+          <t xml:space="preserve">prop.tv</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blush.png</t>
+          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blush 대사 표정 전신</t>
+          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blush</t>
+          <t xml:space="preserve">star.expression.ilan.angry</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_empty.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno empty 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.empty</t>
+          <t xml:space="preserve">star.expression.ilan.blank</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.neutral</t>
+          <t xml:space="preserve">star.expression.ilan.blush</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_pain.png</t>
+          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno pain 대사 표정 전신</t>
+          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.pain</t>
+          <t xml:space="preserve">star.expression.ilan.empty</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_sad.png</t>
+          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno sad 대사 표정 전신</t>
+          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.sad</t>
+          <t xml:space="preserve">star.expression.ilan.neutral</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_smile.png</t>
+          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno smile 대사 표정 전신</t>
+          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.smile</t>
+          <t xml:space="preserve">star.expression.ilan.pain</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
+          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
+          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.surprise</t>
+          <t xml:space="preserve">star.expression.ilan.sad</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_angry.png</t>
+          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin angry 대사 표정 전신</t>
+          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.angry</t>
+          <t xml:space="preserve">star.expression.ilan.smile</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blank.png</t>
+          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blank 대사 표정 전신</t>
+          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blank</t>
+          <t xml:space="preserve">star.expression.ilan.surprise</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blush.png</t>
+          <t xml:space="preserve">star/expressions/juno_angry.png</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blush 대사 표정 전신</t>
+          <t xml:space="preserve">juno angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blush</t>
+          <t xml:space="preserve">star.expression.juno.angry</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_empty.png</t>
+          <t xml:space="preserve">star/expressions/juno_blank.png</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin empty 대사 표정 전신</t>
+          <t xml:space="preserve">juno blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.empty</t>
+          <t xml:space="preserve">star.expression.juno.blank</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
+          <t xml:space="preserve">star/expressions/juno_blush.png</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
+          <t xml:space="preserve">juno blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.neutral</t>
+          <t xml:space="preserve">star.expression.juno.blush</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_pain.png</t>
+          <t xml:space="preserve">star/expressions/juno_empty.png</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin pain 대사 표정 전신</t>
+          <t xml:space="preserve">juno empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.pain</t>
+          <t xml:space="preserve">star.expression.juno.empty</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_sad.png</t>
+          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin sad 대사 표정 전신</t>
+          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.sad</t>
+          <t xml:space="preserve">star.expression.juno.neutral</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_smile.png</t>
+          <t xml:space="preserve">star/expressions/juno_pain.png</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin smile 대사 표정 전신</t>
+          <t xml:space="preserve">juno pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.smile</t>
+          <t xml:space="preserve">star.expression.juno.pain</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
+          <t xml:space="preserve">star/expressions/juno_sad.png</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
+          <t xml:space="preserve">juno sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.surprise</t>
+          <t xml:space="preserve">star.expression.juno.sad</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_angry.png</t>
+          <t xml:space="preserve">star/expressions/juno_smile.png</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor angry 대사 표정 전신</t>
+          <t xml:space="preserve">juno smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.angry</t>
+          <t xml:space="preserve">star.expression.juno.smile</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blank.png</t>
+          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blank 대사 표정 전신</t>
+          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blank</t>
+          <t xml:space="preserve">star.expression.juno.surprise</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blush.png</t>
+          <t xml:space="preserve">star/expressions/karin_angry.png</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blush 대사 표정 전신</t>
+          <t xml:space="preserve">karin angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blush</t>
+          <t xml:space="preserve">star.expression.karin.angry</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_empty.png</t>
+          <t xml:space="preserve">star/expressions/karin_blank.png</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor empty 대사 표정 전신</t>
+          <t xml:space="preserve">karin blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.empty</t>
+          <t xml:space="preserve">star.expression.karin.blank</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
+          <t xml:space="preserve">star/expressions/karin_blush.png</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
+          <t xml:space="preserve">karin blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.neutral</t>
+          <t xml:space="preserve">star.expression.karin.blush</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_pain.png</t>
+          <t xml:space="preserve">star/expressions/karin_empty.png</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor pain 대사 표정 전신</t>
+          <t xml:space="preserve">karin empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.pain</t>
+          <t xml:space="preserve">star.expression.karin.empty</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_sad.png</t>
+          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor sad 대사 표정 전신</t>
+          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.sad</t>
+          <t xml:space="preserve">star.expression.karin.neutral</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_smile.png</t>
+          <t xml:space="preserve">star/expressions/karin_pain.png</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor smile 대사 표정 전신</t>
+          <t xml:space="preserve">karin pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.smile</t>
+          <t xml:space="preserve">star.expression.karin.pain</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
+          <t xml:space="preserve">star/expressions/karin_sad.png</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
+          <t xml:space="preserve">karin sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.surprise</t>
+          <t xml:space="preserve">star.expression.karin.sad</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_angry.png</t>
+          <t xml:space="preserve">star/expressions/karin_smile.png</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela angry 대사 표정 전신</t>
+          <t xml:space="preserve">karin smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.angry</t>
+          <t xml:space="preserve">star.expression.karin.smile</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blank.png</t>
+          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blank 대사 표정 전신</t>
+          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blank</t>
+          <t xml:space="preserve">star.expression.karin.surprise</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blush.png</t>
+          <t xml:space="preserve">star/expressions/mor_angry.png</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blush 대사 표정 전신</t>
+          <t xml:space="preserve">mor angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blush</t>
+          <t xml:space="preserve">star.expression.mor.angry</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_empty.png</t>
+          <t xml:space="preserve">star/expressions/mor_blank.png</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela empty 대사 표정 전신</t>
+          <t xml:space="preserve">mor blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.empty</t>
+          <t xml:space="preserve">star.expression.mor.blank</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
+          <t xml:space="preserve">star/expressions/mor_blush.png</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
+          <t xml:space="preserve">mor blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.neutral</t>
+          <t xml:space="preserve">star.expression.mor.blush</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_pain.png</t>
+          <t xml:space="preserve">star/expressions/mor_empty.png</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela pain 대사 표정 전신</t>
+          <t xml:space="preserve">mor empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.pain</t>
+          <t xml:space="preserve">star.expression.mor.empty</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_sad.png</t>
+          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela sad 대사 표정 전신</t>
+          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.sad</t>
+          <t xml:space="preserve">star.expression.mor.neutral</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_smile.png</t>
+          <t xml:space="preserve">star/expressions/mor_pain.png</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela smile 대사 표정 전신</t>
+          <t xml:space="preserve">mor pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.smile</t>
+          <t xml:space="preserve">star.expression.mor.pain</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
+          <t xml:space="preserve">star/expressions/mor_sad.png</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
+          <t xml:space="preserve">mor sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.surprise</t>
+          <t xml:space="preserve">star.expression.mor.sad</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/mor_smile.png</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 대사 전신</t>
+          <t xml:space="preserve">mor smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.ilan</t>
+          <t xml:space="preserve">star.expression.mor.smile</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_expression.png</t>
+          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 표정 전신</t>
+          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan</t>
+          <t xml:space="preserve">star.expression.mor.surprise</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_angry.png</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 대사 전신</t>
+          <t xml:space="preserve">sela angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.juno</t>
+          <t xml:space="preserve">star.expression.sela.angry</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_blank.png</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
+          <t xml:space="preserve">sela blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno</t>
+          <t xml:space="preserve">star.expression.sela.blank</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_blush.png</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 대사 전신</t>
+          <t xml:space="preserve">sela blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.karin</t>
+          <t xml:space="preserve">star.expression.sela.blush</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_empty.png</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 표정 전신</t>
+          <t xml:space="preserve">sela empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin</t>
+          <t xml:space="preserve">star.expression.sela.empty</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 대사 전신</t>
+          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.mor</t>
+          <t xml:space="preserve">star.expression.sela.neutral</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_pain.png</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 표정 전신</t>
+          <t xml:space="preserve">sela pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor</t>
+          <t xml:space="preserve">star.expression.sela.pain</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/ilan.png</t>
+          <t xml:space="preserve">star/expressions/sela_sad.png</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50×60</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">sela sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.ilan</t>
+          <t xml:space="preserve">star.expression.sela.sad</t>
         </is>
       </c>
     </row>
@@ -5581,12 +5581,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/juno.png</t>
+          <t xml:space="preserve">star/expressions/sela_smile.png</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64×55</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">sela smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.juno</t>
+          <t xml:space="preserve">star.expression.sela.smile</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/karin.png</t>
+          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84×57</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.karin</t>
+          <t xml:space="preserve">star.expression.sela.surprise</t>
         </is>
       </c>
     </row>
@@ -5661,12 +5661,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/mor.png</t>
+          <t xml:space="preserve">star/ilan_dialogue.png</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56×40</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">일란 대사 전신</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.mor</t>
+          <t xml:space="preserve">star.dialogue.ilan</t>
         </is>
       </c>
     </row>
@@ -5701,12 +5701,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/sela.png</t>
+          <t xml:space="preserve">star/ilan_expression.png</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40×16</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">일란 표정 전신</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.sela</t>
+          <t xml:space="preserve">star.expression.ilan</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_dialogue.png</t>
+          <t xml:space="preserve">star/juno_dialogue.png</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 대사 전신</t>
+          <t xml:space="preserve">주노 대사 전신</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.sela</t>
+          <t xml:space="preserve">star.dialogue.juno</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_expression.png</t>
+          <t xml:space="preserve">star/juno_expression.png</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 표정 전신</t>
+          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -5806,47 +5806,47 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela</t>
+          <t xml:space="preserve">star.expression.juno</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="0">
-        <v>4</v>
-      </c>
-      <c r="B144" s="0" t="inlineStr">
+      <c r="A144" s="2">
+        <v>4</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
-      <c r="C144" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star/silhouette.png</t>
-        </is>
-      </c>
-      <c r="D144" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1536×480</t>
-        </is>
-      </c>
-      <c r="E144" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F144" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
-        </is>
-      </c>
-      <c r="G144" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H144" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star.silhouette</t>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/karin_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카린 대사 전신</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.dialogue.karin</t>
         </is>
       </c>
     </row>
@@ -5856,17 +5856,17 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/character_cover.png</t>
+          <t xml:space="preserve">star/karin_expression.png</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1087×258</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
+          <t xml:space="preserve">카린 표정 전신</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.guest.cover</t>
+          <t xml:space="preserve">star.expression.karin</t>
         </is>
       </c>
     </row>
@@ -5896,17 +5896,17 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_hour.png</t>
+          <t xml:space="preserve">star/mor_dialogue.png</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29×42</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock hour hand</t>
+          <t xml:space="preserve">모르 대사 전신</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.hour</t>
+          <t xml:space="preserve">star.dialogue.mor</t>
         </is>
       </c>
     </row>
@@ -5936,17 +5936,17 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_minute.png</t>
+          <t xml:space="preserve">star/mor_expression.png</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8×56</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock minute hand</t>
+          <t xml:space="preserve">모르 표정 전신</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.minute</t>
+          <t xml:space="preserve">star.expression.mor</t>
         </is>
       </c>
     </row>
@@ -5976,17 +5976,17 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/contract_sheet.png</t>
+          <t xml:space="preserve">star/mouth/ilan.png</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×914</t>
+          <t xml:space="preserve">50×60</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
+          <t xml:space="preserve">ilan 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -6006,47 +6006,47 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.contract.sheet</t>
+          <t xml:space="preserve">star.mouth.ilan</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="0">
-        <v>4</v>
-      </c>
-      <c r="B149" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C149" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/cursor.png</t>
-        </is>
-      </c>
-      <c r="D149" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E149" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F149" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
-        </is>
-      </c>
-      <c r="G149" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H149" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.cursor</t>
+      <c r="A149" s="2">
+        <v>4</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/mouth/juno.png</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64×55</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juno 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.mouth.juno</t>
         </is>
       </c>
     </row>
@@ -6056,17 +6056,17 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">star/mouth/karin.png</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">84×57</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">karin 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">star.mouth.karin</t>
         </is>
       </c>
     </row>
@@ -6096,17 +6096,17 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
+          <t xml:space="preserve">star/mouth/mor.png</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×144</t>
+          <t xml:space="preserve">56×40</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+          <t xml:space="preserve">mor 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+          <t xml:space="preserve">star.mouth.mor</t>
         </is>
       </c>
     </row>
@@ -6136,17 +6136,17 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">star/mouth/sela.png</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">40×16</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">sela 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">star.mouth.sela</t>
         </is>
       </c>
     </row>
@@ -6176,17 +6176,17 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">star/sela_dialogue.png</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">세라 대사 전신</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">star.dialogue.sela</t>
         </is>
       </c>
     </row>
@@ -6216,17 +6216,17 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">star/sela_expression.png</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">세라 표정 전신</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -6246,47 +6246,47 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">star.expression.sela</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2">
-        <v>4</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112×112</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.icon.options</t>
+      <c r="A155" s="0">
+        <v>4</v>
+      </c>
+      <c r="B155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/silhouette.png</t>
+        </is>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536×480</t>
+        </is>
+      </c>
+      <c r="E155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+        </is>
+      </c>
+      <c r="G155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.silhouette</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">ui/character_cover.png</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">1087×258</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">ui.guest.cover</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">ui/clock_hour.png</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">29×42</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">HUD game-clock hour hand</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">ui.clock.hour</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
+          <t xml:space="preserve">ui/clock_minute.png</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452×831</t>
+          <t xml:space="preserve">8×56</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
+          <t xml:space="preserve">HUD game-clock minute hand</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+          <t xml:space="preserve">ui.clock.minute</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">ui/contract_sheet.png</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">700×914</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -6446,47 +6446,47 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">ui.contract.sheet</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2">
-        <v>4</v>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="A160" s="0">
+        <v>4</v>
+      </c>
+      <c r="B160" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">536×302</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/cursor.png</t>
+        </is>
+      </c>
+      <c r="D160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32×32</t>
+        </is>
+      </c>
+      <c r="E160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
+        </is>
+      </c>
+      <c r="G160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.cursor</t>
         </is>
       </c>
     </row>
@@ -6501,12 +6501,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">ui/hud_status.png</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">700×144</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">ui.hud.status</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">ui/hud_tools.png</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">740×144</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">ui.hud.tools</t>
         </is>
       </c>
     </row>
@@ -6581,12 +6581,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">ui.icon.help.hover</t>
         </is>
       </c>
     </row>
@@ -6621,12 +6621,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">ui/icon_help.png</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">ui.icon.help</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_selected.png</t>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×240</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">ui.icon.options.hover</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">ui/icon_options.png</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">ui.icon.options</t>
         </is>
       </c>
     </row>
@@ -6741,12 +6741,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">ui.icon.save.hover</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">ui/icon_save.png</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">ui.icon.save</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">ui/inventory_window.png</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">1452×831</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">ui.inventory.window</t>
         </is>
       </c>
     </row>
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">536×94</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
         </is>
       </c>
     </row>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">536×302</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
         </is>
       </c>
     </row>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">ui/item_info_section.png</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">536×238</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">ui.inventory.info.section</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">536×177</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">ui/item_info_top.png</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">536×318</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">ui.inventory.info.top</t>
         </is>
       </c>
     </row>
@@ -7061,12 +7061,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">ui/item_info_window.png</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">536×1129</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">장비 상세 정보창</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">ui.inventory.info</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_superchat.png</t>
+          <t xml:space="preserve">ui/item_selected.png</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383×62</t>
+          <t xml:space="preserve">228×240</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -7126,87 +7126,87 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.superchat</t>
+          <t xml:space="preserve">ui.inventory.selected</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="0">
-        <v>4</v>
-      </c>
-      <c r="B177" s="0" t="inlineStr">
+      <c r="A177" s="2">
+        <v>4</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C177" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D177" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E177" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F177" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G177" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H177" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_badge.png</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206×74</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ LIVE 표시</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.badge</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="0">
-        <v>4</v>
-      </c>
-      <c r="B178" s="0" t="inlineStr">
+      <c r="A178" s="2">
+        <v>4</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C178" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D178" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E178" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F178" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G178" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H178" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_blink.png</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26×28</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.blink</t>
         </is>
       </c>
     </row>
@@ -7221,22 +7221,22 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/shelf_arrow.png</t>
+          <t xml:space="preserve">ui/live_chat.png</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154×161</t>
+          <t xml:space="preserve">424×298</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.shelf.arrow</t>
+          <t xml:space="preserve">ui.live.chat</t>
         </is>
       </c>
     </row>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">1040×200</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.live.dialogue</t>
         </is>
       </c>
     </row>
@@ -7301,12 +7301,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/live_door.png</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.live.door</t>
         </is>
       </c>
     </row>
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/live_floors.png</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.live.floors</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/live_lantern.png</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">460×568</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.live.lantern</t>
         </is>
       </c>
     </row>
@@ -7421,116 +7421,556 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/live_map.png</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620×786</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.map</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2">
+        <v>4</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_noise.png</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2">
+        <v>4</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_radio.png</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220×420</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 무전기</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2">
+        <v>4</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_superchat.png</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383×62</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.superchat</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0">
+        <v>4</v>
+      </c>
+      <c r="B188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0">
+        <v>4</v>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2">
+        <v>4</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154×161</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.shelf.arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2">
+        <v>4</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2">
+        <v>4</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2">
+        <v>4</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2">
+        <v>4</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2">
+        <v>4</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/suspicion5.png</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×128</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.suspicion5</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="0">
-        <v>4</v>
-      </c>
-      <c r="B185" s="0" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="0">
+        <v>4</v>
+      </c>
+      <c r="B196" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C185" s="0" t="inlineStr">
+      <c r="C196" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D185" s="0" t="inlineStr">
+      <c r="D196" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E185" s="0" t="inlineStr">
+      <c r="E196" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F185" s="0" t="inlineStr">
+      <c r="F196" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G185" s="0" t="inlineStr">
+      <c r="G196" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H185" s="0" t="inlineStr">
+      <c r="H196" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="0">
-        <v>4</v>
-      </c>
-      <c r="B186" s="0" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="0">
+        <v>4</v>
+      </c>
+      <c r="B197" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C186" s="0" t="inlineStr">
+      <c r="C197" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D186" s="0" t="inlineStr">
+      <c r="D197" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E186" s="0" t="inlineStr">
+      <c r="E197" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F186" s="0" t="inlineStr">
+      <c r="F197" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G186" s="0" t="inlineStr">
+      <c r="G197" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H186" s="0" t="inlineStr">
+      <c r="H197" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H186"/>
+  <autoFilter ref="A1:H197"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/death.mp3</t>
+          <t xml:space="preserve">sfx/contract_stamp.mp3</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
+          <t xml:space="preserve">계약서 확정 도장을 찍는 쾅 소리</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.death</t>
+          <t xml:space="preserve">sfx.contract.stamp</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/fork.mp3</t>
+          <t xml:space="preserve">sfx/death.mp3</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">무전 — 갈림길에서 문을 열었다 (사운드V4)</t>
+          <t xml:space="preserve">신호 두절 — 방송 끊김음 + 저역 험 (M06 §8 「소리가 절반이다」)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.radio.fork</t>
+          <t xml:space="preserve">sfx.death</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/guard.mp3</t>
+          <t xml:space="preserve">sfx/fork.mp3</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 — 막았다 (사운드V4)</t>
+          <t xml:space="preserve">무전 — 갈림길에서 문을 열었다 (사운드V4)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.combat.guard</t>
+          <t xml:space="preserve">sfx.radio.fork</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/hit.mp3</t>
+          <t xml:space="preserve">sfx/guard.mp3</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 — 적의 반격이 들어왔다 (사운드V4 · 공격_혹)</t>
+          <t xml:space="preserve">전투 — 막았다 (사운드V4)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.combat.hit</t>
+          <t xml:space="preserve">sfx.combat.guard</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/item_drop.mp3</t>
+          <t xml:space="preserve">sfx/hit.mp3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비를 진열대에 놓는다 (사운드V4 · 물건드랍_중간 철)</t>
+          <t xml:space="preserve">전투 — 적의 반격이 들어왔다 (사운드V4 · 공격_혹)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.item.drop</t>
+          <t xml:space="preserve">sfx.combat.hit</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/item_pick.mp3</t>
+          <t xml:space="preserve">sfx/item_drop.mp3</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비를 집어 든다 (사운드V4 · 버튼 뽑)</t>
+          <t xml:space="preserve">장비를 진열대에 놓는다 (사운드V4 · 물건드랍_중간 철)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.item.pick</t>
+          <t xml:space="preserve">sfx.item.drop</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/potion.mp3</t>
+          <t xml:space="preserve">sfx/item_pick.mp3</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 — 물약을 마신다 (사운드V4 · 포션먹음이)</t>
+          <t xml:space="preserve">장비를 집어 든다 (사운드V4 · 버튼 뽑)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.potion</t>
+          <t xml:space="preserve">sfx.item.pick</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/record.mp3</t>
+          <t xml:space="preserve">sfx/potion.mp3</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신기록 갱신</t>
+          <t xml:space="preserve">전투 — 물약을 마신다 (사운드V4 · 포션먹음이)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.record</t>
+          <t xml:space="preserve">sfx.potion</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive_knock.mp3</t>
+          <t xml:space="preserve">sfx/record.mp3</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
+          <t xml:space="preserve">신기록 갱신</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive.knock</t>
+          <t xml:space="preserve">sfx.record</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive.mp3</t>
+          <t xml:space="preserve">sfx/revive_knock.mp3</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
+          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive</t>
+          <t xml:space="preserve">sfx.revive.knock</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/signal_back.mp3</t>
+          <t xml:space="preserve">sfx/revive.mp3</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">방송 개시 — 끊겼던 신호가 돌아온다 (사운드V4 · 방송사고_끝)</t>
+          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.signal.back</t>
+          <t xml:space="preserve">sfx.revive</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/stamp.mp3</t>
+          <t xml:space="preserve">sfx/signal_back.mp3</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
+          <t xml:space="preserve">방송 개시 — 끊겼던 신호가 돌아온다 (사운드V4 · 방송사고_끝)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.stamp</t>
+          <t xml:space="preserve">sfx.signal.back</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/superchat.mp3</t>
+          <t xml:space="preserve">sfx/stamp.mp3</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">슈퍼챗 알림 (사운드V4 · 전용 효과음)</t>
+          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.superchat</t>
+          <t xml:space="preserve">sfx.stamp</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text_female.wav</t>
+          <t xml:space="preserve">sfx/superchat.mp3</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대사 타자음 · 여성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
+          <t xml:space="preserve">슈퍼챗 알림 (사운드V4 · 전용 효과음)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text.female</t>
+          <t xml:space="preserve">sfx.superchat</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text_male.wav</t>
+          <t xml:space="preserve">sfx/text_female.wav</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대사 타자음 · 남성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
+          <t xml:space="preserve">대사 타자음 · 여성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text.male</t>
+          <t xml:space="preserve">sfx.text.female</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text.mp3</t>
+          <t xml:space="preserve">sfx/text_male.wav</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
+          <t xml:space="preserve">대사 타자음 · 남성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text</t>
+          <t xml:space="preserve">sfx.text.male</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_chime.mp3</t>
+          <t xml:space="preserve">sfx/text.mp3</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
+          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.chime</t>
+          <t xml:space="preserve">sfx.text</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_door.mp3</t>
+          <t xml:space="preserve">sfx/title_chime.mp3</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
+          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.door</t>
+          <t xml:space="preserve">sfx.title.chime</t>
         </is>
       </c>
     </row>
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/lamp.png</t>
+          <t xml:space="preserve">sfx/title_door.mp3</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224×352</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.lamp</t>
+          <t xml:space="preserve">sfx.title.door</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/ledger.png</t>
+          <t xml:space="preserve">prop/contract_stamp.png</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336×264</t>
+          <t xml:space="preserve">179×178</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 출연자 서류철</t>
+          <t xml:space="preserve">계약서 우측 하단에 찍는 확정 도장</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.ledger</t>
+          <t xml:space="preserve">prop.contract.stamp</t>
         </is>
       </c>
     </row>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/scroll.png</t>
+          <t xml:space="preserve">prop/lamp.png</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176×64</t>
+          <t xml:space="preserve">224×352</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 서류 조각</t>
+          <t xml:space="preserve">작업대의 실제 석유 램프</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.scroll</t>
+          <t xml:space="preserve">prop.lamp</t>
         </is>
       </c>
     </row>
@@ -3661,12 +3661,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/stamp.png</t>
+          <t xml:space="preserve">prop/ledger.png</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128×208</t>
+          <t xml:space="preserve">336×264</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+          <t xml:space="preserve">작업대의 출연자 서류철</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.stamp</t>
+          <t xml:space="preserve">prop.ledger</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tag.png</t>
+          <t xml:space="preserve">prop/scroll.png</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152×104</t>
+          <t xml:space="preserve">176×64</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 가격표</t>
+          <t xml:space="preserve">계약서 서류 조각</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tag</t>
+          <t xml:space="preserve">prop.scroll</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tv_live_hover.png</t>
+          <t xml:space="preserve">prop/stamp.png</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×216</t>
+          <t xml:space="preserve">128×208</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">방송 시작 TV의 마우스 오버 상태</t>
+          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tv.live.hover</t>
+          <t xml:space="preserve">prop.stamp</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tv_live.png</t>
+          <t xml:space="preserve">prop/tag.png</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219×202</t>
+          <t xml:space="preserve">152×104</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약 확정 뒤 방송을 시작할 수 있는 TV</t>
+          <t xml:space="preserve">작업대의 가격표</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tv.live</t>
+          <t xml:space="preserve">prop.tag</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tv.png</t>
+          <t xml:space="preserve">prop/tv_live_hover.png</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219×202</t>
+          <t xml:space="preserve">228×216</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 용사 배경의 왼쪽 상자 위 브라운관 TV</t>
+          <t xml:space="preserve">방송 시작 TV의 마우스 오버 상태</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tv</t>
+          <t xml:space="preserve">prop.tv.live.hover</t>
         </is>
       </c>
     </row>
@@ -3856,17 +3856,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
+          <t xml:space="preserve">prop/tv_live.png</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">219×202</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
+          <t xml:space="preserve">계약 확정 뒤 방송을 시작할 수 있는 TV</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.angry</t>
+          <t xml:space="preserve">prop.tv.live</t>
         </is>
       </c>
     </row>
@@ -3896,17 +3896,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
+          <t xml:space="preserve">prop/tv.png</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">219×202</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
+          <t xml:space="preserve">편성실 용사 배경의 왼쪽 상자 위 브라운관 TV</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blank</t>
+          <t xml:space="preserve">prop.tv</t>
         </is>
       </c>
     </row>
@@ -3941,22 +3941,22 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
+          <t xml:space="preserve">star/corpse_ilan.png</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
+          <t xml:space="preserve">미레(마법사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blush</t>
+          <t xml:space="preserve">star.corpse.ilan</t>
         </is>
       </c>
     </row>
@@ -3981,22 +3981,22 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
+          <t xml:space="preserve">star/corpse_juno.png</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
+          <t xml:space="preserve">펜로(궁수) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.empty</t>
+          <t xml:space="preserve">star.corpse.juno</t>
         </is>
       </c>
     </row>
@@ -4021,22 +4021,22 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
+          <t xml:space="preserve">star/corpse_karin.png</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
+          <t xml:space="preserve">노일(검사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.neutral</t>
+          <t xml:space="preserve">star.corpse.karin</t>
         </is>
       </c>
     </row>
@@ -4061,22 +4061,22 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
+          <t xml:space="preserve">star/corpse_mor.png</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1779×1215</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
+          <t xml:space="preserve">헤일(힐러) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.pain</t>
+          <t xml:space="preserve">star.corpse.mor</t>
         </is>
       </c>
     </row>
@@ -4101,22 +4101,22 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
+          <t xml:space="preserve">star/corpse_sela.png</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
+          <t xml:space="preserve">녹스(도적) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.sad</t>
+          <t xml:space="preserve">star.corpse.sela</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
+          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
+          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.smile</t>
+          <t xml:space="preserve">star.expression.ilan.angry</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.surprise</t>
+          <t xml:space="preserve">star.expression.ilan.blank</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_angry.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno angry 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.angry</t>
+          <t xml:space="preserve">star.expression.ilan.blush</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blank.png</t>
+          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blank 대사 표정 전신</t>
+          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blank</t>
+          <t xml:space="preserve">star.expression.ilan.empty</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blush.png</t>
+          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blush 대사 표정 전신</t>
+          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blush</t>
+          <t xml:space="preserve">star.expression.ilan.neutral</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_empty.png</t>
+          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno empty 대사 표정 전신</t>
+          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.empty</t>
+          <t xml:space="preserve">star.expression.ilan.pain</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
+          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
+          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.neutral</t>
+          <t xml:space="preserve">star.expression.ilan.sad</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_pain.png</t>
+          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno pain 대사 표정 전신</t>
+          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.pain</t>
+          <t xml:space="preserve">star.expression.ilan.smile</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_sad.png</t>
+          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno sad 대사 표정 전신</t>
+          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.sad</t>
+          <t xml:space="preserve">star.expression.ilan.surprise</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_smile.png</t>
+          <t xml:space="preserve">star/expressions/juno_angry.png</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno smile 대사 표정 전신</t>
+          <t xml:space="preserve">juno angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.smile</t>
+          <t xml:space="preserve">star.expression.juno.angry</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
+          <t xml:space="preserve">star/expressions/juno_blank.png</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
+          <t xml:space="preserve">juno blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.surprise</t>
+          <t xml:space="preserve">star.expression.juno.blank</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_angry.png</t>
+          <t xml:space="preserve">star/expressions/juno_blush.png</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin angry 대사 표정 전신</t>
+          <t xml:space="preserve">juno blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.angry</t>
+          <t xml:space="preserve">star.expression.juno.blush</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blank.png</t>
+          <t xml:space="preserve">star/expressions/juno_empty.png</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blank 대사 표정 전신</t>
+          <t xml:space="preserve">juno empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blank</t>
+          <t xml:space="preserve">star.expression.juno.empty</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blush.png</t>
+          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blush 대사 표정 전신</t>
+          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blush</t>
+          <t xml:space="preserve">star.expression.juno.neutral</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_empty.png</t>
+          <t xml:space="preserve">star/expressions/juno_pain.png</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin empty 대사 표정 전신</t>
+          <t xml:space="preserve">juno pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.empty</t>
+          <t xml:space="preserve">star.expression.juno.pain</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
+          <t xml:space="preserve">star/expressions/juno_sad.png</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
+          <t xml:space="preserve">juno sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.neutral</t>
+          <t xml:space="preserve">star.expression.juno.sad</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_pain.png</t>
+          <t xml:space="preserve">star/expressions/juno_smile.png</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin pain 대사 표정 전신</t>
+          <t xml:space="preserve">juno smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.pain</t>
+          <t xml:space="preserve">star.expression.juno.smile</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_sad.png</t>
+          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin sad 대사 표정 전신</t>
+          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.sad</t>
+          <t xml:space="preserve">star.expression.juno.surprise</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_smile.png</t>
+          <t xml:space="preserve">star/expressions/karin_angry.png</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin smile 대사 표정 전신</t>
+          <t xml:space="preserve">karin angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.smile</t>
+          <t xml:space="preserve">star.expression.karin.angry</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
+          <t xml:space="preserve">star/expressions/karin_blank.png</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
+          <t xml:space="preserve">karin blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.surprise</t>
+          <t xml:space="preserve">star.expression.karin.blank</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_angry.png</t>
+          <t xml:space="preserve">star/expressions/karin_blush.png</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor angry 대사 표정 전신</t>
+          <t xml:space="preserve">karin blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.angry</t>
+          <t xml:space="preserve">star.expression.karin.blush</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blank.png</t>
+          <t xml:space="preserve">star/expressions/karin_empty.png</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blank 대사 표정 전신</t>
+          <t xml:space="preserve">karin empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blank</t>
+          <t xml:space="preserve">star.expression.karin.empty</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blush.png</t>
+          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blush 대사 표정 전신</t>
+          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blush</t>
+          <t xml:space="preserve">star.expression.karin.neutral</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_empty.png</t>
+          <t xml:space="preserve">star/expressions/karin_pain.png</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor empty 대사 표정 전신</t>
+          <t xml:space="preserve">karin pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.empty</t>
+          <t xml:space="preserve">star.expression.karin.pain</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
+          <t xml:space="preserve">star/expressions/karin_sad.png</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
+          <t xml:space="preserve">karin sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.neutral</t>
+          <t xml:space="preserve">star.expression.karin.sad</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_pain.png</t>
+          <t xml:space="preserve">star/expressions/karin_smile.png</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor pain 대사 표정 전신</t>
+          <t xml:space="preserve">karin smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.pain</t>
+          <t xml:space="preserve">star.expression.karin.smile</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_sad.png</t>
+          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor sad 대사 표정 전신</t>
+          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.sad</t>
+          <t xml:space="preserve">star.expression.karin.surprise</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_smile.png</t>
+          <t xml:space="preserve">star/expressions/mor_angry.png</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor smile 대사 표정 전신</t>
+          <t xml:space="preserve">mor angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.smile</t>
+          <t xml:space="preserve">star.expression.mor.angry</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
+          <t xml:space="preserve">star/expressions/mor_blank.png</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
+          <t xml:space="preserve">mor blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.surprise</t>
+          <t xml:space="preserve">star.expression.mor.blank</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_angry.png</t>
+          <t xml:space="preserve">star/expressions/mor_blush.png</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela angry 대사 표정 전신</t>
+          <t xml:space="preserve">mor blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.angry</t>
+          <t xml:space="preserve">star.expression.mor.blush</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blank.png</t>
+          <t xml:space="preserve">star/expressions/mor_empty.png</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blank 대사 표정 전신</t>
+          <t xml:space="preserve">mor empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blank</t>
+          <t xml:space="preserve">star.expression.mor.empty</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blush.png</t>
+          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blush 대사 표정 전신</t>
+          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blush</t>
+          <t xml:space="preserve">star.expression.mor.neutral</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_empty.png</t>
+          <t xml:space="preserve">star/expressions/mor_pain.png</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela empty 대사 표정 전신</t>
+          <t xml:space="preserve">mor pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.empty</t>
+          <t xml:space="preserve">star.expression.mor.pain</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
+          <t xml:space="preserve">star/expressions/mor_sad.png</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
+          <t xml:space="preserve">mor sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.neutral</t>
+          <t xml:space="preserve">star.expression.mor.sad</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_pain.png</t>
+          <t xml:space="preserve">star/expressions/mor_smile.png</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela pain 대사 표정 전신</t>
+          <t xml:space="preserve">mor smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.pain</t>
+          <t xml:space="preserve">star.expression.mor.smile</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_sad.png</t>
+          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela sad 대사 표정 전신</t>
+          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.sad</t>
+          <t xml:space="preserve">star.expression.mor.surprise</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_smile.png</t>
+          <t xml:space="preserve">star/expressions/sela_angry.png</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela smile 대사 표정 전신</t>
+          <t xml:space="preserve">sela angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.smile</t>
+          <t xml:space="preserve">star.expression.sela.angry</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
+          <t xml:space="preserve">star/expressions/sela_blank.png</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
+          <t xml:space="preserve">sela blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.surprise</t>
+          <t xml:space="preserve">star.expression.sela.blank</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_blush.png</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 대사 전신</t>
+          <t xml:space="preserve">sela blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.ilan</t>
+          <t xml:space="preserve">star.expression.sela.blush</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_empty.png</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 표정 전신</t>
+          <t xml:space="preserve">sela empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan</t>
+          <t xml:space="preserve">star.expression.sela.empty</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 대사 전신</t>
+          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.juno</t>
+          <t xml:space="preserve">star.expression.sela.neutral</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_pain.png</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
+          <t xml:space="preserve">sela pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno</t>
+          <t xml:space="preserve">star.expression.sela.pain</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_sad.png</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 대사 전신</t>
+          <t xml:space="preserve">sela sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.karin</t>
+          <t xml:space="preserve">star.expression.sela.sad</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_smile.png</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 표정 전신</t>
+          <t xml:space="preserve">sela smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin</t>
+          <t xml:space="preserve">star.expression.sela.smile</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 대사 전신</t>
+          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.mor</t>
+          <t xml:space="preserve">star.expression.sela.surprise</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_expression.png</t>
+          <t xml:space="preserve">star/ilan_dialogue.png</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 표정 전신</t>
+          <t xml:space="preserve">일란 대사 전신</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor</t>
+          <t xml:space="preserve">star.dialogue.ilan</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/ilan.png</t>
+          <t xml:space="preserve">star/ilan_expression.png</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50×60</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">일란 표정 전신</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.ilan</t>
+          <t xml:space="preserve">star.expression.ilan</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/juno.png</t>
+          <t xml:space="preserve">star/juno_dialogue.png</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64×55</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">주노 대사 전신</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.juno</t>
+          <t xml:space="preserve">star.dialogue.juno</t>
         </is>
       </c>
     </row>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/karin.png</t>
+          <t xml:space="preserve">star/juno_expression.png</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84×57</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.karin</t>
+          <t xml:space="preserve">star.expression.juno</t>
         </is>
       </c>
     </row>
@@ -6101,12 +6101,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/mor.png</t>
+          <t xml:space="preserve">star/karin_dialogue.png</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56×40</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">카린 대사 전신</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.mor</t>
+          <t xml:space="preserve">star.dialogue.karin</t>
         </is>
       </c>
     </row>
@@ -6141,12 +6141,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/sela.png</t>
+          <t xml:space="preserve">star/karin_expression.png</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40×16</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">카린 표정 전신</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.sela</t>
+          <t xml:space="preserve">star.expression.karin</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_dialogue.png</t>
+          <t xml:space="preserve">star/mor_dialogue.png</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 대사 전신</t>
+          <t xml:space="preserve">모르 대사 전신</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.sela</t>
+          <t xml:space="preserve">star.dialogue.mor</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_expression.png</t>
+          <t xml:space="preserve">star/mor_expression.png</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 표정 전신</t>
+          <t xml:space="preserve">모르 표정 전신</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -6246,47 +6246,47 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela</t>
+          <t xml:space="preserve">star.expression.mor</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="0">
-        <v>4</v>
-      </c>
-      <c r="B155" s="0" t="inlineStr">
+      <c r="A155" s="2">
+        <v>4</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
-      <c r="C155" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star/silhouette.png</t>
-        </is>
-      </c>
-      <c r="D155" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1536×480</t>
-        </is>
-      </c>
-      <c r="E155" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F155" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
-        </is>
-      </c>
-      <c r="G155" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H155" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star.silhouette</t>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/mouth/ilan.png</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50×60</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilan 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.mouth.ilan</t>
         </is>
       </c>
     </row>
@@ -6296,17 +6296,17 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/character_cover.png</t>
+          <t xml:space="preserve">star/mouth/juno.png</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1087×258</t>
+          <t xml:space="preserve">64×55</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
+          <t xml:space="preserve">juno 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.guest.cover</t>
+          <t xml:space="preserve">star.mouth.juno</t>
         </is>
       </c>
     </row>
@@ -6336,17 +6336,17 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_hour.png</t>
+          <t xml:space="preserve">star/mouth/karin.png</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29×42</t>
+          <t xml:space="preserve">84×57</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock hour hand</t>
+          <t xml:space="preserve">karin 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.hour</t>
+          <t xml:space="preserve">star.mouth.karin</t>
         </is>
       </c>
     </row>
@@ -6376,17 +6376,17 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_minute.png</t>
+          <t xml:space="preserve">star/mouth/mor.png</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8×56</t>
+          <t xml:space="preserve">56×40</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock minute hand</t>
+          <t xml:space="preserve">mor 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.minute</t>
+          <t xml:space="preserve">star.mouth.mor</t>
         </is>
       </c>
     </row>
@@ -6416,17 +6416,17 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/contract_sheet.png</t>
+          <t xml:space="preserve">star/mouth/sela.png</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×914</t>
+          <t xml:space="preserve">40×16</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
+          <t xml:space="preserve">sela 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -6446,47 +6446,47 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.contract.sheet</t>
+          <t xml:space="preserve">star.mouth.sela</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="0">
-        <v>4</v>
-      </c>
-      <c r="B160" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C160" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/cursor.png</t>
-        </is>
-      </c>
-      <c r="D160" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E160" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F160" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
-        </is>
-      </c>
-      <c r="G160" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H160" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.cursor</t>
+      <c r="A160" s="2">
+        <v>4</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/sela_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세라 대사 전신</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.dialogue.sela</t>
         </is>
       </c>
     </row>
@@ -6496,17 +6496,17 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">star/sela_expression.png</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">세라 표정 전신</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -6526,47 +6526,47 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">star.expression.sela</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2">
-        <v>4</v>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">740×144</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+      <c r="A162" s="0">
+        <v>4</v>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/silhouette.png</t>
+        </is>
+      </c>
+      <c r="D162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536×480</t>
+        </is>
+      </c>
+      <c r="E162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+        </is>
+      </c>
+      <c r="G162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.silhouette</t>
         </is>
       </c>
     </row>
@@ -6581,12 +6581,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">ui/character_cover.png</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">1087×258</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">ui.guest.cover</t>
         </is>
       </c>
     </row>
@@ -6621,12 +6621,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">ui/clock_hour.png</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">29×42</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">HUD game-clock hour hand</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">ui.clock.hour</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">ui/clock_minute.png</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">8×56</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">HUD game-clock minute hand</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">ui.clock.minute</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">ui/contract_sheet.png</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">795×1036</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -6726,47 +6726,47 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">ui.contract.sheet</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2">
-        <v>4</v>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="A167" s="0">
+        <v>4</v>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112×112</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/cursor.png</t>
+        </is>
+      </c>
+      <c r="D167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32×32</t>
+        </is>
+      </c>
+      <c r="E167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
+        </is>
+      </c>
+      <c r="G167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.cursor</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">ui/hud_status.png</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">700×144</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">ui.hud.status</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
+          <t xml:space="preserve">ui/hud_tools.png</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452×831</t>
+          <t xml:space="preserve">740×144</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+          <t xml:space="preserve">ui.hud.tools</t>
         </is>
       </c>
     </row>
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">ui.icon.help.hover</t>
         </is>
       </c>
     </row>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
+          <t xml:space="preserve">ui/icon_help.png</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×302</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+          <t xml:space="preserve">ui.icon.help</t>
         </is>
       </c>
     </row>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">ui.icon.options.hover</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">ui/icon_options.png</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">ui.icon.options</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">ui.icon.save.hover</t>
         </is>
       </c>
     </row>
@@ -7061,12 +7061,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">ui/icon_save.png</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">ui.icon.save</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_selected.png</t>
+          <t xml:space="preserve">ui/inventory_window.png</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×240</t>
+          <t xml:space="preserve">1452×831</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">ui.inventory.window</t>
         </is>
       </c>
     </row>
@@ -7141,12 +7141,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">536×94</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
         </is>
       </c>
     </row>
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">536×302</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
         </is>
       </c>
     </row>
@@ -7221,12 +7221,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">ui/item_info_section.png</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">536×238</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">ui.inventory.info.section</t>
         </is>
       </c>
     </row>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">536×177</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
         </is>
       </c>
     </row>
@@ -7301,12 +7301,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">ui/item_info_top.png</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">536×318</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">ui.inventory.info.top</t>
         </is>
       </c>
     </row>
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">ui/item_info_window.png</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">536×1129</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">장비 상세 정보창</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">ui.inventory.info</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">ui/item_selected.png</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">228×240</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">ui.inventory.selected</t>
         </is>
       </c>
     </row>
@@ -7421,12 +7421,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">ui/live_badge.png</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">206×74</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">③ LIVE 표시</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">ui.live.badge</t>
         </is>
       </c>
     </row>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">ui/live_blink.png</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">26×28</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">ui.live.blink</t>
         </is>
       </c>
     </row>
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">ui/live_chat.png</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">424×298</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">ui.live.chat</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7541,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_superchat.png</t>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383×62</t>
+          <t xml:space="preserve">1040×200</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -7566,87 +7566,87 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.superchat</t>
+          <t xml:space="preserve">ui.live.dialogue</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="0">
-        <v>4</v>
-      </c>
-      <c r="B188" s="0" t="inlineStr">
+      <c r="A188" s="2">
+        <v>4</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C188" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D188" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E188" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F188" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G188" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H188" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_door.png</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.door</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="0">
-        <v>4</v>
-      </c>
-      <c r="B189" s="0" t="inlineStr">
+      <c r="A189" s="2">
+        <v>4</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C189" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D189" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E189" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F189" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G189" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H189" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_floors.png</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors</t>
         </is>
       </c>
     </row>
@@ -7661,22 +7661,22 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/shelf_arrow.png</t>
+          <t xml:space="preserve">ui/live_lantern.png</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154×161</t>
+          <t xml:space="preserve">460×568</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.shelf.arrow</t>
+          <t xml:space="preserve">ui.live.lantern</t>
         </is>
       </c>
     </row>
@@ -7701,12 +7701,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/live_map.png</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">620×786</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.live.map</t>
         </is>
       </c>
     </row>
@@ -7741,12 +7741,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/live_noise.png</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.live.noise</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/live_radio.png</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">220×420</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 무전기</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.live.radio</t>
         </is>
       </c>
     </row>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/live_superchat.png</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">383×62</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -7846,47 +7846,47 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.live.superchat</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2">
-        <v>4</v>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="A195" s="0">
+        <v>4</v>
+      </c>
+      <c r="B195" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/suspicion5.png</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×128</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.suspicion5</t>
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
         </is>
       </c>
     </row>
@@ -7896,81 +7896,361 @@
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2">
+        <v>4</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154×161</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.shelf.arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2">
+        <v>4</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2">
+        <v>4</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2">
+        <v>4</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2">
+        <v>4</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2">
+        <v>4</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion5.png</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion5</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0">
+        <v>4</v>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C196" s="0" t="inlineStr">
+      <c r="C203" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D196" s="0" t="inlineStr">
+      <c r="D203" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E196" s="0" t="inlineStr">
+      <c r="E203" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F196" s="0" t="inlineStr">
+      <c r="F203" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G196" s="0" t="inlineStr">
+      <c r="G203" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H196" s="0" t="inlineStr">
+      <c r="H203" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="0">
-        <v>4</v>
-      </c>
-      <c r="B197" s="0" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="0">
+        <v>4</v>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C197" s="0" t="inlineStr">
+      <c r="C204" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D197" s="0" t="inlineStr">
+      <c r="D204" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E197" s="0" t="inlineStr">
+      <c r="E204" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F197" s="0" t="inlineStr">
+      <c r="F204" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G197" s="0" t="inlineStr">
+      <c r="G204" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H197" s="0" t="inlineStr">
+      <c r="H204" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H197"/>
+  <autoFilter ref="A1:H204"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -6781,12 +6781,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">ui/floors/floor_01.png</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 1층 채움</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">ui.live.floors.1</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
+          <t xml:space="preserve">ui/floors/floor_02.png</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×144</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 2층 채움</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+          <t xml:space="preserve">ui.live.floors.2</t>
         </is>
       </c>
     </row>
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">ui/floors/floor_03.png</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 3층 채움</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">ui.live.floors.3</t>
         </is>
       </c>
     </row>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">ui/floors/floor_04.png</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 4층 채움</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">ui.live.floors.4</t>
         </is>
       </c>
     </row>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">ui/floors/floor_05.png</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 5층 채움</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">ui.live.floors.5</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">ui/floors/floor_06.png</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 6층 채움</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">ui.live.floors.6</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">ui/floors/floor_07.png</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 7층 채움</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">ui.live.floors.7</t>
         </is>
       </c>
     </row>
@@ -7061,12 +7061,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">ui/floors/floor_08.png</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 8층 채움</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">ui.live.floors.8</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
+          <t xml:space="preserve">ui/floors/floor_09.png</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452×831</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 9층 채움</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+          <t xml:space="preserve">ui.live.floors.9</t>
         </is>
       </c>
     </row>
@@ -7141,12 +7141,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">ui/floors/floor_10.png</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 10층 채움</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">ui.live.floors.10</t>
         </is>
       </c>
     </row>
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
+          <t xml:space="preserve">ui/floors/floor_11.png</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×302</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 11층 채움</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+          <t xml:space="preserve">ui.live.floors.11</t>
         </is>
       </c>
     </row>
@@ -7221,12 +7221,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">ui/floors/floor_12.png</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 12층 채움</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">ui.live.floors.12</t>
         </is>
       </c>
     </row>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">ui/floors/floor_13.png</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 13층 채움</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">ui.live.floors.13</t>
         </is>
       </c>
     </row>
@@ -7301,12 +7301,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">ui/floors/floor_14.png</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 14층 채움</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">ui.live.floors.14</t>
         </is>
       </c>
     </row>
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">ui/floors/floor_15.png</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 15층 채움</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">ui.live.floors.15</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_selected.png</t>
+          <t xml:space="preserve">ui/floors/floor_16.png</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×240</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 16층 채움</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">ui.live.floors.16</t>
         </is>
       </c>
     </row>
@@ -7421,12 +7421,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">ui/floors/floor_17.png</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 17층 채움</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">ui.live.floors.17</t>
         </is>
       </c>
     </row>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">ui/floors/floor_18.png</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 18층 채움</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">ui.live.floors.18</t>
         </is>
       </c>
     </row>
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">ui/floors/floor_19.png</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 19층 채움</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">ui.live.floors.19</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7541,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">ui/floors/floor_20.png</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 20층 채움</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">ui.live.floors.20</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">ui/floors/floor_21.png</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 21층 채움</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">ui.live.floors.21</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">ui/floors/floor_22.png</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 22층 채움</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">ui.live.floors.22</t>
         </is>
       </c>
     </row>
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">ui/floors/floor_23.png</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 23층 채움</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">ui.live.floors.23</t>
         </is>
       </c>
     </row>
@@ -7701,12 +7701,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">ui/floors/floor_24.png</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 24층 채움</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">ui.live.floors.24</t>
         </is>
       </c>
     </row>
@@ -7741,12 +7741,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">ui/floors/floor_25.png</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 25층 채움</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">ui.live.floors.25</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">ui/floors/floor_26.png</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 26층 채움</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">ui.live.floors.26</t>
         </is>
       </c>
     </row>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_superchat.png</t>
+          <t xml:space="preserve">ui/floors/floor_27.png</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383×62</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 27층 채움</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -7846,87 +7846,87 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.superchat</t>
+          <t xml:space="preserve">ui.live.floors.27</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="0">
-        <v>4</v>
-      </c>
-      <c r="B195" s="0" t="inlineStr">
+      <c r="A195" s="2">
+        <v>4</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C195" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D195" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E195" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F195" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G195" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H195" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/floors/floor_28.png</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 28층 채움</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors.28</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="0">
-        <v>4</v>
-      </c>
-      <c r="B196" s="0" t="inlineStr">
+      <c r="A196" s="2">
+        <v>4</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C196" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D196" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E196" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F196" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G196" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H196" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/floors/floor_29.png</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 29층 채움</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors.29</t>
         </is>
       </c>
     </row>
@@ -7941,22 +7941,22 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/shelf_arrow.png</t>
+          <t xml:space="preserve">ui/floors/floor_30.png</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154×161</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 30층 채움</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.shelf.arrow</t>
+          <t xml:space="preserve">ui.live.floors.30</t>
         </is>
       </c>
     </row>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/floors/floor_31.png</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 31층 채움</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.live.floors.31</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/floors/floor_32.png</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 32층 채움</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.live.floors.32</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/floors/floor_33.png</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 33층 채움</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.live.floors.33</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/floors/floor_34.png</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 34층 채움</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.live.floors.34</t>
         </is>
       </c>
     </row>
@@ -8141,116 +8141,1716 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/floors/floor_35.png</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 35층 채움</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2">
+        <v>4</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/floors/floor_36.png</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 36층 채움</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2">
+        <v>4</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/floors/floor_37.png</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 37층 채움</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2">
+        <v>4</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/floors/floor_38.png</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 38층 채움</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2">
+        <v>4</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/floors/floor_39.png</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 39층 채움</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2">
+        <v>4</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/floors/floor_40.png</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 40층 채움</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2">
+        <v>4</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/hud_status.png</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700×144</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.hud.status</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2">
+        <v>4</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/hud_tools.png</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740×144</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.hud.tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2">
+        <v>4</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.help.hover</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2">
+        <v>4</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_help.png</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.help</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2">
+        <v>4</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.options.hover</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2">
+        <v>4</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_options.png</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.options</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2">
+        <v>4</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.save.hover</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2">
+        <v>4</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/icon_save.png</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112×112</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.icon.save</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2">
+        <v>4</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/inventory_window.png</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1452×831</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.window</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2">
+        <v>4</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×94</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2">
+        <v>4</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×302</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2">
+        <v>4</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_section.png</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×238</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.section</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2">
+        <v>4</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×177</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2">
+        <v>4</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_top.png</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×318</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.top</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2">
+        <v>4</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_window.png</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×1129</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장비 상세 정보창</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2">
+        <v>4</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_selected.png</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228×240</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2">
+        <v>4</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_badge.png</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206×74</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ LIVE 표시</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.badge</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2">
+        <v>4</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_blink.png</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26×28</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.blink</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2">
+        <v>4</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_chat.png</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424×298</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2">
+        <v>4</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1040×200</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.dialogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2">
+        <v>4</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_door.png</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.door</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2">
+        <v>4</v>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_floors.png</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2">
+        <v>4</v>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_lantern.png</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">460×568</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.lantern</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2">
+        <v>4</v>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_map.png</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620×786</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.map</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2">
+        <v>4</v>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_noise.png</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2">
+        <v>4</v>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_radio.png</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220×420</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 무전기</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2">
+        <v>4</v>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_superchat.png</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383×62</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.superchat</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0">
+        <v>4</v>
+      </c>
+      <c r="B235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0">
+        <v>4</v>
+      </c>
+      <c r="B236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2">
+        <v>4</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154×161</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.shelf.arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2">
+        <v>4</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2">
+        <v>4</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2">
+        <v>4</v>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2">
+        <v>4</v>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2">
+        <v>4</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/suspicion5.png</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×128</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.suspicion5</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="0">
-        <v>4</v>
-      </c>
-      <c r="B203" s="0" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="0">
+        <v>4</v>
+      </c>
+      <c r="B243" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C203" s="0" t="inlineStr">
+      <c r="C243" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D203" s="0" t="inlineStr">
+      <c r="D243" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E203" s="0" t="inlineStr">
+      <c r="E243" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F203" s="0" t="inlineStr">
+      <c r="F243" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G203" s="0" t="inlineStr">
+      <c r="G243" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H203" s="0" t="inlineStr">
+      <c r="H243" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="0">
-        <v>4</v>
-      </c>
-      <c r="B204" s="0" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="0">
+        <v>4</v>
+      </c>
+      <c r="B244" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C204" s="0" t="inlineStr">
+      <c r="C244" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D204" s="0" t="inlineStr">
+      <c r="D244" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E204" s="0" t="inlineStr">
+      <c r="E244" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F204" s="0" t="inlineStr">
+      <c r="F244" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G204" s="0" t="inlineStr">
+      <c r="G244" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H204" s="0" t="inlineStr">
+      <c r="H244" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H204"/>
+  <autoFilter ref="A1:H244"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -8381,12 +8381,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">ui/fx_sword.png</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">1920×480</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">③ 공격 연출 — 칼 슬래시 10프레임, 공격 선택 시 1회 재생</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">ui.live.fx.sword</t>
         </is>
       </c>
     </row>
@@ -8421,12 +8421,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
+          <t xml:space="preserve">ui/hud_status.png</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×144</t>
+          <t xml:space="preserve">700×144</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+          <t xml:space="preserve">ui.hud.status</t>
         </is>
       </c>
     </row>
@@ -8461,12 +8461,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">ui/hud_tools.png</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">740×144</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">ui.hud.tools</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">ui.icon.help.hover</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">ui/icon_help.png</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">ui.icon.help</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">ui.icon.options.hover</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">ui/icon_options.png</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">ui.icon.options</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">ui.icon.save.hover</t>
         </is>
       </c>
     </row>
@@ -8701,12 +8701,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
+          <t xml:space="preserve">ui/icon_save.png</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452×831</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+          <t xml:space="preserve">ui.icon.save</t>
         </is>
       </c>
     </row>
@@ -8741,12 +8741,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">ui/inventory_window.png</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">1452×831</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">ui.inventory.window</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×302</t>
+          <t xml:space="preserve">536×94</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">536×302</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">ui/item_info_section.png</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">536×238</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">ui.inventory.info.section</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">536×177</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
         </is>
       </c>
     </row>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">ui/item_info_top.png</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">536×318</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">ui.inventory.info.top</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_selected.png</t>
+          <t xml:space="preserve">ui/item_info_window.png</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×240</t>
+          <t xml:space="preserve">536×1129</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+          <t xml:space="preserve">장비 상세 정보창</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">ui.inventory.info</t>
         </is>
       </c>
     </row>
@@ -9021,12 +9021,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">ui/item_selected.png</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">228×240</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">ui.inventory.selected</t>
         </is>
       </c>
     </row>
@@ -9061,12 +9061,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">ui/live_badge.png</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">206×74</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">③ LIVE 표시</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">ui.live.badge</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">ui/live_blink.png</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">26×28</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">ui.live.blink</t>
         </is>
       </c>
     </row>
@@ -9141,12 +9141,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">ui/live_chat.png</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">424×298</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">ui.live.chat</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">1040×200</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">ui.live.dialogue</t>
         </is>
       </c>
     </row>
@@ -9221,12 +9221,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">ui/live_door.png</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">ui.live.door</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">ui/live_floors.png</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">ui.live.floors</t>
         </is>
       </c>
     </row>
@@ -9301,12 +9301,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">ui/live_lantern.png</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">460×568</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">ui.live.lantern</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9341,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">ui/live_map.png</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">620×786</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">ui.live.map</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">ui/live_noise.png</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">ui.live.noise</t>
         </is>
       </c>
     </row>
@@ -9421,72 +9421,72 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/live_radio.png</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220×420</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 무전기</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2">
+        <v>4</v>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/live_superchat.png</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">383×62</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.live.superchat</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="0">
-        <v>4</v>
-      </c>
-      <c r="B235" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C235" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D235" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E235" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F235" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G235" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H235" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
         </is>
       </c>
     </row>
@@ -9501,72 +9501,72 @@
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0">
+        <v>4</v>
+      </c>
+      <c r="B237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/seal.png</t>
         </is>
       </c>
-      <c r="D236" s="0" t="inlineStr">
+      <c r="D237" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">768×192</t>
         </is>
       </c>
-      <c r="E236" s="0" t="inlineStr">
+      <c r="E237" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
         </is>
       </c>
-      <c r="F236" s="0" t="inlineStr">
+      <c r="F237" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">봉랍 도장 4프레임</t>
         </is>
       </c>
-      <c r="G236" s="0" t="inlineStr">
+      <c r="G237" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H236" s="0" t="inlineStr">
+      <c r="H237" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.seal</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2">
-        <v>4</v>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/shelf_arrow.png</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154×161</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정확히 1/2 (77x80)</t>
-        </is>
-      </c>
-      <c r="F237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
-        </is>
-      </c>
-      <c r="G237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.shelf.arrow</t>
         </is>
       </c>
     </row>
@@ -9581,22 +9581,22 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">154×161</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.shelf.arrow</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/suspicion1.png</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.suspicion1</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/suspicion2.png</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.suspicion2</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/suspicion3.png</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.suspicion3</t>
         </is>
       </c>
     </row>
@@ -9741,72 +9741,72 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2">
+        <v>4</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/suspicion5.png</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×128</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.suspicion5</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="0">
-        <v>4</v>
-      </c>
-      <c r="B243" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 패널</t>
-        </is>
-      </c>
-      <c r="C243" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/panel_sunken.png</t>
-        </is>
-      </c>
-      <c r="D243" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48×48</t>
-        </is>
-      </c>
-      <c r="E243" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F243" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
-        </is>
-      </c>
-      <c r="G243" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H243" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
@@ -9821,36 +9821,76 @@
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/panel_sunken.png</t>
+        </is>
+      </c>
+      <c r="D244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48×48</t>
+        </is>
+      </c>
+      <c r="E244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
+        </is>
+      </c>
+      <c r="F244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
+        </is>
+      </c>
+      <c r="G244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.panel.sunken.9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0">
+        <v>4</v>
+      </c>
+      <c r="B245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 패널</t>
+        </is>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D244" s="0" t="inlineStr">
+      <c r="D245" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E244" s="0" t="inlineStr">
+      <c r="E245" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F244" s="0" t="inlineStr">
+      <c r="F245" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G244" s="0" t="inlineStr">
+      <c r="G245" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H244" s="0" t="inlineStr">
+      <c r="H245" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H244"/>
+  <autoFilter ref="A1:H245"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/item_drop.mp3</t>
+          <t xml:space="preserve">sfx/item_drop_heavy.mp3</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비를 진열대에 놓는다 (사운드V4 · 물건드랍_중간 철)</t>
+          <t xml:space="preserve">장비를 진열대에 놓는 무거운 금속음</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.item.drop</t>
+          <t xml:space="preserve">sfx.item.drop.heavy</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/item_pick.mp3</t>
+          <t xml:space="preserve">sfx/item_drop_light.mp3</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비를 집어 든다 (사운드V4 · 버튼 뽑)</t>
+          <t xml:space="preserve">물약·유물을 진열대에 놓는 가벼운 금속음</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.item.pick</t>
+          <t xml:space="preserve">sfx.item.drop.light</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/potion.mp3</t>
+          <t xml:space="preserve">sfx/item_drop.mp3</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 — 물약을 마신다 (사운드V4 · 포션먹음이)</t>
+          <t xml:space="preserve">장비를 진열대에 놓는다 (사운드V4 · 물건드랍_중간 철)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.potion</t>
+          <t xml:space="preserve">sfx.item.drop</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/record.mp3</t>
+          <t xml:space="preserve">sfx/item_pick.mp3</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신기록 갱신</t>
+          <t xml:space="preserve">장비를 집어 든다 (사운드V4 · 버튼 뽑)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.record</t>
+          <t xml:space="preserve">sfx.item.pick</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive_knock.mp3</t>
+          <t xml:space="preserve">sfx/office_walk.mp3</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
+          <t xml:space="preserve">편성실 용사의 입·퇴장 걸음</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive.knock</t>
+          <t xml:space="preserve">sfx.office.walk</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive.mp3</t>
+          <t xml:space="preserve">sfx/potion.mp3</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
+          <t xml:space="preserve">전투 — 물약을 마신다 (사운드V4 · 포션먹음이)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive</t>
+          <t xml:space="preserve">sfx.potion</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/signal_back.mp3</t>
+          <t xml:space="preserve">sfx/record.mp3</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">방송 개시 — 끊겼던 신호가 돌아온다 (사운드V4 · 방송사고_끝)</t>
+          <t xml:space="preserve">신기록 갱신</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.signal.back</t>
+          <t xml:space="preserve">sfx.record</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/stamp.mp3</t>
+          <t xml:space="preserve">sfx/revive_knock.mp3</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
+          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.stamp</t>
+          <t xml:space="preserve">sfx.revive.knock</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/superchat.mp3</t>
+          <t xml:space="preserve">sfx/revive.mp3</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">슈퍼챗 알림 (사운드V4 · 전용 효과음)</t>
+          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.superchat</t>
+          <t xml:space="preserve">sfx.revive</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text_female.wav</t>
+          <t xml:space="preserve">sfx/signal_back.mp3</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대사 타자음 · 여성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
+          <t xml:space="preserve">방송 개시 — 끊겼던 신호가 돌아온다 (사운드V4 · 방송사고_끝)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text.female</t>
+          <t xml:space="preserve">sfx.signal.back</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text_male.wav</t>
+          <t xml:space="preserve">sfx/stamp.mp3</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대사 타자음 · 남성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
+          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text.male</t>
+          <t xml:space="preserve">sfx.stamp</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text.mp3</t>
+          <t xml:space="preserve">sfx/superchat.mp3</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
+          <t xml:space="preserve">슈퍼챗 알림 (사운드V4 · 전용 효과음)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text</t>
+          <t xml:space="preserve">sfx.superchat</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_chime.mp3</t>
+          <t xml:space="preserve">sfx/text_female.wav</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
+          <t xml:space="preserve">대사 타자음 · 여성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.chime</t>
+          <t xml:space="preserve">sfx.text.female</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_door.mp3</t>
+          <t xml:space="preserve">sfx/text_male.wav</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
+          <t xml:space="preserve">대사 타자음 · 남성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.door</t>
+          <t xml:space="preserve">sfx.text.male</t>
         </is>
       </c>
     </row>
@@ -3576,17 +3576,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/contract_stamp.png</t>
+          <t xml:space="preserve">sfx/text.mp3</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179×178</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 우측 하단에 찍는 확정 도장</t>
+          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.contract.stamp</t>
+          <t xml:space="preserve">sfx.text</t>
         </is>
       </c>
     </row>
@@ -3616,17 +3616,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/lamp.png</t>
+          <t xml:space="preserve">sfx/title_chime.mp3</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224×352</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.lamp</t>
+          <t xml:space="preserve">sfx.title.chime</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/ledger.png</t>
+          <t xml:space="preserve">sfx/title_door.mp3</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336×264</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 출연자 서류철</t>
+          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.ledger</t>
+          <t xml:space="preserve">sfx.title.door</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/scroll.png</t>
+          <t xml:space="preserve">prop/contract_stamp.png</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176×64</t>
+          <t xml:space="preserve">179×178</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 서류 조각</t>
+          <t xml:space="preserve">계약서 우측 하단에 찍는 확정 도장</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.scroll</t>
+          <t xml:space="preserve">prop.contract.stamp</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/stamp.png</t>
+          <t xml:space="preserve">prop/lamp.png</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128×208</t>
+          <t xml:space="preserve">224×352</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+          <t xml:space="preserve">작업대의 실제 석유 램프</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.stamp</t>
+          <t xml:space="preserve">prop.lamp</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tag.png</t>
+          <t xml:space="preserve">prop/ledger.png</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152×104</t>
+          <t xml:space="preserve">336×264</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 가격표</t>
+          <t xml:space="preserve">작업대의 출연자 서류철</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tag</t>
+          <t xml:space="preserve">prop.ledger</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tv_live_hover.png</t>
+          <t xml:space="preserve">prop/revive_stamp_a.png</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×216</t>
+          <t xml:space="preserve">412×424</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">방송 시작 TV의 마우스 오버 상태</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 A</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tv.live.hover</t>
+          <t xml:space="preserve">prop.revive.stamp.a</t>
         </is>
       </c>
     </row>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tv_live.png</t>
+          <t xml:space="preserve">prop/revive_stamp_b.png</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219×202</t>
+          <t xml:space="preserve">424×420</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약 확정 뒤 방송을 시작할 수 있는 TV</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 B</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tv.live</t>
+          <t xml:space="preserve">prop.revive.stamp.b</t>
         </is>
       </c>
     </row>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tv.png</t>
+          <t xml:space="preserve">prop/revive_stamp_c.png</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219×202</t>
+          <t xml:space="preserve">380×408</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 용사 배경의 왼쪽 상자 위 브라운관 TV</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 C</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tv</t>
+          <t xml:space="preserve">prop.revive.stamp.c</t>
         </is>
       </c>
     </row>
@@ -3936,27 +3936,27 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_ilan.png</t>
+          <t xml:space="preserve">prop/revive_stamp_f.png</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780×1215</t>
+          <t xml:space="preserve">396×404</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미레(마법사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 F (훼손)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.ilan</t>
+          <t xml:space="preserve">prop.revive.stamp.f</t>
         </is>
       </c>
     </row>
@@ -3976,27 +3976,27 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_juno.png</t>
+          <t xml:space="preserve">prop/revive_stamp_s.png</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780×1215</t>
+          <t xml:space="preserve">404×420</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">펜로(궁수) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 S (온전)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.juno</t>
+          <t xml:space="preserve">prop.revive.stamp.s</t>
         </is>
       </c>
     </row>
@@ -4016,27 +4016,27 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_karin.png</t>
+          <t xml:space="preserve">prop/scroll.png</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780×1215</t>
+          <t xml:space="preserve">176×64</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">노일(검사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">계약서 서류 조각</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.karin</t>
+          <t xml:space="preserve">prop.scroll</t>
         </is>
       </c>
     </row>
@@ -4056,27 +4056,27 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_mor.png</t>
+          <t xml:space="preserve">prop/stamp.png</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1779×1215</t>
+          <t xml:space="preserve">128×208</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">헤일(힐러) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.mor</t>
+          <t xml:space="preserve">prop.stamp</t>
         </is>
       </c>
     </row>
@@ -4096,27 +4096,27 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_sela.png</t>
+          <t xml:space="preserve">prop/tag.png</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780×1215</t>
+          <t xml:space="preserve">152×104</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">녹스(도적) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">작업대의 가격표</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.sela</t>
+          <t xml:space="preserve">prop.tag</t>
         </is>
       </c>
     </row>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
+          <t xml:space="preserve">prop/tv_live_hover.png</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">228×216</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
+          <t xml:space="preserve">방송 시작 TV의 마우스 오버 상태</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.angry</t>
+          <t xml:space="preserve">prop.tv.live.hover</t>
         </is>
       </c>
     </row>
@@ -4176,17 +4176,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
+          <t xml:space="preserve">prop/tv_live.png</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">219×202</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
+          <t xml:space="preserve">계약 확정 뒤 방송을 시작할 수 있는 TV</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blank</t>
+          <t xml:space="preserve">prop.tv.live</t>
         </is>
       </c>
     </row>
@@ -4216,17 +4216,17 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
+          <t xml:space="preserve">prop/tv.png</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">219×202</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
+          <t xml:space="preserve">편성실 용사 배경의 왼쪽 상자 위 브라운관 TV</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blush</t>
+          <t xml:space="preserve">prop.tv</t>
         </is>
       </c>
     </row>
@@ -4261,22 +4261,22 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
+          <t xml:space="preserve">star/corpse_ilan.png</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
+          <t xml:space="preserve">미레(마법사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.empty</t>
+          <t xml:space="preserve">star.corpse.ilan</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4301,22 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
+          <t xml:space="preserve">star/corpse_juno.png</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
+          <t xml:space="preserve">펜로(궁수) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.neutral</t>
+          <t xml:space="preserve">star.corpse.juno</t>
         </is>
       </c>
     </row>
@@ -4341,22 +4341,22 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
+          <t xml:space="preserve">star/corpse_karin.png</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
+          <t xml:space="preserve">노일(검사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.pain</t>
+          <t xml:space="preserve">star.corpse.karin</t>
         </is>
       </c>
     </row>
@@ -4381,22 +4381,22 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
+          <t xml:space="preserve">star/corpse_mor.png</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1779×1215</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
+          <t xml:space="preserve">헤일(힐러) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.sad</t>
+          <t xml:space="preserve">star.corpse.mor</t>
         </is>
       </c>
     </row>
@@ -4421,22 +4421,22 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
+          <t xml:space="preserve">star/corpse_sela.png</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
+          <t xml:space="preserve">녹스(도적) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.smile</t>
+          <t xml:space="preserve">star.corpse.sela</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
+          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
+          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.surprise</t>
+          <t xml:space="preserve">star.expression.ilan.angry</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_angry.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno angry 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.angry</t>
+          <t xml:space="preserve">star.expression.ilan.blank</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blank.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blank 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blank</t>
+          <t xml:space="preserve">star.expression.ilan.blush</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blush.png</t>
+          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blush 대사 표정 전신</t>
+          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blush</t>
+          <t xml:space="preserve">star.expression.ilan.empty</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_empty.png</t>
+          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno empty 대사 표정 전신</t>
+          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.empty</t>
+          <t xml:space="preserve">star.expression.ilan.neutral</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
+          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
+          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.neutral</t>
+          <t xml:space="preserve">star.expression.ilan.pain</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_pain.png</t>
+          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno pain 대사 표정 전신</t>
+          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.pain</t>
+          <t xml:space="preserve">star.expression.ilan.sad</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_sad.png</t>
+          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno sad 대사 표정 전신</t>
+          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.sad</t>
+          <t xml:space="preserve">star.expression.ilan.smile</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_smile.png</t>
+          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno smile 대사 표정 전신</t>
+          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.smile</t>
+          <t xml:space="preserve">star.expression.ilan.surprise</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
+          <t xml:space="preserve">star/expressions/juno_angry.png</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
+          <t xml:space="preserve">juno angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.surprise</t>
+          <t xml:space="preserve">star.expression.juno.angry</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_angry.png</t>
+          <t xml:space="preserve">star/expressions/juno_blank.png</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin angry 대사 표정 전신</t>
+          <t xml:space="preserve">juno blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.angry</t>
+          <t xml:space="preserve">star.expression.juno.blank</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blank.png</t>
+          <t xml:space="preserve">star/expressions/juno_blush.png</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blank 대사 표정 전신</t>
+          <t xml:space="preserve">juno blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blank</t>
+          <t xml:space="preserve">star.expression.juno.blush</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blush.png</t>
+          <t xml:space="preserve">star/expressions/juno_empty.png</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blush 대사 표정 전신</t>
+          <t xml:space="preserve">juno empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blush</t>
+          <t xml:space="preserve">star.expression.juno.empty</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_empty.png</t>
+          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin empty 대사 표정 전신</t>
+          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.empty</t>
+          <t xml:space="preserve">star.expression.juno.neutral</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
+          <t xml:space="preserve">star/expressions/juno_pain.png</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
+          <t xml:space="preserve">juno pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.neutral</t>
+          <t xml:space="preserve">star.expression.juno.pain</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_pain.png</t>
+          <t xml:space="preserve">star/expressions/juno_sad.png</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin pain 대사 표정 전신</t>
+          <t xml:space="preserve">juno sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.pain</t>
+          <t xml:space="preserve">star.expression.juno.sad</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_sad.png</t>
+          <t xml:space="preserve">star/expressions/juno_smile.png</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin sad 대사 표정 전신</t>
+          <t xml:space="preserve">juno smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.sad</t>
+          <t xml:space="preserve">star.expression.juno.smile</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_smile.png</t>
+          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin smile 대사 표정 전신</t>
+          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.smile</t>
+          <t xml:space="preserve">star.expression.juno.surprise</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
+          <t xml:space="preserve">star/expressions/karin_angry.png</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
+          <t xml:space="preserve">karin angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.surprise</t>
+          <t xml:space="preserve">star.expression.karin.angry</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_angry.png</t>
+          <t xml:space="preserve">star/expressions/karin_blank.png</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor angry 대사 표정 전신</t>
+          <t xml:space="preserve">karin blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.angry</t>
+          <t xml:space="preserve">star.expression.karin.blank</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blank.png</t>
+          <t xml:space="preserve">star/expressions/karin_blush.png</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blank 대사 표정 전신</t>
+          <t xml:space="preserve">karin blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blank</t>
+          <t xml:space="preserve">star.expression.karin.blush</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blush.png</t>
+          <t xml:space="preserve">star/expressions/karin_empty.png</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blush 대사 표정 전신</t>
+          <t xml:space="preserve">karin empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blush</t>
+          <t xml:space="preserve">star.expression.karin.empty</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_empty.png</t>
+          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor empty 대사 표정 전신</t>
+          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.empty</t>
+          <t xml:space="preserve">star.expression.karin.neutral</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
+          <t xml:space="preserve">star/expressions/karin_pain.png</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
+          <t xml:space="preserve">karin pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.neutral</t>
+          <t xml:space="preserve">star.expression.karin.pain</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_pain.png</t>
+          <t xml:space="preserve">star/expressions/karin_sad.png</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor pain 대사 표정 전신</t>
+          <t xml:space="preserve">karin sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.pain</t>
+          <t xml:space="preserve">star.expression.karin.sad</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_sad.png</t>
+          <t xml:space="preserve">star/expressions/karin_smile.png</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor sad 대사 표정 전신</t>
+          <t xml:space="preserve">karin smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.sad</t>
+          <t xml:space="preserve">star.expression.karin.smile</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_smile.png</t>
+          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor smile 대사 표정 전신</t>
+          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.smile</t>
+          <t xml:space="preserve">star.expression.karin.surprise</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
+          <t xml:space="preserve">star/expressions/mor_angry.png</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
+          <t xml:space="preserve">mor angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.surprise</t>
+          <t xml:space="preserve">star.expression.mor.angry</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_angry.png</t>
+          <t xml:space="preserve">star/expressions/mor_blank.png</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela angry 대사 표정 전신</t>
+          <t xml:space="preserve">mor blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.angry</t>
+          <t xml:space="preserve">star.expression.mor.blank</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blank.png</t>
+          <t xml:space="preserve">star/expressions/mor_blush.png</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blank 대사 표정 전신</t>
+          <t xml:space="preserve">mor blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blank</t>
+          <t xml:space="preserve">star.expression.mor.blush</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blush.png</t>
+          <t xml:space="preserve">star/expressions/mor_empty.png</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blush 대사 표정 전신</t>
+          <t xml:space="preserve">mor empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blush</t>
+          <t xml:space="preserve">star.expression.mor.empty</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_empty.png</t>
+          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela empty 대사 표정 전신</t>
+          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.empty</t>
+          <t xml:space="preserve">star.expression.mor.neutral</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
+          <t xml:space="preserve">star/expressions/mor_pain.png</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
+          <t xml:space="preserve">mor pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.neutral</t>
+          <t xml:space="preserve">star.expression.mor.pain</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_pain.png</t>
+          <t xml:space="preserve">star/expressions/mor_sad.png</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela pain 대사 표정 전신</t>
+          <t xml:space="preserve">mor sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.pain</t>
+          <t xml:space="preserve">star.expression.mor.sad</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_sad.png</t>
+          <t xml:space="preserve">star/expressions/mor_smile.png</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela sad 대사 표정 전신</t>
+          <t xml:space="preserve">mor smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.sad</t>
+          <t xml:space="preserve">star.expression.mor.smile</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_smile.png</t>
+          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela smile 대사 표정 전신</t>
+          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.smile</t>
+          <t xml:space="preserve">star.expression.mor.surprise</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
+          <t xml:space="preserve">star/expressions/sela_angry.png</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
+          <t xml:space="preserve">sela angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.surprise</t>
+          <t xml:space="preserve">star.expression.sela.angry</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_blank.png</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 대사 전신</t>
+          <t xml:space="preserve">sela blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.ilan</t>
+          <t xml:space="preserve">star.expression.sela.blank</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_blush.png</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 표정 전신</t>
+          <t xml:space="preserve">sela blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan</t>
+          <t xml:space="preserve">star.expression.sela.blush</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_empty.png</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 대사 전신</t>
+          <t xml:space="preserve">sela empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.juno</t>
+          <t xml:space="preserve">star.expression.sela.empty</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
+          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno</t>
+          <t xml:space="preserve">star.expression.sela.neutral</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_pain.png</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 대사 전신</t>
+          <t xml:space="preserve">sela pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.karin</t>
+          <t xml:space="preserve">star.expression.sela.pain</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_sad.png</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 표정 전신</t>
+          <t xml:space="preserve">sela sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin</t>
+          <t xml:space="preserve">star.expression.sela.sad</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_smile.png</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 대사 전신</t>
+          <t xml:space="preserve">sela smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.mor</t>
+          <t xml:space="preserve">star.expression.sela.smile</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 표정 전신</t>
+          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor</t>
+          <t xml:space="preserve">star.expression.sela.surprise</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6261,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/ilan.png</t>
+          <t xml:space="preserve">star/ilan_dialogue.png</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50×60</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">일란 대사 전신</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.ilan</t>
+          <t xml:space="preserve">star.dialogue.ilan</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/juno.png</t>
+          <t xml:space="preserve">star/ilan_expression.png</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64×55</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">일란 표정 전신</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.juno</t>
+          <t xml:space="preserve">star.expression.ilan</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/karin.png</t>
+          <t xml:space="preserve">star/juno_dialogue.png</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84×57</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">주노 대사 전신</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.karin</t>
+          <t xml:space="preserve">star.dialogue.juno</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/mor.png</t>
+          <t xml:space="preserve">star/juno_expression.png</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56×40</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.mor</t>
+          <t xml:space="preserve">star.expression.juno</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/sela.png</t>
+          <t xml:space="preserve">star/karin_dialogue.png</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40×16</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">카린 대사 전신</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.sela</t>
+          <t xml:space="preserve">star.dialogue.karin</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_dialogue.png</t>
+          <t xml:space="preserve">star/karin_expression.png</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 대사 전신</t>
+          <t xml:space="preserve">카린 표정 전신</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.sela</t>
+          <t xml:space="preserve">star.expression.karin</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_expression.png</t>
+          <t xml:space="preserve">star/mor_dialogue.png</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 표정 전신</t>
+          <t xml:space="preserve">모르 대사 전신</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -6526,47 +6526,47 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela</t>
+          <t xml:space="preserve">star.dialogue.mor</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="0">
-        <v>4</v>
-      </c>
-      <c r="B162" s="0" t="inlineStr">
+      <c r="A162" s="2">
+        <v>4</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
-      <c r="C162" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star/silhouette.png</t>
-        </is>
-      </c>
-      <c r="D162" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1536×480</t>
-        </is>
-      </c>
-      <c r="E162" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F162" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
-        </is>
-      </c>
-      <c r="G162" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H162" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star.silhouette</t>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/mor_expression.png</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모르 표정 전신</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.mor</t>
         </is>
       </c>
     </row>
@@ -6576,17 +6576,17 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/character_cover.png</t>
+          <t xml:space="preserve">star/mouth/ilan.png</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1087×258</t>
+          <t xml:space="preserve">50×60</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
+          <t xml:space="preserve">ilan 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.guest.cover</t>
+          <t xml:space="preserve">star.mouth.ilan</t>
         </is>
       </c>
     </row>
@@ -6616,17 +6616,17 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_hour.png</t>
+          <t xml:space="preserve">star/mouth/juno.png</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29×42</t>
+          <t xml:space="preserve">64×55</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock hour hand</t>
+          <t xml:space="preserve">juno 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.hour</t>
+          <t xml:space="preserve">star.mouth.juno</t>
         </is>
       </c>
     </row>
@@ -6656,17 +6656,17 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_minute.png</t>
+          <t xml:space="preserve">star/mouth/karin.png</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8×56</t>
+          <t xml:space="preserve">84×57</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock minute hand</t>
+          <t xml:space="preserve">karin 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.minute</t>
+          <t xml:space="preserve">star.mouth.karin</t>
         </is>
       </c>
     </row>
@@ -6696,17 +6696,17 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/contract_sheet.png</t>
+          <t xml:space="preserve">star/mouth/mor.png</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">795×1036</t>
+          <t xml:space="preserve">56×40</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
+          <t xml:space="preserve">mor 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -6726,47 +6726,47 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.contract.sheet</t>
+          <t xml:space="preserve">star.mouth.mor</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="0">
-        <v>4</v>
-      </c>
-      <c r="B167" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C167" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/cursor.png</t>
-        </is>
-      </c>
-      <c r="D167" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E167" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F167" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
-        </is>
-      </c>
-      <c r="G167" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H167" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.cursor</t>
+      <c r="A167" s="2">
+        <v>4</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/mouth/sela.png</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40×16</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sela 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.mouth.sela</t>
         </is>
       </c>
     </row>
@@ -6776,17 +6776,17 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_01.png</t>
+          <t xml:space="preserve">star/sela_dialogue.png</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 1층 채움</t>
+          <t xml:space="preserve">세라 대사 전신</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.1</t>
+          <t xml:space="preserve">star.dialogue.sela</t>
         </is>
       </c>
     </row>
@@ -6816,17 +6816,17 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_02.png</t>
+          <t xml:space="preserve">star/sela_expression.png</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 2층 채움</t>
+          <t xml:space="preserve">세라 표정 전신</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -6846,47 +6846,47 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.2</t>
+          <t xml:space="preserve">star.expression.sela</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2">
-        <v>4</v>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/floors/floor_03.png</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210×936</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 3층 채움</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.live.floors.3</t>
+      <c r="A170" s="0">
+        <v>4</v>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/silhouette.png</t>
+        </is>
+      </c>
+      <c r="D170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536×480</t>
+        </is>
+      </c>
+      <c r="E170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+        </is>
+      </c>
+      <c r="G170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.silhouette</t>
         </is>
       </c>
     </row>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_04.png</t>
+          <t xml:space="preserve">ui/character_cover.png</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">1087×258</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 4층 채움</t>
+          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.4</t>
+          <t xml:space="preserve">ui.guest.cover</t>
         </is>
       </c>
     </row>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_05.png</t>
+          <t xml:space="preserve">ui/clock_hour.png</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">29×42</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 5층 채움</t>
+          <t xml:space="preserve">HUD game-clock hour hand</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.5</t>
+          <t xml:space="preserve">ui.clock.hour</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_06.png</t>
+          <t xml:space="preserve">ui/clock_minute.png</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">8×56</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 6층 채움</t>
+          <t xml:space="preserve">HUD game-clock minute hand</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.6</t>
+          <t xml:space="preserve">ui.clock.minute</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_07.png</t>
+          <t xml:space="preserve">ui/contract_sheet.png</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">795×1036</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 7층 채움</t>
+          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -7046,47 +7046,47 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.7</t>
+          <t xml:space="preserve">ui.contract.sheet</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2">
-        <v>4</v>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="A175" s="0">
+        <v>4</v>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/floors/floor_08.png</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210×936</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 8층 채움</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.live.floors.8</t>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/cursor.png</t>
+        </is>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32×32</t>
+        </is>
+      </c>
+      <c r="E175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
+        </is>
+      </c>
+      <c r="G175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.cursor</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_09.png</t>
+          <t xml:space="preserve">ui/floors/floor_01.png</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 9층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 1층 채움</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.9</t>
+          <t xml:space="preserve">ui.live.floors.1</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_10.png</t>
+          <t xml:space="preserve">ui/floors/floor_02.png</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 10층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 2층 채움</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.10</t>
+          <t xml:space="preserve">ui.live.floors.2</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_11.png</t>
+          <t xml:space="preserve">ui/floors/floor_03.png</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 11층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 3층 채움</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.11</t>
+          <t xml:space="preserve">ui.live.floors.3</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_12.png</t>
+          <t xml:space="preserve">ui/floors/floor_04.png</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 12층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 4층 채움</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.12</t>
+          <t xml:space="preserve">ui.live.floors.4</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7261,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_13.png</t>
+          <t xml:space="preserve">ui/floors/floor_05.png</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 13층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 5층 채움</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.13</t>
+          <t xml:space="preserve">ui.live.floors.5</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_14.png</t>
+          <t xml:space="preserve">ui/floors/floor_06.png</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 14층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 6층 채움</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.14</t>
+          <t xml:space="preserve">ui.live.floors.6</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_15.png</t>
+          <t xml:space="preserve">ui/floors/floor_07.png</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 15층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 7층 채움</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.15</t>
+          <t xml:space="preserve">ui.live.floors.7</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_16.png</t>
+          <t xml:space="preserve">ui/floors/floor_08.png</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 16층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 8층 채움</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.16</t>
+          <t xml:space="preserve">ui.live.floors.8</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_17.png</t>
+          <t xml:space="preserve">ui/floors/floor_09.png</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 17층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 9층 채움</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.17</t>
+          <t xml:space="preserve">ui.live.floors.9</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_18.png</t>
+          <t xml:space="preserve">ui/floors/floor_10.png</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 18층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 10층 채움</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.18</t>
+          <t xml:space="preserve">ui.live.floors.10</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_19.png</t>
+          <t xml:space="preserve">ui/floors/floor_11.png</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 19층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 11층 채움</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.19</t>
+          <t xml:space="preserve">ui.live.floors.11</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_20.png</t>
+          <t xml:space="preserve">ui/floors/floor_12.png</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 20층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 12층 채움</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.20</t>
+          <t xml:space="preserve">ui.live.floors.12</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_21.png</t>
+          <t xml:space="preserve">ui/floors/floor_13.png</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 21층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 13층 채움</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.21</t>
+          <t xml:space="preserve">ui.live.floors.13</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_22.png</t>
+          <t xml:space="preserve">ui/floors/floor_14.png</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 22층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 14층 채움</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.22</t>
+          <t xml:space="preserve">ui.live.floors.14</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_23.png</t>
+          <t xml:space="preserve">ui/floors/floor_15.png</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 23층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 15층 채움</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.23</t>
+          <t xml:space="preserve">ui.live.floors.15</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_24.png</t>
+          <t xml:space="preserve">ui/floors/floor_16.png</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 24층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 16층 채움</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.24</t>
+          <t xml:space="preserve">ui.live.floors.16</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_25.png</t>
+          <t xml:space="preserve">ui/floors/floor_17.png</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 25층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 17층 채움</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.25</t>
+          <t xml:space="preserve">ui.live.floors.17</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_26.png</t>
+          <t xml:space="preserve">ui/floors/floor_18.png</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 26층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 18층 채움</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.26</t>
+          <t xml:space="preserve">ui.live.floors.18</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_27.png</t>
+          <t xml:space="preserve">ui/floors/floor_19.png</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 27층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 19층 채움</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.27</t>
+          <t xml:space="preserve">ui.live.floors.19</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_28.png</t>
+          <t xml:space="preserve">ui/floors/floor_20.png</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 28층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 20층 채움</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.28</t>
+          <t xml:space="preserve">ui.live.floors.20</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_29.png</t>
+          <t xml:space="preserve">ui/floors/floor_21.png</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 29층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 21층 채움</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.29</t>
+          <t xml:space="preserve">ui.live.floors.21</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_30.png</t>
+          <t xml:space="preserve">ui/floors/floor_22.png</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 30층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 22층 채움</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.30</t>
+          <t xml:space="preserve">ui.live.floors.22</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_31.png</t>
+          <t xml:space="preserve">ui/floors/floor_23.png</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 31층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 23층 채움</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.31</t>
+          <t xml:space="preserve">ui.live.floors.23</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_32.png</t>
+          <t xml:space="preserve">ui/floors/floor_24.png</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 32층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 24층 채움</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.32</t>
+          <t xml:space="preserve">ui.live.floors.24</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_33.png</t>
+          <t xml:space="preserve">ui/floors/floor_25.png</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 33층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 25층 채움</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.33</t>
+          <t xml:space="preserve">ui.live.floors.25</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_34.png</t>
+          <t xml:space="preserve">ui/floors/floor_26.png</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 34층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 26층 채움</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.34</t>
+          <t xml:space="preserve">ui.live.floors.26</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_35.png</t>
+          <t xml:space="preserve">ui/floors/floor_27.png</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 35층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 27층 채움</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.35</t>
+          <t xml:space="preserve">ui.live.floors.27</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_36.png</t>
+          <t xml:space="preserve">ui/floors/floor_28.png</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 36층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 28층 채움</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.36</t>
+          <t xml:space="preserve">ui.live.floors.28</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_37.png</t>
+          <t xml:space="preserve">ui/floors/floor_29.png</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 37층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 29층 채움</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.37</t>
+          <t xml:space="preserve">ui.live.floors.29</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_38.png</t>
+          <t xml:space="preserve">ui/floors/floor_30.png</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 38층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 30층 채움</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.38</t>
+          <t xml:space="preserve">ui.live.floors.30</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_39.png</t>
+          <t xml:space="preserve">ui/floors/floor_31.png</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 39층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 31층 채움</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.39</t>
+          <t xml:space="preserve">ui.live.floors.31</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_40.png</t>
+          <t xml:space="preserve">ui/floors/floor_32.png</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 40층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 32층 채움</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.40</t>
+          <t xml:space="preserve">ui.live.floors.32</t>
         </is>
       </c>
     </row>
@@ -8381,12 +8381,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/fx_sword.png</t>
+          <t xml:space="preserve">ui/floors/floor_33.png</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×480</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 공격 연출 — 칼 슬래시 10프레임, 공격 선택 시 1회 재생</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 33층 채움</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.fx.sword</t>
+          <t xml:space="preserve">ui.live.floors.33</t>
         </is>
       </c>
     </row>
@@ -8421,12 +8421,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">ui/floors/floor_34.png</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 34층 채움</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">ui.live.floors.34</t>
         </is>
       </c>
     </row>
@@ -8461,12 +8461,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
+          <t xml:space="preserve">ui/floors/floor_35.png</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×144</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 35층 채움</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+          <t xml:space="preserve">ui.live.floors.35</t>
         </is>
       </c>
     </row>
@@ -8501,12 +8501,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">ui/floors/floor_36.png</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 36층 채움</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">ui.live.floors.36</t>
         </is>
       </c>
     </row>
@@ -8541,12 +8541,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">ui/floors/floor_37.png</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 37층 채움</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">ui.live.floors.37</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">ui/floors/floor_38.png</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 38층 채움</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">ui.live.floors.38</t>
         </is>
       </c>
     </row>
@@ -8621,12 +8621,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">ui/floors/floor_39.png</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 39층 채움</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">ui.live.floors.39</t>
         </is>
       </c>
     </row>
@@ -8661,12 +8661,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">ui/floors/floor_40.png</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 40층 채움</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">ui.live.floors.40</t>
         </is>
       </c>
     </row>
@@ -8701,12 +8701,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">ui/fx_shield.png</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">1680×420</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">③ 방어 연출 — 방패 막기 15프레임, 방어 선택 시 1회 재생</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">ui.live.fx.shield</t>
         </is>
       </c>
     </row>
@@ -8741,12 +8741,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
+          <t xml:space="preserve">ui/fx_sword.png</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452×831</t>
+          <t xml:space="preserve">1920×480</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
+          <t xml:space="preserve">③ 공격 연출 — 칼 슬래시 10프레임, 공격 선택 시 1회 재생</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+          <t xml:space="preserve">ui.live.fx.sword</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">ui/hud_status.png</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">700×144</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">ui.hud.status</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
+          <t xml:space="preserve">ui/hud_tools.png</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×302</t>
+          <t xml:space="preserve">740×144</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+          <t xml:space="preserve">ui.hud.tools</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">ui.icon.help.hover</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">ui/icon_help.png</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">ui.icon.help</t>
         </is>
       </c>
     </row>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">ui.icon.options.hover</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">ui/icon_options.png</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">ui.icon.options</t>
         </is>
       </c>
     </row>
@@ -9021,12 +9021,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_selected.png</t>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×240</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">ui.icon.save.hover</t>
         </is>
       </c>
     </row>
@@ -9061,12 +9061,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">ui/icon_save.png</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">ui.icon.save</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">ui/inventory_window.png</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">1452×831</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">ui.inventory.window</t>
         </is>
       </c>
     </row>
@@ -9141,12 +9141,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">536×94</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">536×302</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
         </is>
       </c>
     </row>
@@ -9221,12 +9221,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">ui/item_info_section.png</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">536×238</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">ui.inventory.info.section</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">536×177</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
         </is>
       </c>
     </row>
@@ -9301,12 +9301,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">ui/item_info_top.png</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">536×318</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">ui.inventory.info.top</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9341,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">ui/item_info_window.png</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">536×1129</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">장비 상세 정보창</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">ui.inventory.info</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">ui/item_selected.png</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">228×240</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">ui.inventory.selected</t>
         </is>
       </c>
     </row>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">ui/live_badge.png</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">206×74</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">③ LIVE 표시</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">ui.live.badge</t>
         </is>
       </c>
     </row>
@@ -9461,12 +9461,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_superchat.png</t>
+          <t xml:space="preserve">ui/live_blink.png</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383×62</t>
+          <t xml:space="preserve">26×28</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -9486,87 +9486,87 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.superchat</t>
+          <t xml:space="preserve">ui.live.blink</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="0">
-        <v>4</v>
-      </c>
-      <c r="B236" s="0" t="inlineStr">
+      <c r="A236" s="2">
+        <v>4</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C236" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D236" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E236" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F236" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G236" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H236" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_chat.png</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424×298</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.chat</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="0">
-        <v>4</v>
-      </c>
-      <c r="B237" s="0" t="inlineStr">
+      <c r="A237" s="2">
+        <v>4</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C237" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D237" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E237" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F237" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G237" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H237" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1040×200</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.dialogue</t>
         </is>
       </c>
     </row>
@@ -9581,22 +9581,22 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/shelf_arrow.png</t>
+          <t xml:space="preserve">ui/live_door.png</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154×161</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.shelf.arrow</t>
+          <t xml:space="preserve">ui.live.door</t>
         </is>
       </c>
     </row>
@@ -9621,12 +9621,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/live_floors.png</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.live.floors</t>
         </is>
       </c>
     </row>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/live_lantern.png</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">460×568</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.live.lantern</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/live_map.png</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">620×786</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.live.map</t>
         </is>
       </c>
     </row>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/live_noise.png</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.live.noise</t>
         </is>
       </c>
     </row>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion5.png</t>
+          <t xml:space="preserve">ui/live_radio.png</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">220×420</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 무전기</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -9806,47 +9806,47 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion5</t>
+          <t xml:space="preserve">ui.live.radio</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="0">
-        <v>4</v>
-      </c>
-      <c r="B244" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 패널</t>
-        </is>
-      </c>
-      <c r="C244" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/panel_sunken.png</t>
-        </is>
-      </c>
-      <c r="D244" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48×48</t>
-        </is>
-      </c>
-      <c r="E244" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
-        </is>
-      </c>
-      <c r="F244" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
-        </is>
-      </c>
-      <c r="G244" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H244" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.panel.sunken.9s</t>
+      <c r="A244" s="2">
+        <v>4</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_superchat.png</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383×62</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.superchat</t>
         </is>
       </c>
     </row>
@@ -9856,41 +9856,441 @@
       </c>
       <c r="B245" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960×240</t>
+        </is>
+      </c>
+      <c r="E245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2">
+        <v>4</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/revive_record.png</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740×1226</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소생실 사망 기록 서류 — 책상 위 축소본과 확대 리더가 같은 그림을 쓴다</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.revive.record</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0">
+        <v>4</v>
+      </c>
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2">
+        <v>4</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154×161</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.shelf.arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2">
+        <v>4</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2">
+        <v>4</v>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2">
+        <v>4</v>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2">
+        <v>4</v>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2">
+        <v>4</v>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion5.png</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion5</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0">
+        <v>4</v>
+      </c>
+      <c r="B254" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C245" s="0" t="inlineStr">
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/panel_sunken.png</t>
+        </is>
+      </c>
+      <c r="D254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48×48</t>
+        </is>
+      </c>
+      <c r="E254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
+        </is>
+      </c>
+      <c r="F254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
+        </is>
+      </c>
+      <c r="G254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.panel.sunken.9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0">
+        <v>4</v>
+      </c>
+      <c r="B255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 패널</t>
+        </is>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D245" s="0" t="inlineStr">
+      <c r="D255" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E245" s="0" t="inlineStr">
+      <c r="E255" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F245" s="0" t="inlineStr">
+      <c r="F255" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G245" s="0" t="inlineStr">
+      <c r="G255" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H245" s="0" t="inlineStr">
+      <c r="H255" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H245"/>
+  <autoFilter ref="A1:H255"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -7101,12 +7101,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_01.png</t>
+          <t xml:space="preserve">ui/equipment_selected.png</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">275×275</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 1층 채움</t>
+          <t xml:space="preserve">인벤토리 선택 장비 테두리</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.1</t>
+          <t xml:space="preserve">ui.inventory.selected</t>
         </is>
       </c>
     </row>
@@ -7141,12 +7141,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_02.png</t>
+          <t xml:space="preserve">ui/equipment_slot.png</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">231×240</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 2층 채움</t>
+          <t xml:space="preserve">인벤토리 장비 칸 기본 테두리</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.2</t>
+          <t xml:space="preserve">ui.inventory.slot</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_03.png</t>
+          <t xml:space="preserve">ui/floors/floor_01.png</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 3층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 1층 채움</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.3</t>
+          <t xml:space="preserve">ui.live.floors.1</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_04.png</t>
+          <t xml:space="preserve">ui/floors/floor_02.png</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 4층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 2층 채움</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.4</t>
+          <t xml:space="preserve">ui.live.floors.2</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7261,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_05.png</t>
+          <t xml:space="preserve">ui/floors/floor_03.png</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 5층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 3층 채움</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.5</t>
+          <t xml:space="preserve">ui.live.floors.3</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_06.png</t>
+          <t xml:space="preserve">ui/floors/floor_04.png</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 6층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 4층 채움</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.6</t>
+          <t xml:space="preserve">ui.live.floors.4</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_07.png</t>
+          <t xml:space="preserve">ui/floors/floor_05.png</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 7층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 5층 채움</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.7</t>
+          <t xml:space="preserve">ui.live.floors.5</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_08.png</t>
+          <t xml:space="preserve">ui/floors/floor_06.png</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 8층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 6층 채움</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.8</t>
+          <t xml:space="preserve">ui.live.floors.6</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_09.png</t>
+          <t xml:space="preserve">ui/floors/floor_07.png</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 9층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 7층 채움</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.9</t>
+          <t xml:space="preserve">ui.live.floors.7</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_10.png</t>
+          <t xml:space="preserve">ui/floors/floor_08.png</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 10층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 8층 채움</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.10</t>
+          <t xml:space="preserve">ui.live.floors.8</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_11.png</t>
+          <t xml:space="preserve">ui/floors/floor_09.png</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 11층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 9층 채움</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.11</t>
+          <t xml:space="preserve">ui.live.floors.9</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_12.png</t>
+          <t xml:space="preserve">ui/floors/floor_10.png</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 12층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 10층 채움</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.12</t>
+          <t xml:space="preserve">ui.live.floors.10</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_13.png</t>
+          <t xml:space="preserve">ui/floors/floor_11.png</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 13층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 11층 채움</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.13</t>
+          <t xml:space="preserve">ui.live.floors.11</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_14.png</t>
+          <t xml:space="preserve">ui/floors/floor_12.png</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 14층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 12층 채움</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.14</t>
+          <t xml:space="preserve">ui.live.floors.12</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_15.png</t>
+          <t xml:space="preserve">ui/floors/floor_13.png</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 15층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 13층 채움</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.15</t>
+          <t xml:space="preserve">ui.live.floors.13</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_16.png</t>
+          <t xml:space="preserve">ui/floors/floor_14.png</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 16층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 14층 채움</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.16</t>
+          <t xml:space="preserve">ui.live.floors.14</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_17.png</t>
+          <t xml:space="preserve">ui/floors/floor_15.png</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 17층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 15층 채움</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.17</t>
+          <t xml:space="preserve">ui.live.floors.15</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_18.png</t>
+          <t xml:space="preserve">ui/floors/floor_16.png</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 18층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 16층 채움</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.18</t>
+          <t xml:space="preserve">ui.live.floors.16</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_19.png</t>
+          <t xml:space="preserve">ui/floors/floor_17.png</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 19층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 17층 채움</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.19</t>
+          <t xml:space="preserve">ui.live.floors.17</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_20.png</t>
+          <t xml:space="preserve">ui/floors/floor_18.png</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 20층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 18층 채움</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.20</t>
+          <t xml:space="preserve">ui.live.floors.18</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_21.png</t>
+          <t xml:space="preserve">ui/floors/floor_19.png</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 21층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 19층 채움</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.21</t>
+          <t xml:space="preserve">ui.live.floors.19</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_22.png</t>
+          <t xml:space="preserve">ui/floors/floor_20.png</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 22층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 20층 채움</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.22</t>
+          <t xml:space="preserve">ui.live.floors.20</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_23.png</t>
+          <t xml:space="preserve">ui/floors/floor_21.png</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 23층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 21층 채움</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.23</t>
+          <t xml:space="preserve">ui.live.floors.21</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_24.png</t>
+          <t xml:space="preserve">ui/floors/floor_22.png</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 24층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 22층 채움</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.24</t>
+          <t xml:space="preserve">ui.live.floors.22</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_25.png</t>
+          <t xml:space="preserve">ui/floors/floor_23.png</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 25층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 23층 채움</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.25</t>
+          <t xml:space="preserve">ui.live.floors.23</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_26.png</t>
+          <t xml:space="preserve">ui/floors/floor_24.png</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 26층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 24층 채움</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.26</t>
+          <t xml:space="preserve">ui.live.floors.24</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_27.png</t>
+          <t xml:space="preserve">ui/floors/floor_25.png</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 27층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 25층 채움</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.27</t>
+          <t xml:space="preserve">ui.live.floors.25</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_28.png</t>
+          <t xml:space="preserve">ui/floors/floor_26.png</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 28층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 26층 채움</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.28</t>
+          <t xml:space="preserve">ui.live.floors.26</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_29.png</t>
+          <t xml:space="preserve">ui/floors/floor_27.png</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 29층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 27층 채움</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.29</t>
+          <t xml:space="preserve">ui.live.floors.27</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_30.png</t>
+          <t xml:space="preserve">ui/floors/floor_28.png</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 30층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 28층 채움</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.30</t>
+          <t xml:space="preserve">ui.live.floors.28</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_31.png</t>
+          <t xml:space="preserve">ui/floors/floor_29.png</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 31층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 29층 채움</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.31</t>
+          <t xml:space="preserve">ui.live.floors.29</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_32.png</t>
+          <t xml:space="preserve">ui/floors/floor_30.png</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 32층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 30층 채움</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.32</t>
+          <t xml:space="preserve">ui.live.floors.30</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_33.png</t>
+          <t xml:space="preserve">ui/floors/floor_31.png</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 33층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 31층 채움</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.33</t>
+          <t xml:space="preserve">ui.live.floors.31</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_34.png</t>
+          <t xml:space="preserve">ui/floors/floor_32.png</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 34층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 32층 채움</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.34</t>
+          <t xml:space="preserve">ui.live.floors.32</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_35.png</t>
+          <t xml:space="preserve">ui/floors/floor_33.png</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 35층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 33층 채움</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.35</t>
+          <t xml:space="preserve">ui.live.floors.33</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_36.png</t>
+          <t xml:space="preserve">ui/floors/floor_34.png</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 36층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 34층 채움</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.36</t>
+          <t xml:space="preserve">ui.live.floors.34</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_37.png</t>
+          <t xml:space="preserve">ui/floors/floor_35.png</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 37층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 35층 채움</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.37</t>
+          <t xml:space="preserve">ui.live.floors.35</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_38.png</t>
+          <t xml:space="preserve">ui/floors/floor_36.png</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 38층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 36층 채움</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.38</t>
+          <t xml:space="preserve">ui.live.floors.36</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_39.png</t>
+          <t xml:space="preserve">ui/floors/floor_37.png</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 39층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 37층 채움</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.39</t>
+          <t xml:space="preserve">ui.live.floors.37</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_40.png</t>
+          <t xml:space="preserve">ui/floors/floor_38.png</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 40층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 38층 채움</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.40</t>
+          <t xml:space="preserve">ui.live.floors.38</t>
         </is>
       </c>
     </row>
@@ -8701,12 +8701,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/fx_shield.png</t>
+          <t xml:space="preserve">ui/floors/floor_39.png</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680×420</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방어 연출 — 방패 막기 15프레임, 방어 선택 시 1회 재생</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 39층 채움</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.fx.shield</t>
+          <t xml:space="preserve">ui.live.floors.39</t>
         </is>
       </c>
     </row>
@@ -8741,12 +8741,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/fx_sword.png</t>
+          <t xml:space="preserve">ui/floors/floor_40.png</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×480</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 공격 연출 — 칼 슬래시 10프레임, 공격 선택 시 1회 재생</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 40층 채움</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.fx.sword</t>
+          <t xml:space="preserve">ui.live.floors.40</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">ui/fx_shield.png</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">1680×420</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">③ 방어 연출 — 방패 막기 15프레임, 방어 선택 시 1회 재생</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">ui.live.fx.shield</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
+          <t xml:space="preserve">ui/fx_sword.png</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×144</t>
+          <t xml:space="preserve">1920×480</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+          <t xml:space="preserve">③ 공격 연출 — 칼 슬래시 10프레임, 공격 선택 시 1회 재생</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+          <t xml:space="preserve">ui.live.fx.sword</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">ui/hud_status.png</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">700×144</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">ui.hud.status</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">ui/hud_tools.png</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">740×144</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">ui.hud.tools</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">ui.icon.help.hover</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">ui/icon_help.png</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">ui.icon.help</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">ui.icon.options.hover</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">ui/icon_options.png</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">ui.icon.options</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452×831</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+          <t xml:space="preserve">ui.icon.save.hover</t>
         </is>
       </c>
     </row>
@@ -9141,12 +9141,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">ui/icon_save.png</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">ui.icon.save</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
+          <t xml:space="preserve">ui/inventory_window.png</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×302</t>
+          <t xml:space="preserve">1452×831</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+          <t xml:space="preserve">ui.inventory.window</t>
         </is>
       </c>
     </row>
@@ -9221,12 +9221,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">536×94</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">536×302</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
         </is>
       </c>
     </row>
@@ -9301,12 +9301,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">ui/item_info_section.png</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">536×238</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">ui.inventory.info.section</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9341,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">536×177</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_selected.png</t>
+          <t xml:space="preserve">ui/item_info_top.png</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×240</t>
+          <t xml:space="preserve">536×318</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 프레임 (우측 하단 없음)</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">ui.inventory.info.top</t>
         </is>
       </c>
     </row>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">ui/item_info_window.png</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">536×1129</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">장비 상세 정보창</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">ui.inventory.info</t>
         </is>
       </c>
     </row>
@@ -9461,12 +9461,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">ui/live_badge.png</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">206×74</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">③ LIVE 표시</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">ui.live.badge</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">ui/live_blink.png</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">26×28</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">ui.live.blink</t>
         </is>
       </c>
     </row>
@@ -9541,12 +9541,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">ui/live_chat.png</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">424×298</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">ui.live.chat</t>
         </is>
       </c>
     </row>
@@ -9581,12 +9581,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">1040×200</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">ui.live.dialogue</t>
         </is>
       </c>
     </row>
@@ -9621,12 +9621,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">ui/live_door.png</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">ui.live.door</t>
         </is>
       </c>
     </row>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">ui/live_floors.png</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">ui.live.floors</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">ui/live_lantern.png</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">460×568</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">ui.live.lantern</t>
         </is>
       </c>
     </row>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">ui/live_map.png</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">620×786</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">ui.live.map</t>
         </is>
       </c>
     </row>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">ui/live_noise.png</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">ui.live.noise</t>
         </is>
       </c>
     </row>
@@ -9821,72 +9821,72 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/live_radio.png</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220×420</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 무전기</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2">
+        <v>4</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/live_superchat.png</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">383×62</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.live.superchat</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="0">
-        <v>4</v>
-      </c>
-      <c r="B245" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C245" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/logo.png</t>
-        </is>
-      </c>
-      <c r="D245" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960×240</t>
-        </is>
-      </c>
-      <c r="E245" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F245" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타이틀 로고</t>
-        </is>
-      </c>
-      <c r="G245" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H245" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.logo</t>
         </is>
       </c>
     </row>
@@ -9901,112 +9901,112 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890×756</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2">
+        <v>4</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/revive_record.png</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">740×1226</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">소생실 사망 기록 서류 — 책상 위 축소본과 확대 리더가 같은 그림을 쓴다</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.revive.record</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="0">
-        <v>4</v>
-      </c>
-      <c r="B247" s="0" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="0">
+        <v>4</v>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C247" s="0" t="inlineStr">
+      <c r="C248" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/seal.png</t>
         </is>
       </c>
-      <c r="D247" s="0" t="inlineStr">
+      <c r="D248" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">768×192</t>
         </is>
       </c>
-      <c r="E247" s="0" t="inlineStr">
+      <c r="E248" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
         </is>
       </c>
-      <c r="F247" s="0" t="inlineStr">
+      <c r="F248" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">봉랍 도장 4프레임</t>
         </is>
       </c>
-      <c r="G247" s="0" t="inlineStr">
+      <c r="G248" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H247" s="0" t="inlineStr">
+      <c r="H248" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.seal</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2">
-        <v>4</v>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/shelf_arrow.png</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154×161</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정확히 1/2 (77x80)</t>
-        </is>
-      </c>
-      <c r="F248" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
-        </is>
-      </c>
-      <c r="G248" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H248" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.shelf.arrow</t>
         </is>
       </c>
     </row>
@@ -10021,22 +10021,22 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">154×161</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.shelf.arrow</t>
         </is>
       </c>
     </row>
@@ -10061,12 +10061,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/stats_sheet.png</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">705×891</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">Submitted hero descent estimate and stat sheet</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.stats.sheet</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/suspicion1.png</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.suspicion1</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/suspicion2.png</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.suspicion2</t>
         </is>
       </c>
     </row>
@@ -10181,116 +10181,196 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2">
+        <v>4</v>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2">
+        <v>4</v>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/suspicion5.png</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×128</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.suspicion5</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="0">
-        <v>4</v>
-      </c>
-      <c r="B254" s="0" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="0">
+        <v>4</v>
+      </c>
+      <c r="B256" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C254" s="0" t="inlineStr">
+      <c r="C256" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D254" s="0" t="inlineStr">
+      <c r="D256" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E254" s="0" t="inlineStr">
+      <c r="E256" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F254" s="0" t="inlineStr">
+      <c r="F256" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G254" s="0" t="inlineStr">
+      <c r="G256" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H254" s="0" t="inlineStr">
+      <c r="H256" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="0">
-        <v>4</v>
-      </c>
-      <c r="B255" s="0" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="0">
+        <v>4</v>
+      </c>
+      <c r="B257" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C255" s="0" t="inlineStr">
+      <c r="C257" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D255" s="0" t="inlineStr">
+      <c r="D257" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E255" s="0" t="inlineStr">
+      <c r="E257" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F255" s="0" t="inlineStr">
+      <c r="F257" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G255" s="0" t="inlineStr">
+      <c r="G257" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H255" s="0" t="inlineStr">
+      <c r="H257" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H255"/>
+  <autoFilter ref="A1:H257"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/fork.mp3</t>
+          <t xml:space="preserve">sfx/flame_cast.mp3</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">무전 — 갈림길에서 문을 열었다 (사운드V4)</t>
+          <t xml:space="preserve">전투 — 화염 적 공격 (사운드V4)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.radio.fork</t>
+          <t xml:space="preserve">sfx.combat.flameCast</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/guard.mp3</t>
+          <t xml:space="preserve">sfx/flame_hit.mp3</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 — 막았다 (사운드V4)</t>
+          <t xml:space="preserve">전투 — 화염 적 피격 (사운드V4)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.combat.guard</t>
+          <t xml:space="preserve">sfx.combat.flameHit</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/hit.mp3</t>
+          <t xml:space="preserve">sfx/fork.mp3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 — 적의 반격이 들어왔다 (사운드V4 · 공격_혹)</t>
+          <t xml:space="preserve">무전 — 갈림길에서 문을 열었다 (사운드V4)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.combat.hit</t>
+          <t xml:space="preserve">sfx.radio.fork</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/item_drop_heavy.mp3</t>
+          <t xml:space="preserve">sfx/guard_block.mp3</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비를 진열대에 놓는 무거운 금속음</t>
+          <t xml:space="preserve">전투 — 방패로 막았다 (사운드V4)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.item.drop.heavy</t>
+          <t xml:space="preserve">sfx.combat.guardBlock</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/item_drop_light.mp3</t>
+          <t xml:space="preserve">sfx/guard.mp3</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">물약·유물을 진열대에 놓는 가벼운 금속음</t>
+          <t xml:space="preserve">전투 — 막았다 (사운드V4)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.item.drop.light</t>
+          <t xml:space="preserve">sfx.combat.guard</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/item_drop.mp3</t>
+          <t xml:space="preserve">sfx/hit.mp3</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비를 진열대에 놓는다 (사운드V4 · 물건드랍_중간 철)</t>
+          <t xml:space="preserve">전투 — 적의 반격이 들어왔다 (사운드V4 · 공격_혹)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.item.drop</t>
+          <t xml:space="preserve">sfx.combat.hit</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/item_pick.mp3</t>
+          <t xml:space="preserve">sfx/item_drop_heavy.mp3</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비를 집어 든다 (사운드V4 · 버튼 뽑)</t>
+          <t xml:space="preserve">장비를 진열대에 놓는 무거운 금속음</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.item.pick</t>
+          <t xml:space="preserve">sfx.item.drop.heavy</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/office_walk.mp3</t>
+          <t xml:space="preserve">sfx/item_drop_light.mp3</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 용사의 입·퇴장 걸음</t>
+          <t xml:space="preserve">물약·유물을 진열대에 놓는 가벼운 금속음</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.office.walk</t>
+          <t xml:space="preserve">sfx.item.drop.light</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/potion.mp3</t>
+          <t xml:space="preserve">sfx/item_drop.mp3</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 — 물약을 마신다 (사운드V4 · 포션먹음이)</t>
+          <t xml:space="preserve">장비를 진열대에 놓는다 (사운드V4 · 물건드랍_중간 철)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.potion</t>
+          <t xml:space="preserve">sfx.item.drop</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/record.mp3</t>
+          <t xml:space="preserve">sfx/item_pick.mp3</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신기록 갱신</t>
+          <t xml:space="preserve">장비를 집어 든다 (사운드V4 · 버튼 뽑)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.record</t>
+          <t xml:space="preserve">sfx.item.pick</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive_knock.mp3</t>
+          <t xml:space="preserve">sfx/monster_death.mp3</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
+          <t xml:space="preserve">전투 — 몬스터 사망 (사운드V4)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive.knock</t>
+          <t xml:space="preserve">sfx.combat.monsterDeath</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/revive.mp3</t>
+          <t xml:space="preserve">sfx/monster_hit.wav</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
+          <t xml:space="preserve">전투 — 몬스터 피격 (사운드V4 · Wet_blood_splatter, 앞뒤 무음 제거)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.revive</t>
+          <t xml:space="preserve">sfx.combat.monsterHit</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/signal_back.mp3</t>
+          <t xml:space="preserve">sfx/monster_spawn.mp3</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">방송 개시 — 끊겼던 신호가 돌아온다 (사운드V4 · 방송사고_끝)</t>
+          <t xml:space="preserve">전투 — 몬스터 등장 (사운드V4)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.signal.back</t>
+          <t xml:space="preserve">sfx.combat.monsterSpawn</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/stamp.mp3</t>
+          <t xml:space="preserve">sfx/newspaper_rustle.wav</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
+          <t xml:space="preserve">Newspaper friction while dragging</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.stamp</t>
+          <t xml:space="preserve">sfx.newspaper.rustle</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/superchat.mp3</t>
+          <t xml:space="preserve">sfx/newspaper_turn.wav</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">슈퍼챗 알림 (사운드V4 · 전용 효과음)</t>
+          <t xml:space="preserve">Newspaper page turn once fully opened</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.superchat</t>
+          <t xml:space="preserve">sfx.newspaper.turn</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text_female.wav</t>
+          <t xml:space="preserve">sfx/office_walk.mp3</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대사 타자음 · 여성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
+          <t xml:space="preserve">편성실 용사의 입·퇴장 걸음</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text.female</t>
+          <t xml:space="preserve">sfx.office.walk</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text_male.wav</t>
+          <t xml:space="preserve">sfx/potion.mp3</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대사 타자음 · 남성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
+          <t xml:space="preserve">전투 — 물약을 마신다 (사운드V4 · 포션먹음이)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text.male</t>
+          <t xml:space="preserve">sfx.potion</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/text.mp3</t>
+          <t xml:space="preserve">sfx/record.mp3</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
+          <t xml:space="preserve">신기록 갱신</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.text</t>
+          <t xml:space="preserve">sfx.record</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_chime.mp3</t>
+          <t xml:space="preserve">sfx/revive_knock.mp3</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
+          <t xml:space="preserve">빈 소생실에서 2초 뒤 들리는 편성실 쪽 노크</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.chime</t>
+          <t xml:space="preserve">sfx.revive.knock</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx/title_door.mp3</t>
+          <t xml:space="preserve">sfx/revive.mp3</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
+          <t xml:space="preserve">소생 — 수조에서 몸이 일어난다</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sfx.title.door</t>
+          <t xml:space="preserve">sfx.revive</t>
         </is>
       </c>
     </row>
@@ -3696,17 +3696,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/contract_stamp.png</t>
+          <t xml:space="preserve">sfx/signal_back.mp3</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179×178</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 우측 하단에 찍는 확정 도장</t>
+          <t xml:space="preserve">방송 개시 — 끊겼던 신호가 돌아온다 (사운드V4 · 방송사고_끝)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.contract.stamp</t>
+          <t xml:space="preserve">sfx.signal.back</t>
         </is>
       </c>
     </row>
@@ -3736,17 +3736,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/lamp.png</t>
+          <t xml:space="preserve">sfx/stamp.mp3</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224×352</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 실제 석유 램프</t>
+          <t xml:space="preserve">봉랍 도장 — 검시 판정·폐기 확정</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.lamp</t>
+          <t xml:space="preserve">sfx.stamp</t>
         </is>
       </c>
     </row>
@@ -3776,17 +3776,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/ledger.png</t>
+          <t xml:space="preserve">sfx/superchat.mp3</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336×264</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 출연자 서류철</t>
+          <t xml:space="preserve">슈퍼챗 알림 (사운드V4 · 전용 효과음)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.ledger</t>
+          <t xml:space="preserve">sfx.superchat</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/revive_stamp_a.png</t>
+          <t xml:space="preserve">sfx/text_female.wav</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412×424</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 A</t>
+          <t xml:space="preserve">대사 타자음 · 여성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.revive.stamp.a</t>
+          <t xml:space="preserve">sfx.text.female</t>
         </is>
       </c>
     </row>
@@ -3856,17 +3856,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/revive_stamp_b.png</t>
+          <t xml:space="preserve">sfx/text_male.wav</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×420</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 B</t>
+          <t xml:space="preserve">대사 타자음 · 남성 — 원본의 반복 중 한 방만 잘라 낸 90ms (tools/cut-sfx.mjs)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.revive.stamp.b</t>
+          <t xml:space="preserve">sfx.text.male</t>
         </is>
       </c>
     </row>
@@ -3896,17 +3896,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/revive_stamp_c.png</t>
+          <t xml:space="preserve">sfx/text.mp3</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380×408</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 C</t>
+          <t xml:space="preserve">생방송 채팅이 들어올 때의 낮은 텍스트 틱</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.revive.stamp.c</t>
+          <t xml:space="preserve">sfx.text</t>
         </is>
       </c>
     </row>
@@ -3936,17 +3936,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/revive_stamp_f.png</t>
+          <t xml:space="preserve">sfx/title_chime.mp3</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">396×404</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 F (훼손)</t>
+          <t xml:space="preserve">타이틀의 새 게임: 띠링</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.revive.stamp.f</t>
+          <t xml:space="preserve">sfx.title.chime</t>
         </is>
       </c>
     </row>
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소품</t>
+          <t xml:space="preserve">소리</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/revive_stamp_s.png</t>
+          <t xml:space="preserve">sfx/title_door.mp3</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">404×420</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 S (온전)</t>
+          <t xml:space="preserve">타이틀의 새 게임: 가게 문이 열리는 소리 (앞 2초)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.revive.stamp.s</t>
+          <t xml:space="preserve">sfx.title.door</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/scroll.png</t>
+          <t xml:space="preserve">prop/contract_stamp.png</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176×64</t>
+          <t xml:space="preserve">179×178</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서 서류 조각</t>
+          <t xml:space="preserve">계약서 우측 하단에 찍는 확정 도장</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.scroll</t>
+          <t xml:space="preserve">prop.contract.stamp</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/stamp.png</t>
+          <t xml:space="preserve">prop/lamp.png</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128×208</t>
+          <t xml:space="preserve">224×352</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
+          <t xml:space="preserve">작업대의 실제 석유 램프</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.stamp</t>
+          <t xml:space="preserve">prop.lamp</t>
         </is>
       </c>
     </row>
@@ -4101,12 +4101,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tag.png</t>
+          <t xml:space="preserve">prop/ledger.png</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152×104</t>
+          <t xml:space="preserve">336×264</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대의 가격표</t>
+          <t xml:space="preserve">작업대의 출연자 서류철</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tag</t>
+          <t xml:space="preserve">prop.ledger</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tv_live_hover.png</t>
+          <t xml:space="preserve">prop/revive_stamp_a.png</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228×216</t>
+          <t xml:space="preserve">412×424</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">방송 시작 TV의 마우스 오버 상태</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 A</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tv.live.hover</t>
+          <t xml:space="preserve">prop.revive.stamp.a</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tv_live.png</t>
+          <t xml:space="preserve">prop/revive_stamp_b.png</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219×202</t>
+          <t xml:space="preserve">424×420</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약 확정 뒤 방송을 시작할 수 있는 TV</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 B</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tv.live</t>
+          <t xml:space="preserve">prop.revive.stamp.b</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop/tv.png</t>
+          <t xml:space="preserve">prop/revive_stamp_c.png</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219×202</t>
+          <t xml:space="preserve">380×408</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 용사 배경의 왼쪽 상자 위 브라운관 TV</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 C</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prop.tv</t>
+          <t xml:space="preserve">prop.revive.stamp.c</t>
         </is>
       </c>
     </row>
@@ -4256,27 +4256,27 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_ilan.png</t>
+          <t xml:space="preserve">prop/revive_stamp_f.png</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780×1215</t>
+          <t xml:space="preserve">396×404</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미레(마법사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 F (훼손)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.ilan</t>
+          <t xml:space="preserve">prop.revive.stamp.f</t>
         </is>
       </c>
     </row>
@@ -4296,27 +4296,27 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_juno.png</t>
+          <t xml:space="preserve">prop/revive_stamp_s.png</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780×1215</t>
+          <t xml:space="preserve">404×420</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">펜로(궁수) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">소생실 서류 도장 — 시체 상태 등급 S (온전)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.juno</t>
+          <t xml:space="preserve">prop.revive.stamp.s</t>
         </is>
       </c>
     </row>
@@ -4336,27 +4336,27 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_karin.png</t>
+          <t xml:space="preserve">prop/scroll.png</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780×1215</t>
+          <t xml:space="preserve">176×64</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">노일(검사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">계약서 서류 조각</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.karin</t>
+          <t xml:space="preserve">prop.scroll</t>
         </is>
       </c>
     </row>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_mor.png</t>
+          <t xml:space="preserve">prop/stamp.png</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1779×1215</t>
+          <t xml:space="preserve">128×208</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">헤일(힐러) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">최종 판정서에서 잘라낸 실물 도장</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.mor</t>
+          <t xml:space="preserve">prop.stamp</t>
         </is>
       </c>
     </row>
@@ -4416,27 +4416,27 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/corpse_sela.png</t>
+          <t xml:space="preserve">prop/tag.png</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780×1215</t>
+          <t xml:space="preserve">152×104</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">녹스(도적) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
+          <t xml:space="preserve">작업대의 가격표</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.corpse.sela</t>
+          <t xml:space="preserve">prop.tag</t>
         </is>
       </c>
     </row>
@@ -4456,17 +4456,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
+          <t xml:space="preserve">prop/tv_live_hover.png</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">228×216</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
+          <t xml:space="preserve">방송 시작 TV의 마우스 오버 상태</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.angry</t>
+          <t xml:space="preserve">prop.tv.live.hover</t>
         </is>
       </c>
     </row>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
+          <t xml:space="preserve">prop/tv_live.png</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">219×202</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
+          <t xml:space="preserve">계약 확정 뒤 방송을 시작할 수 있는 TV</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blank</t>
+          <t xml:space="preserve">prop.tv.live</t>
         </is>
       </c>
     </row>
@@ -4536,17 +4536,17 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">소품</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
+          <t xml:space="preserve">prop/tv.png</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">219×202</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
+          <t xml:space="preserve">편성실 용사 배경의 왼쪽 상자 위 브라운관 TV</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.blush</t>
+          <t xml:space="preserve">prop.tv</t>
         </is>
       </c>
     </row>
@@ -4576,17 +4576,17 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">오프닝 스토리</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
+          <t xml:space="preserve">story/ch1.png</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1686×948</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
+          <t xml:space="preserve">오프닝 1장 · 세계</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.empty</t>
+          <t xml:space="preserve">story.ch1</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">오프닝 스토리</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
+          <t xml:space="preserve">story/ch2.png</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1688×949</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
+          <t xml:space="preserve">오프닝 2장 · 영생</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.neutral</t>
+          <t xml:space="preserve">story.ch2</t>
         </is>
       </c>
     </row>
@@ -4656,17 +4656,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">오프닝 스토리</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
+          <t xml:space="preserve">story/ch3.png</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1689×950</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
+          <t xml:space="preserve">오프닝 3장 · 지루해진 죽음</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.pain</t>
+          <t xml:space="preserve">story.ch3</t>
         </is>
       </c>
     </row>
@@ -4696,17 +4696,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">오프닝 스토리</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
+          <t xml:space="preserve">story/ch4.png</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1688×949</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
+          <t xml:space="preserve">오프닝 4장 · 방송</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.sad</t>
+          <t xml:space="preserve">story.ch4</t>
         </is>
       </c>
     </row>
@@ -4736,17 +4736,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">오프닝 스토리</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
+          <t xml:space="preserve">story/ch5.png</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1689×949</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
+          <t xml:space="preserve">오프닝 5장 · 회수</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.smile</t>
+          <t xml:space="preserve">story.ch5</t>
         </is>
       </c>
     </row>
@@ -4776,17 +4776,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">오프닝 스토리</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
+          <t xml:space="preserve">story/ch6.png</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1688×949</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
+          <t xml:space="preserve">오프닝 6장 · 가게</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan.surprise</t>
+          <t xml:space="preserve">story.ch6</t>
         </is>
       </c>
     </row>
@@ -4816,17 +4816,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캐릭터 · 기타</t>
+          <t xml:space="preserve">오프닝 스토리</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_angry.png</t>
+          <t xml:space="preserve">story/ch7.png</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1689×949</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno angry 대사 표정 전신</t>
+          <t xml:space="preserve">오프닝 7장 · 주인</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.angry</t>
+          <t xml:space="preserve">story.ch7</t>
         </is>
       </c>
     </row>
@@ -4861,22 +4861,22 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blank.png</t>
+          <t xml:space="preserve">star/corpse_ilan.png</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blank 대사 표정 전신</t>
+          <t xml:space="preserve">미레(마법사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blank</t>
+          <t xml:space="preserve">star.corpse.ilan</t>
         </is>
       </c>
     </row>
@@ -4901,22 +4901,22 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_blush.png</t>
+          <t xml:space="preserve">star/corpse_juno.png</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno blush 대사 표정 전신</t>
+          <t xml:space="preserve">펜로(궁수) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.blush</t>
+          <t xml:space="preserve">star.corpse.juno</t>
         </is>
       </c>
     </row>
@@ -4941,22 +4941,22 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_empty.png</t>
+          <t xml:space="preserve">star/corpse_karin.png</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno empty 대사 표정 전신</t>
+          <t xml:space="preserve">노일(검사) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.empty</t>
+          <t xml:space="preserve">star.corpse.karin</t>
         </is>
       </c>
     </row>
@@ -4981,22 +4981,22 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
+          <t xml:space="preserve">star/corpse_mor.png</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1779×1215</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
+          <t xml:space="preserve">헤일(힐러) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.neutral</t>
+          <t xml:space="preserve">star.corpse.mor</t>
         </is>
       </c>
     </row>
@@ -5021,22 +5021,22 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_pain.png</t>
+          <t xml:space="preserve">star/corpse_sela.png</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752×792</t>
+          <t xml:space="preserve">1780×1215</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">작업대 칸(1160x792)을 채운다</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno pain 대사 표정 전신</t>
+          <t xml:space="preserve">녹스(도적) 시체 연출 — ① 소생실 작업대. 시체가 있을 때만 배경 대신 깔린다</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.pain</t>
+          <t xml:space="preserve">star.corpse.sela</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_sad.png</t>
+          <t xml:space="preserve">star/expressions/ilan_angry.png</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno sad 대사 표정 전신</t>
+          <t xml:space="preserve">ilan angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.sad</t>
+          <t xml:space="preserve">star.expression.ilan.angry</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_smile.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blank.png</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno smile 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.smile</t>
+          <t xml:space="preserve">star.expression.ilan.blank</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
+          <t xml:space="preserve">star/expressions/ilan_blush.png</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
+          <t xml:space="preserve">ilan blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno.surprise</t>
+          <t xml:space="preserve">star.expression.ilan.blush</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_angry.png</t>
+          <t xml:space="preserve">star/expressions/ilan_empty.png</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin angry 대사 표정 전신</t>
+          <t xml:space="preserve">ilan empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.angry</t>
+          <t xml:space="preserve">star.expression.ilan.empty</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blank.png</t>
+          <t xml:space="preserve">star/expressions/ilan_neutral.png</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blank 대사 표정 전신</t>
+          <t xml:space="preserve">ilan neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blank</t>
+          <t xml:space="preserve">star.expression.ilan.neutral</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_blush.png</t>
+          <t xml:space="preserve">star/expressions/ilan_pain.png</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin blush 대사 표정 전신</t>
+          <t xml:space="preserve">ilan pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.blush</t>
+          <t xml:space="preserve">star.expression.ilan.pain</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_empty.png</t>
+          <t xml:space="preserve">star/expressions/ilan_sad.png</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin empty 대사 표정 전신</t>
+          <t xml:space="preserve">ilan sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.empty</t>
+          <t xml:space="preserve">star.expression.ilan.sad</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
+          <t xml:space="preserve">star/expressions/ilan_smile.png</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
+          <t xml:space="preserve">ilan smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.neutral</t>
+          <t xml:space="preserve">star.expression.ilan.smile</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_pain.png</t>
+          <t xml:space="preserve">star/expressions/ilan_surprise.png</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin pain 대사 표정 전신</t>
+          <t xml:space="preserve">ilan surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.pain</t>
+          <t xml:space="preserve">star.expression.ilan.surprise</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_sad.png</t>
+          <t xml:space="preserve">star/expressions/juno_angry.png</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin sad 대사 표정 전신</t>
+          <t xml:space="preserve">juno angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.sad</t>
+          <t xml:space="preserve">star.expression.juno.angry</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_smile.png</t>
+          <t xml:space="preserve">star/expressions/juno_blank.png</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin smile 대사 표정 전신</t>
+          <t xml:space="preserve">juno blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.smile</t>
+          <t xml:space="preserve">star.expression.juno.blank</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
+          <t xml:space="preserve">star/expressions/juno_blush.png</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
+          <t xml:space="preserve">juno blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin.surprise</t>
+          <t xml:space="preserve">star.expression.juno.blush</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_angry.png</t>
+          <t xml:space="preserve">star/expressions/juno_empty.png</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor angry 대사 표정 전신</t>
+          <t xml:space="preserve">juno empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.angry</t>
+          <t xml:space="preserve">star.expression.juno.empty</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blank.png</t>
+          <t xml:space="preserve">star/expressions/juno_neutral.png</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blank 대사 표정 전신</t>
+          <t xml:space="preserve">juno neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blank</t>
+          <t xml:space="preserve">star.expression.juno.neutral</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_blush.png</t>
+          <t xml:space="preserve">star/expressions/juno_pain.png</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor blush 대사 표정 전신</t>
+          <t xml:space="preserve">juno pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.blush</t>
+          <t xml:space="preserve">star.expression.juno.pain</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_empty.png</t>
+          <t xml:space="preserve">star/expressions/juno_sad.png</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor empty 대사 표정 전신</t>
+          <t xml:space="preserve">juno sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.empty</t>
+          <t xml:space="preserve">star.expression.juno.sad</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
+          <t xml:space="preserve">star/expressions/juno_smile.png</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
+          <t xml:space="preserve">juno smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.neutral</t>
+          <t xml:space="preserve">star.expression.juno.smile</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_pain.png</t>
+          <t xml:space="preserve">star/expressions/juno_surprise.png</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor pain 대사 표정 전신</t>
+          <t xml:space="preserve">juno surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.pain</t>
+          <t xml:space="preserve">star.expression.juno.surprise</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_sad.png</t>
+          <t xml:space="preserve">star/expressions/karin_angry.png</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor sad 대사 표정 전신</t>
+          <t xml:space="preserve">karin angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.sad</t>
+          <t xml:space="preserve">star.expression.karin.angry</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_smile.png</t>
+          <t xml:space="preserve">star/expressions/karin_blank.png</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor smile 대사 표정 전신</t>
+          <t xml:space="preserve">karin blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.smile</t>
+          <t xml:space="preserve">star.expression.karin.blank</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
+          <t xml:space="preserve">star/expressions/karin_blush.png</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
+          <t xml:space="preserve">karin blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor.surprise</t>
+          <t xml:space="preserve">star.expression.karin.blush</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_angry.png</t>
+          <t xml:space="preserve">star/expressions/karin_empty.png</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela angry 대사 표정 전신</t>
+          <t xml:space="preserve">karin empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.angry</t>
+          <t xml:space="preserve">star.expression.karin.empty</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blank.png</t>
+          <t xml:space="preserve">star/expressions/karin_neutral.png</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blank 대사 표정 전신</t>
+          <t xml:space="preserve">karin neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blank</t>
+          <t xml:space="preserve">star.expression.karin.neutral</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_blush.png</t>
+          <t xml:space="preserve">star/expressions/karin_pain.png</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela blush 대사 표정 전신</t>
+          <t xml:space="preserve">karin pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.blush</t>
+          <t xml:space="preserve">star.expression.karin.pain</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_empty.png</t>
+          <t xml:space="preserve">star/expressions/karin_sad.png</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela empty 대사 표정 전신</t>
+          <t xml:space="preserve">karin sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.empty</t>
+          <t xml:space="preserve">star.expression.karin.sad</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
+          <t xml:space="preserve">star/expressions/karin_smile.png</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
+          <t xml:space="preserve">karin smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.neutral</t>
+          <t xml:space="preserve">star.expression.karin.smile</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_pain.png</t>
+          <t xml:space="preserve">star/expressions/karin_surprise.png</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela pain 대사 표정 전신</t>
+          <t xml:space="preserve">karin surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.pain</t>
+          <t xml:space="preserve">star.expression.karin.surprise</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_sad.png</t>
+          <t xml:space="preserve">star/expressions/mor_angry.png</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela sad 대사 표정 전신</t>
+          <t xml:space="preserve">mor angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.sad</t>
+          <t xml:space="preserve">star.expression.mor.angry</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_smile.png</t>
+          <t xml:space="preserve">star/expressions/mor_blank.png</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela smile 대사 표정 전신</t>
+          <t xml:space="preserve">mor blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.smile</t>
+          <t xml:space="preserve">star.expression.mor.blank</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
+          <t xml:space="preserve">star/expressions/mor_blush.png</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
+          <t xml:space="preserve">mor blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela.surprise</t>
+          <t xml:space="preserve">star.expression.mor.blush</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/mor_empty.png</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 대사 전신</t>
+          <t xml:space="preserve">mor empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.ilan</t>
+          <t xml:space="preserve">star.expression.mor.empty</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/ilan_expression.png</t>
+          <t xml:space="preserve">star/expressions/mor_neutral.png</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일란 표정 전신</t>
+          <t xml:space="preserve">mor neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.ilan</t>
+          <t xml:space="preserve">star.expression.mor.neutral</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/mor_pain.png</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 대사 전신</t>
+          <t xml:space="preserve">mor pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.juno</t>
+          <t xml:space="preserve">star.expression.mor.pain</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/juno_expression.png</t>
+          <t xml:space="preserve">star/expressions/mor_sad.png</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
+          <t xml:space="preserve">mor sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.juno</t>
+          <t xml:space="preserve">star.expression.mor.sad</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/mor_smile.png</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 대사 전신</t>
+          <t xml:space="preserve">mor smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.karin</t>
+          <t xml:space="preserve">star.expression.mor.smile</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/karin_expression.png</t>
+          <t xml:space="preserve">star/expressions/mor_surprise.png</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카린 표정 전신</t>
+          <t xml:space="preserve">mor surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.karin</t>
+          <t xml:space="preserve">star.expression.mor.surprise</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_angry.png</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 대사 전신</t>
+          <t xml:space="preserve">sela angry 대사 표정 전신</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.mor</t>
+          <t xml:space="preserve">star.expression.sela.angry</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mor_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_blank.png</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모르 표정 전신</t>
+          <t xml:space="preserve">sela blank 대사 표정 전신</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.mor</t>
+          <t xml:space="preserve">star.expression.sela.blank</t>
         </is>
       </c>
     </row>
@@ -6581,12 +6581,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/ilan.png</t>
+          <t xml:space="preserve">star/expressions/sela_blush.png</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50×60</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ilan 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">sela blush 대사 표정 전신</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.ilan</t>
+          <t xml:space="preserve">star.expression.sela.blush</t>
         </is>
       </c>
     </row>
@@ -6621,12 +6621,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/juno.png</t>
+          <t xml:space="preserve">star/expressions/sela_empty.png</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64×55</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juno 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">sela empty 대사 표정 전신</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.juno</t>
+          <t xml:space="preserve">star.expression.sela.empty</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/karin.png</t>
+          <t xml:space="preserve">star/expressions/sela_neutral.png</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84×57</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">karin 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">sela neutral 대사 표정 전신</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.karin</t>
+          <t xml:space="preserve">star.expression.sela.neutral</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/mor.png</t>
+          <t xml:space="preserve">star/expressions/sela_pain.png</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56×40</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mor 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">sela pain 대사 표정 전신</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.mor</t>
+          <t xml:space="preserve">star.expression.sela.pain</t>
         </is>
       </c>
     </row>
@@ -6741,12 +6741,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/mouth/sela.png</t>
+          <t xml:space="preserve">star/expressions/sela_sad.png</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40×16</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sela 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
+          <t xml:space="preserve">sela sad 대사 표정 전신</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.mouth.sela</t>
+          <t xml:space="preserve">star.expression.sela.sad</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_dialogue.png</t>
+          <t xml:space="preserve">star/expressions/sela_smile.png</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 대사 전신</t>
+          <t xml:space="preserve">sela smile 대사 표정 전신</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.dialogue.sela</t>
+          <t xml:space="preserve">star.expression.sela.smile</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star/sela_expression.png</t>
+          <t xml:space="preserve">star/expressions/sela_surprise.png</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세라 표정 전신</t>
+          <t xml:space="preserve">sela surprise 대사 표정 전신</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -6846,47 +6846,47 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">star.expression.sela</t>
+          <t xml:space="preserve">star.expression.sela.surprise</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="0">
-        <v>4</v>
-      </c>
-      <c r="B170" s="0" t="inlineStr">
+      <c r="A170" s="2">
+        <v>4</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
-      <c r="C170" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star/silhouette.png</t>
-        </is>
-      </c>
-      <c r="D170" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1536×480</t>
-        </is>
-      </c>
-      <c r="E170" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F170" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
-        </is>
-      </c>
-      <c r="G170" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H170" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">star.silhouette</t>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/ilan_dialogue.png</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일란 대사 전신</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.dialogue.ilan</t>
         </is>
       </c>
     </row>
@@ -6896,17 +6896,17 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/character_cover.png</t>
+          <t xml:space="preserve">star/ilan_expression.png</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1087×258</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
+          <t xml:space="preserve">일란 표정 전신</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.guest.cover</t>
+          <t xml:space="preserve">star.expression.ilan</t>
         </is>
       </c>
     </row>
@@ -6936,17 +6936,17 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_hour.png</t>
+          <t xml:space="preserve">star/juno_dialogue.png</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29×42</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock hour hand</t>
+          <t xml:space="preserve">주노 대사 전신</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.hour</t>
+          <t xml:space="preserve">star.dialogue.juno</t>
         </is>
       </c>
     </row>
@@ -6976,17 +6976,17 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/clock_minute.png</t>
+          <t xml:space="preserve">star/juno_expression.png</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8×56</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD game-clock minute hand</t>
+          <t xml:space="preserve">주노 큰웃음 표정 전신</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.clock.minute</t>
+          <t xml:space="preserve">star.expression.juno</t>
         </is>
       </c>
     </row>
@@ -7016,17 +7016,17 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/contract_sheet.png</t>
+          <t xml:space="preserve">star/karin_dialogue.png</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">795×1036</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
+          <t xml:space="preserve">카린 대사 전신</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -7046,47 +7046,47 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.contract.sheet</t>
+          <t xml:space="preserve">star.dialogue.karin</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="0">
-        <v>4</v>
-      </c>
-      <c r="B175" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C175" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/cursor.png</t>
-        </is>
-      </c>
-      <c r="D175" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32×32</t>
-        </is>
-      </c>
-      <c r="E175" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F175" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
-        </is>
-      </c>
-      <c r="G175" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H175" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.cursor</t>
+      <c r="A175" s="2">
+        <v>4</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/karin_expression.png</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752×792</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카린 표정 전신</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.expression.karin</t>
         </is>
       </c>
     </row>
@@ -7096,17 +7096,17 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/equipment_selected.png</t>
+          <t xml:space="preserve">star/mor_dialogue.png</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275×275</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 선택 장비 테두리</t>
+          <t xml:space="preserve">모르 대사 전신</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.selected</t>
+          <t xml:space="preserve">star.dialogue.mor</t>
         </is>
       </c>
     </row>
@@ -7136,17 +7136,17 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/equipment_slot.png</t>
+          <t xml:space="preserve">star/mor_expression.png</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231×240</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인벤토리 장비 칸 기본 테두리</t>
+          <t xml:space="preserve">모르 표정 전신</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.slot</t>
+          <t xml:space="preserve">star.expression.mor</t>
         </is>
       </c>
     </row>
@@ -7176,17 +7176,17 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_01.png</t>
+          <t xml:space="preserve">star/mouth/ilan.png</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">50×60</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 1층 채움</t>
+          <t xml:space="preserve">ilan 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.1</t>
+          <t xml:space="preserve">star.mouth.ilan</t>
         </is>
       </c>
     </row>
@@ -7216,17 +7216,17 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_02.png</t>
+          <t xml:space="preserve">star/mouth/juno.png</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">64×55</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 2층 채움</t>
+          <t xml:space="preserve">juno 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.2</t>
+          <t xml:space="preserve">star.mouth.juno</t>
         </is>
       </c>
     </row>
@@ -7256,17 +7256,17 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_03.png</t>
+          <t xml:space="preserve">star/mouth/karin.png</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">84×57</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 3층 채움</t>
+          <t xml:space="preserve">karin 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.3</t>
+          <t xml:space="preserve">star.mouth.karin</t>
         </is>
       </c>
     </row>
@@ -7296,17 +7296,17 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_04.png</t>
+          <t xml:space="preserve">star/mouth/mor.png</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">56×40</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 4층 채움</t>
+          <t xml:space="preserve">mor 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.4</t>
+          <t xml:space="preserve">star.mouth.mor</t>
         </is>
       </c>
     </row>
@@ -7336,17 +7336,17 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_05.png</t>
+          <t xml:space="preserve">star/mouth/sela.png</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">40×16</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 5층 채움</t>
+          <t xml:space="preserve">sela 말하는 입 — 표정 스프라이트(752x792) 위에 얹는다 (tools/key-white.mjs 로 흰 배경 제거)</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.5</t>
+          <t xml:space="preserve">star.mouth.sela</t>
         </is>
       </c>
     </row>
@@ -7376,17 +7376,17 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_06.png</t>
+          <t xml:space="preserve">star/sela_dialogue.png</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 6층 채움</t>
+          <t xml:space="preserve">세라 대사 전신</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.6</t>
+          <t xml:space="preserve">star.dialogue.sela</t>
         </is>
       </c>
     </row>
@@ -7416,17 +7416,17 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI · 기타</t>
+          <t xml:space="preserve">캐릭터 · 기타</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_07.png</t>
+          <t xml:space="preserve">star/sela_expression.png</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">752×792</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 7층 채움</t>
+          <t xml:space="preserve">세라 표정 전신</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -7446,47 +7446,47 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.7</t>
+          <t xml:space="preserve">star.expression.sela</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2">
-        <v>4</v>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI · 기타</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/floors/floor_08.png</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210×936</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 8층 채움</t>
-        </is>
-      </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.live.floors.8</t>
+      <c r="A185" s="0">
+        <v>4</v>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐릭터 · 기타</t>
+        </is>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star/silhouette.png</t>
+        </is>
+      </c>
+      <c r="D185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536×480</t>
+        </is>
+      </c>
+      <c r="E185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384×480 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 없는 몸 실루엣 4프레임</t>
+        </is>
+      </c>
+      <c r="G185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">star.silhouette</t>
         </is>
       </c>
     </row>
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_09.png</t>
+          <t xml:space="preserve">ui/character_cover.png</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">1087×258</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 9층 채움</t>
+          <t xml:space="preserve">편성실 좌측 캐릭터 전경 가리개 — 대사 배치용</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.9</t>
+          <t xml:space="preserve">ui.guest.cover</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7541,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_10.png</t>
+          <t xml:space="preserve">ui/clock_hour.png</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">29×42</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 10층 채움</t>
+          <t xml:space="preserve">HUD game-clock hour hand</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.10</t>
+          <t xml:space="preserve">ui.clock.hour</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_11.png</t>
+          <t xml:space="preserve">ui/clock_minute.png</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">8×56</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 11층 채움</t>
+          <t xml:space="preserve">HUD game-clock minute hand</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.11</t>
+          <t xml:space="preserve">ui.clock.minute</t>
         </is>
       </c>
     </row>
@@ -7621,12 +7621,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_12.png</t>
+          <t xml:space="preserve">ui/contract_sheet.png</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">795×1036</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 12층 채움</t>
+          <t xml:space="preserve">Submitted hero contract; click its desk copy to inspect</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -7646,47 +7646,47 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.12</t>
+          <t xml:space="preserve">ui.contract.sheet</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2">
-        <v>4</v>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="A190" s="0">
+        <v>4</v>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/floors/floor_13.png</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210×936</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 13층 채움</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.live.floors.13</t>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/cursor.png</t>
+        </is>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32×32</t>
+        </is>
+      </c>
+      <c r="E190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마우스 커서 — 봉랍 도장. 뾰족한 끝이 좌상단(0,0)에 오게 그려라</t>
+        </is>
+      </c>
+      <c r="G190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.cursor</t>
         </is>
       </c>
     </row>
@@ -7701,12 +7701,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_14.png</t>
+          <t xml:space="preserve">ui/equipment_selected.png</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">275×275</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 14층 채움</t>
+          <t xml:space="preserve">인벤토리 선택 장비 테두리</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.14</t>
+          <t xml:space="preserve">ui.inventory.selected</t>
         </is>
       </c>
     </row>
@@ -7741,12 +7741,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_15.png</t>
+          <t xml:space="preserve">ui/equipment_slot.png</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">231×240</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 15층 채움</t>
+          <t xml:space="preserve">인벤토리 장비 칸 기본 테두리</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.15</t>
+          <t xml:space="preserve">ui.inventory.slot</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_16.png</t>
+          <t xml:space="preserve">ui/floors/floor_01.png</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 16층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 1층 채움</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.16</t>
+          <t xml:space="preserve">ui.live.floors.1</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_17.png</t>
+          <t xml:space="preserve">ui/floors/floor_02.png</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 17층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 2층 채움</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.17</t>
+          <t xml:space="preserve">ui.live.floors.2</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_18.png</t>
+          <t xml:space="preserve">ui/floors/floor_03.png</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 18층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 3층 채움</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.18</t>
+          <t xml:space="preserve">ui.live.floors.3</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_19.png</t>
+          <t xml:space="preserve">ui/floors/floor_04.png</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 19층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 4층 채움</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.19</t>
+          <t xml:space="preserve">ui.live.floors.4</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_20.png</t>
+          <t xml:space="preserve">ui/floors/floor_05.png</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 20층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 5층 채움</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.20</t>
+          <t xml:space="preserve">ui.live.floors.5</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_21.png</t>
+          <t xml:space="preserve">ui/floors/floor_06.png</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 21층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 6층 채움</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.21</t>
+          <t xml:space="preserve">ui.live.floors.6</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_22.png</t>
+          <t xml:space="preserve">ui/floors/floor_07.png</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 22층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 7층 채움</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.22</t>
+          <t xml:space="preserve">ui.live.floors.7</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_23.png</t>
+          <t xml:space="preserve">ui/floors/floor_08.png</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 23층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 8층 채움</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.23</t>
+          <t xml:space="preserve">ui.live.floors.8</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_24.png</t>
+          <t xml:space="preserve">ui/floors/floor_09.png</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 24층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 9층 채움</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.24</t>
+          <t xml:space="preserve">ui.live.floors.9</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_25.png</t>
+          <t xml:space="preserve">ui/floors/floor_10.png</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 25층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 10층 채움</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.25</t>
+          <t xml:space="preserve">ui.live.floors.10</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_26.png</t>
+          <t xml:space="preserve">ui/floors/floor_11.png</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 26층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 11층 채움</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.26</t>
+          <t xml:space="preserve">ui.live.floors.11</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_27.png</t>
+          <t xml:space="preserve">ui/floors/floor_12.png</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 27층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 12층 채움</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.27</t>
+          <t xml:space="preserve">ui.live.floors.12</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_28.png</t>
+          <t xml:space="preserve">ui/floors/floor_13.png</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 28층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 13층 채움</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.28</t>
+          <t xml:space="preserve">ui.live.floors.13</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_29.png</t>
+          <t xml:space="preserve">ui/floors/floor_14.png</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 29층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 14층 채움</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.29</t>
+          <t xml:space="preserve">ui.live.floors.14</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_30.png</t>
+          <t xml:space="preserve">ui/floors/floor_15.png</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 30층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 15층 채움</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.30</t>
+          <t xml:space="preserve">ui.live.floors.15</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_31.png</t>
+          <t xml:space="preserve">ui/floors/floor_16.png</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 31층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 16층 채움</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.31</t>
+          <t xml:space="preserve">ui.live.floors.16</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_32.png</t>
+          <t xml:space="preserve">ui/floors/floor_17.png</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 32층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 17층 채움</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.32</t>
+          <t xml:space="preserve">ui.live.floors.17</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_33.png</t>
+          <t xml:space="preserve">ui/floors/floor_18.png</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 33층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 18층 채움</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.33</t>
+          <t xml:space="preserve">ui.live.floors.18</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_34.png</t>
+          <t xml:space="preserve">ui/floors/floor_19.png</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 34층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 19층 채움</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.34</t>
+          <t xml:space="preserve">ui.live.floors.19</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_35.png</t>
+          <t xml:space="preserve">ui/floors/floor_20.png</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 35층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 20층 채움</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.35</t>
+          <t xml:space="preserve">ui.live.floors.20</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_36.png</t>
+          <t xml:space="preserve">ui/floors/floor_21.png</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 36층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 21층 채움</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.36</t>
+          <t xml:space="preserve">ui.live.floors.21</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_37.png</t>
+          <t xml:space="preserve">ui/floors/floor_22.png</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 37층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 22층 채움</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.37</t>
+          <t xml:space="preserve">ui.live.floors.22</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_38.png</t>
+          <t xml:space="preserve">ui/floors/floor_23.png</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 38층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 23층 채움</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.38</t>
+          <t xml:space="preserve">ui.live.floors.23</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_39.png</t>
+          <t xml:space="preserve">ui/floors/floor_24.png</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 39층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 24층 채움</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.39</t>
+          <t xml:space="preserve">ui.live.floors.24</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/floors/floor_40.png</t>
+          <t xml:space="preserve">ui/floors/floor_25.png</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 — 40층 채움</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 25층 채움</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors.40</t>
+          <t xml:space="preserve">ui.live.floors.25</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/fx_shield.png</t>
+          <t xml:space="preserve">ui/floors/floor_26.png</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680×420</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방어 연출 — 방패 막기 15프레임, 방어 선택 시 1회 재생</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 26층 채움</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.fx.shield</t>
+          <t xml:space="preserve">ui.live.floors.26</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/fx_sword.png</t>
+          <t xml:space="preserve">ui/floors/floor_27.png</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920×480</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 공격 연출 — 칼 슬래시 10프레임, 공격 선택 시 1회 재생</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 27층 채움</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.fx.sword</t>
+          <t xml:space="preserve">ui.live.floors.27</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_status.png</t>
+          <t xml:space="preserve">ui/floors/floor_28.png</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700×144</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 28층 채움</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.status</t>
+          <t xml:space="preserve">ui.live.floors.28</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/hud_tools.png</t>
+          <t xml:space="preserve">ui/floors/floor_29.png</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×144</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 29층 채움</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.hud.tools</t>
+          <t xml:space="preserve">ui.live.floors.29</t>
         </is>
       </c>
     </row>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help_hover.png</t>
+          <t xml:space="preserve">ui/floors/floor_30.png</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 30층 채움</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help.hover</t>
+          <t xml:space="preserve">ui.live.floors.30</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_help.png</t>
+          <t xml:space="preserve">ui/floors/floor_31.png</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 31층 채움</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.help</t>
+          <t xml:space="preserve">ui.live.floors.31</t>
         </is>
       </c>
     </row>
@@ -9021,12 +9021,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options_hover.png</t>
+          <t xml:space="preserve">ui/floors/floor_32.png</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 32층 채움</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options.hover</t>
+          <t xml:space="preserve">ui.live.floors.32</t>
         </is>
       </c>
     </row>
@@ -9061,12 +9061,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_options.png</t>
+          <t xml:space="preserve">ui/floors/floor_33.png</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 33층 채움</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.options</t>
+          <t xml:space="preserve">ui.live.floors.33</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save_hover.png</t>
+          <t xml:space="preserve">ui/floors/floor_34.png</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 34층 채움</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save.hover</t>
+          <t xml:space="preserve">ui.live.floors.34</t>
         </is>
       </c>
     </row>
@@ -9141,12 +9141,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/icon_save.png</t>
+          <t xml:space="preserve">ui/floors/floor_35.png</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112×112</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단바 아이콘 · 저장</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 35층 채움</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.icon.save</t>
+          <t xml:space="preserve">ui.live.floors.35</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/inventory_window.png</t>
+          <t xml:space="preserve">ui/floors/floor_36.png</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452×831</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">편성실 인벤토리 창</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 36층 채움</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.window</t>
+          <t xml:space="preserve">ui.live.floors.36</t>
         </is>
       </c>
     </row>
@@ -9221,12 +9221,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_bottom.png</t>
+          <t xml:space="preserve">ui/floors/floor_37.png</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×94</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 37층 채움</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.bottom</t>
+          <t xml:space="preserve">ui.live.floors.37</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_notes.png</t>
+          <t xml:space="preserve">ui/floors/floor_38.png</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×302</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 38층 채움</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.notes</t>
+          <t xml:space="preserve">ui.live.floors.38</t>
         </is>
       </c>
     </row>
@@ -9301,12 +9301,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_section.png</t>
+          <t xml:space="preserve">ui/floors/floor_39.png</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×238</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 39층 채움</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.section</t>
+          <t xml:space="preserve">ui.live.floors.39</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9341,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_stats.png</t>
+          <t xml:space="preserve">ui/floors/floor_40.png</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×177</t>
+          <t xml:space="preserve">210×936</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
+          <t xml:space="preserve">③ 좌측 층계 게이지 — 40층 채움</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.stats</t>
+          <t xml:space="preserve">ui.live.floors.40</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_top.png</t>
+          <t xml:space="preserve">ui/fx_shield.png</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×318</t>
+          <t xml:space="preserve">1680×420</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+          <t xml:space="preserve">③ 방어 연출 — 방패 막기 15프레임, 방어 선택 시 1회 재생</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info.top</t>
+          <t xml:space="preserve">ui.live.fx.shield</t>
         </is>
       </c>
     </row>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/item_info_window.png</t>
+          <t xml:space="preserve">ui/fx_sword.png</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536×1129</t>
+          <t xml:space="preserve">1920×480</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장비 상세 정보창</t>
+          <t xml:space="preserve">③ 공격 연출 — 칼 슬래시 10프레임, 공격 선택 시 1회 재생</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.inventory.info</t>
+          <t xml:space="preserve">ui.live.fx.sword</t>
         </is>
       </c>
     </row>
@@ -9461,12 +9461,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_badge.png</t>
+          <t xml:space="preserve">ui/hud_status.png</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206×74</t>
+          <t xml:space="preserve">700×144</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 표시</t>
+          <t xml:space="preserve">상단바 좌 — DAY·골드·팬·평판 4칸</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.badge</t>
+          <t xml:space="preserve">ui.hud.status</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_blink.png</t>
+          <t xml:space="preserve">ui/hud_tools.png</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26×28</t>
+          <t xml:space="preserve">740×144</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
+          <t xml:space="preserve">상단바 우 — 시계·도달층 게이지</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.blink</t>
+          <t xml:space="preserve">ui.hud.tools</t>
         </is>
       </c>
     </row>
@@ -9541,12 +9541,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_chat.png</t>
+          <t xml:space="preserve">ui/icon_help_hover.png</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424×298</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책) (눌림)</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.chat</t>
+          <t xml:space="preserve">ui.icon.help.hover</t>
         </is>
       </c>
     </row>
@@ -9581,12 +9581,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_dialogue.png</t>
+          <t xml:space="preserve">ui/icon_help.png</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040×200</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
+          <t xml:space="preserve">상단바 아이콘 · 조작 안내(책)</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.dialogue</t>
+          <t xml:space="preserve">ui.icon.help</t>
         </is>
       </c>
     </row>
@@ -9621,12 +9621,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_door.png</t>
+          <t xml:space="preserve">ui/icon_options_hover.png</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니) (눌림)</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.door</t>
+          <t xml:space="preserve">ui.icon.options.hover</t>
         </is>
       </c>
     </row>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_floors.png</t>
+          <t xml:space="preserve">ui/icon_options.png</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210×936</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+          <t xml:space="preserve">상단바 아이콘 · 옵션(톱니)</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.floors</t>
+          <t xml:space="preserve">ui.icon.options</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_lantern.png</t>
+          <t xml:space="preserve">ui/icon_save_hover.png</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460×568</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장 (눌림)</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.lantern</t>
+          <t xml:space="preserve">ui.icon.save.hover</t>
         </is>
       </c>
     </row>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_map.png</t>
+          <t xml:space="preserve">ui/icon_save.png</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620×786</t>
+          <t xml:space="preserve">112×112</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+          <t xml:space="preserve">상단바 아이콘 · 저장</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.map</t>
+          <t xml:space="preserve">ui.icon.save</t>
         </is>
       </c>
     </row>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_noise.png</t>
+          <t xml:space="preserve">ui/inventory_window.png</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182×936</t>
+          <t xml:space="preserve">1452×831</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+          <t xml:space="preserve">편성실 인벤토리 창</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.noise</t>
+          <t xml:space="preserve">ui.inventory.window</t>
         </is>
       </c>
     </row>
@@ -9821,12 +9821,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_radio.png</t>
+          <t xml:space="preserve">ui/item_info_bottom.png</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220×420</t>
+          <t xml:space="preserve">536×94</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 무전기</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 하단 프레임</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.radio</t>
+          <t xml:space="preserve">ui.inventory.info.bottom</t>
         </is>
       </c>
     </row>
@@ -9861,12 +9861,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/live_superchat.png</t>
+          <t xml:space="preserve">ui/item_info_notes.png</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383×62</t>
+          <t xml:space="preserve">536×302</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 긴 기록 구획</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.live.superchat</t>
+          <t xml:space="preserve">ui.inventory.info.notes</t>
         </is>
       </c>
     </row>
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/logo.png</t>
+          <t xml:space="preserve">ui/item_info_section.png</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890×756</t>
+          <t xml:space="preserve">536×238</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀 로고</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 반복 특성 구획</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.logo</t>
+          <t xml:space="preserve">ui.inventory.info.section</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9941,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/revive_record.png</t>
+          <t xml:space="preserve">ui/item_info_stats.png</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×1226</t>
+          <t xml:space="preserve">536×177</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생실 사망 기록 서류 — 책상 위 축소본과 확대 리더가 같은 그림을 쓴다</t>
+          <t xml:space="preserve">가변 장비 정보창 조립용 스탯 구획</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -9966,47 +9966,47 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.revive.record</t>
+          <t xml:space="preserve">ui.inventory.info.stats</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="0">
-        <v>4</v>
-      </c>
-      <c r="B248" s="0" t="inlineStr">
+      <c r="A248" s="2">
+        <v>4</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C248" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D248" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E248" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F248" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G248" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H248" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/item_info_top.png</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536×318</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가변 장비 정보창 조립용 상단 — 이름·등급·아이콘</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.inventory.info.top</t>
         </is>
       </c>
     </row>
@@ -10021,22 +10021,22 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/shelf_arrow.png</t>
+          <t xml:space="preserve">ui/item_info_window.png</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154×161</t>
+          <t xml:space="preserve">536×1129</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+          <t xml:space="preserve">장비 상세 정보창</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.shelf.arrow</t>
+          <t xml:space="preserve">ui.inventory.info</t>
         </is>
       </c>
     </row>
@@ -10061,12 +10061,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/stats_sheet.png</t>
+          <t xml:space="preserve">ui/live_badge.png</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">705×891</t>
+          <t xml:space="preserve">206×74</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submitted hero descent estimate and stat sheet</t>
+          <t xml:space="preserve">③ LIVE 표시</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.stats.sheet</t>
+          <t xml:space="preserve">ui.live.badge</t>
         </is>
       </c>
     </row>
@@ -10101,12 +10101,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/live_blink.png</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">26×28</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ LIVE 붉은 마름모 (깜빡인다)</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.live.blink</t>
         </is>
       </c>
     </row>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/live_chat.png</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">424×298</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 채팅창. 상단 타이틀 바 42px 는 늘어나지 않는다 (9-slice top)</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.live.chat</t>
         </is>
       </c>
     </row>
@@ -10181,12 +10181,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/live_dialogue.png</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">1040×200</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 용사 대사 배너 (무전이 열리면 뜬다)</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.live.dialogue</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10221,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/live_door.png</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">1182×936</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">③ 갈림길 문 오버레이 (무전 3택)</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.live.door</t>
         </is>
       </c>
     </row>
@@ -10261,116 +10261,876 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/live_floors.png</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210×936</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 좌측 층계 게이지 (탑 단면)</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.floors</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2">
+        <v>4</v>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_lantern.png</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">460×568</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 랜턴 든 팔 (우하단 전경)</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.lantern</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2">
+        <v>4</v>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_map.png</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620×786</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 플레이어가 보는 지도 (찢어진 종이)</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.map</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2">
+        <v>4</v>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_noise.png</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182×936</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 방송 잡음 1장 (씬이 뒤집어 가며 쓴다)</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2">
+        <v>4</v>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_radio.png</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220×420</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 무전기</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2">
+        <v>4</v>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/live_superchat.png</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383×62</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">③ 슈퍼챗 팝업 판 — 받은 원본이 383x62 라 1:1 로 놓는다</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.live.superchat</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2">
+        <v>4</v>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/logo.png</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890×756</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타이틀 로고</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2">
+        <v>4</v>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/newspaper_day1.png</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1072×1058</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day 1 end-of-day newspaper</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.newspaper.day1</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2">
+        <v>4</v>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/newspaper_day2.png</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1072×1058</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day 2 end-of-day newspaper</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.newspaper.day2</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2">
+        <v>4</v>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/newspaper_day3.png</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1072×1058</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day 3 end-of-day newspaper</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.newspaper.day3</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2">
+        <v>4</v>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/newspaper_day4.png</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1072×1058</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day 4 end-of-day newspaper</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.newspaper.day4</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2">
+        <v>4</v>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/revive_record.png</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740×1226</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소생실 사망 기록 서류 — 책상 위 축소본과 확대 리더가 같은 그림을 쓴다</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.revive.record</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0">
+        <v>4</v>
+      </c>
+      <c r="B267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2">
+        <v>4</v>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154×161</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.shelf.arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2">
+        <v>4</v>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/stats_sheet.png</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">705×891</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submitted hero descent estimate and stat sheet</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.stats.sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2">
+        <v>4</v>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion1.png</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion1</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2">
+        <v>4</v>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion2.png</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion2</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2">
+        <v>4</v>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2">
+        <v>4</v>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2">
+        <v>4</v>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/suspicion5.png</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×128</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.suspicion5</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="0">
-        <v>4</v>
-      </c>
-      <c r="B256" s="0" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="0">
+        <v>4</v>
+      </c>
+      <c r="B275" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C256" s="0" t="inlineStr">
+      <c r="C275" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D256" s="0" t="inlineStr">
+      <c r="D275" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E256" s="0" t="inlineStr">
+      <c r="E275" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F256" s="0" t="inlineStr">
+      <c r="F275" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G256" s="0" t="inlineStr">
+      <c r="G275" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H256" s="0" t="inlineStr">
+      <c r="H275" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="0">
-        <v>4</v>
-      </c>
-      <c r="B257" s="0" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="0">
+        <v>4</v>
+      </c>
+      <c r="B276" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C257" s="0" t="inlineStr">
+      <c r="C276" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D257" s="0" t="inlineStr">
+      <c r="D276" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E257" s="0" t="inlineStr">
+      <c r="E276" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F257" s="0" t="inlineStr">
+      <c r="F276" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G257" s="0" t="inlineStr">
+      <c r="G276" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H257" s="0" t="inlineStr">
+      <c r="H276" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H257"/>
+  <autoFilter ref="A1:H276"/>
 </worksheet>
 </file>
--- a/아트-발주서.xlsx
+++ b/아트-발주서.xlsx
@@ -10701,12 +10701,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/revive_record.png</t>
+          <t xml:space="preserve">ui/revive_mark_wound.png</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740×1226</t>
+          <t xml:space="preserve">75×79</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">소생실 사망 기록 서류 — 책상 위 축소본과 확대 리더가 같은 그림을 쓴다</t>
+          <t xml:space="preserve">소생실 부위 마크 — 손상 부위에 덮어씌우는 상처 표시</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -10726,47 +10726,47 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.revive.record</t>
+          <t xml:space="preserve">ui.revive.mark.wound</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="0">
-        <v>4</v>
-      </c>
-      <c r="B267" s="0" t="inlineStr">
+      <c r="A267" s="2">
+        <v>4</v>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C267" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/seal.png</t>
-        </is>
-      </c>
-      <c r="D267" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768×192</t>
-        </is>
-      </c>
-      <c r="E267" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
-        </is>
-      </c>
-      <c r="F267" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉랍 도장 4프레임</t>
-        </is>
-      </c>
-      <c r="G267" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대기</t>
-        </is>
-      </c>
-      <c r="H267" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.seal</t>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/revive_mark.png</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532×226</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소생실 부위 마크 — 마크+연결선+빈 라벨 박스 (부위명은 코드가 넣는다)</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.revive.mark</t>
         </is>
       </c>
     </row>
@@ -10781,22 +10781,22 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/shelf_arrow.png</t>
+          <t xml:space="preserve">ui/revive_record.png</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154×161</t>
+          <t xml:space="preserve">740×1226</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확히 1/2 (77x80)</t>
+          <t xml:space="preserve">1:1</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
+          <t xml:space="preserve">소생실 사망 기록 서류 — 책상 위 축소본과 확대 리더가 같은 그림을 쓴다</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -10806,47 +10806,47 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.shelf.arrow</t>
+          <t xml:space="preserve">ui.revive.record</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2">
-        <v>4</v>
-      </c>
-      <c r="B269" s="2" t="inlineStr">
+      <c r="A269" s="0">
+        <v>4</v>
+      </c>
+      <c r="B269" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 기타</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui/stats_sheet.png</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">705×891</t>
-        </is>
-      </c>
-      <c r="E269" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F269" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Submitted hero descent estimate and stat sheet</t>
-        </is>
-      </c>
-      <c r="G269" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H269" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ui.stats.sheet</t>
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/seal.png</t>
+        </is>
+      </c>
+      <c r="D269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768×192</t>
+        </is>
+      </c>
+      <c r="E269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×192 프레임 1칸 (1:1)</t>
+        </is>
+      </c>
+      <c r="F269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉랍 도장 4프레임</t>
+        </is>
+      </c>
+      <c r="G269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기</t>
+        </is>
+      </c>
+      <c r="H269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.seal</t>
         </is>
       </c>
     </row>
@@ -10861,22 +10861,22 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion1.png</t>
+          <t xml:space="preserve">ui/shelf_arrow.png</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">154×161</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1</t>
+          <t xml:space="preserve">정확히 1/2 (77x80)</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">진열대 지시 화살표 — 고른 장비를 놓을 칸 위에 뜬다</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion1</t>
+          <t xml:space="preserve">ui.shelf.arrow</t>
         </is>
       </c>
     </row>
@@ -10901,12 +10901,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion2.png</t>
+          <t xml:space="preserve">ui/stats_sheet.png</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192×128</t>
+          <t xml:space="preserve">705×891</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">Submitted hero descent estimate and stat sheet</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion2</t>
+          <t xml:space="preserve">ui.stats.sheet</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion3.png</t>
+          <t xml:space="preserve">ui/suspicion1.png</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">의심도 1/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion3</t>
+          <t xml:space="preserve">ui.suspicion1</t>
         </is>
       </c>
     </row>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/suspicion4.png</t>
+          <t xml:space="preserve">ui/suspicion2.png</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+          <t xml:space="preserve">의심도 2/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui.suspicion4</t>
+          <t xml:space="preserve">ui.suspicion2</t>
         </is>
       </c>
     </row>
@@ -11021,116 +11021,196 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">ui/suspicion3.png</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 3/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion3</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2">
+        <v>4</v>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/suspicion4.png</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192×128</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의심도 4/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui.suspicion4</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2">
+        <v>4</v>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI · 기타</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ui/suspicion5.png</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192×128</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:1</t>
-        </is>
-      </c>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1:1</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">의심도 5/5 — 눈이 떠지는 5단 (5장 다 있어야 승계 화면에 뜬다)</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도착</t>
-        </is>
-      </c>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도착</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.suspicion5</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="0">
-        <v>4</v>
-      </c>
-      <c r="B275" s="0" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="0">
+        <v>4</v>
+      </c>
+      <c r="B277" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C275" s="0" t="inlineStr">
+      <c r="C277" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel_sunken.png</t>
         </is>
       </c>
-      <c r="D275" s="0" t="inlineStr">
+      <c r="D277" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E275" s="0" t="inlineStr">
+      <c r="E277" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F275" s="0" t="inlineStr">
+      <c r="F277" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (함몰 · 목록/채팅창)</t>
         </is>
       </c>
-      <c r="G275" s="0" t="inlineStr">
+      <c r="G277" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H275" s="0" t="inlineStr">
+      <c r="H277" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.sunken.9s</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="0">
-        <v>4</v>
-      </c>
-      <c r="B276" s="0" t="inlineStr">
+    <row r="278">
+      <c r="A278" s="0">
+        <v>4</v>
+      </c>
+      <c r="B278" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">UI · 패널</t>
         </is>
       </c>
-      <c r="C276" s="0" t="inlineStr">
+      <c r="C278" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui/panel.png</t>
         </is>
       </c>
-      <c r="D276" s="0" t="inlineStr">
+      <c r="D278" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">48×48</t>
         </is>
       </c>
-      <c r="E276" s="0" t="inlineStr">
+      <c r="E278" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">버튼/패널 크기에 맞춰 늘어난다</t>
         </is>
       </c>
-      <c r="F276" s="0" t="inlineStr">
+      <c r="F278" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">패널 테두리 (융기)</t>
         </is>
       </c>
-      <c r="G276" s="0" t="inlineStr">
+      <c r="G278" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">대기</t>
         </is>
       </c>
-      <c r="H276" s="0" t="inlineStr">
+      <c r="H278" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ui.panel.9s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H276"/>
+  <autoFilter ref="A1:H278"/>
 </worksheet>
 </file>